--- a/research/phrasal-verbs/candidates.xlsx
+++ b/research/phrasal-verbs/candidates.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:R156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,12 +441,14 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="90" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="90" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,30 +504,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>pd_hits</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pd_ulster_hits</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>examples</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>lookup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ulster_attested</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>proposed_meaning</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>phil_verdict</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -572,28 +584,38 @@
       <c r="J2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Nuair a chuaigh Éamonn i mbun oibre bhí sé i gceist aige an oifig a riar go héifeachtach ach chuir na riaráistí oibre alltacht air. [UD_Irish-IDT 547, CC BY-SA 3.0]
 Cuirfidh gach imreoir fáilte roimh na gnéithe nua seo ach níl aon amhras ann ach nach mbeadh na hathruithe seo tarlaithe murach an brú a chuir an GPA orthu, agus go mbeidh a thuilleadh ag teacht. [UD_Irish-IDT 649, CC BY-SA 3.0]
 Tá Brian Friel i ndiaidh cead a thabhairt don chomhlacht drámaíochta Aisling Ghéar an chéad leagan Gaeilge dá mhórshaothar Dancing at Lughnasa a chur ar an ardán. [UD_Irish-IDT 767, CC BY-SA 3.0]
 Cha shoirbh triubhas a chur air cat. = It's not easy to put breeches on a cat. [Tatoeba 5745698, CC BY 2.0 FR]
 Chuir sí a coinne ar ceal. = She cancelled her date. [Tatoeba 4521014, CC BY 2.0 FR]
-Ta cios, cana, deachmhadh, sraith contae agus teampuill róthrom, agus ni fuláir a mbeith an faid bheidh an fiach righe, .i. an fiac Sasanach, .i. an fiach do thosadh Rig Uilliam do chur ar an righeacht chum an creidimh gallda do chongbhail suas, agus an creidimh caitliceach do chur sios. [UD_Irish-Cadhan cinlae-244, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+Ta cios, cana, deachmhadh, sraith contae agus teampuill róthrom, agus ni fuláir a mbeith an faid bheidh an fiach righe, .i. an fiac Sasanach, .i. an fiach do thosadh Rig Uilliam do chur ar an righeacht chum an creidimh gallda do chongbhail suas, agus an creidimh caitliceach do chur sios. [UD_Irish-Cadhan cinlae-244, pre-standard, CC BY-SA 4.0]
+Do thiormuig sé iad agus do ghlan sé iad agus chuir sé ar altóir iad agus d'ídhbir sé iad chum na ndéithe úd. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Do cuireadh ar chapal éigin eile iad. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cuir_ar#Irish
 https://tatoeba.org/en/sentences/show/5745698
 https://tatoeba.org/en/sentences/show/4521014
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -636,28 +658,38 @@
       <c r="J3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="n">
+        <v>1091</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Tá mac léinn curtha go Meiriceá ag Foras na Mara agus é ag staidéar i gcuideachta na saineolaithe a rinne an taighde mhór ar na bradáin, sna hochtóidí. [UD_Irish-IDT 482, CC BY-SA 3.0]
 Déantar ar an gcaoi sin den fhéar suaithinseach an paiste slán i lár na ndriseacha agus na bhfiailí inar luigh slán an 'abhlainn bheannaithe a thit uainn fadó', siombail na glaineachta agus na neamhurchóide agus an bhearna trína dtiocfar ar an mbeatha spioradálta atá ionann is ceilte agus plúchta ag na fiailí, ar mar a chéile iad agus an ghné aimrid de nádúr an duine. [UD_Irish-IDT 505, CC BY-SA 3.0]
 Agus tchítear domhsa go ndearnadh leithcheal orthu. [UD_Irish-IDT 536, CC BY-SA 3.0]
 Caithfear cabhair a dhéanamh ar chairde in am an ghátair. = One must help friends in times of such need. [Tatoeba 6319350, CC BY 2.0 FR]
 Déanaim staidéar ar an tSínis i mBéising. = I study Chinese in Beijing. [Tatoeba 3599594, CC BY 2.0 FR]
-Agus do lean buidhean mhór hé, tré gu bhfacadar a chomharthadha dorinne sé ar na dáoinibh éugcruaidhe. [UD_Irish-Cadhan eoin-224, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+Agus do lean buidhean mhór hé, tré gu bhfacadar a chomharthadha dorinne sé ar na dáoinibh éugcruaidhe. [UD_Irish-Cadhan eoin-224, pre-standard, CC BY-SA 4.0]
+Is ní fheicim leigheas ar mo ghalar féin ach scaird a dh'ól [Wikisource: Mná na hÉireann, Ulster-leaning, pre-standard, public domain]
+'S ní spárálfar fíon Spáinneach ar mo Róisín Dubh. [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/déan_ar#Irish
 https://tatoeba.org/en/sentences/show/6319350
 https://tatoeba.org/en/sentences/show/3599594
+https://wikisource.org/wiki/Mn%C3%A1_na_h%C3%89ireann
+https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -700,28 +732,38 @@
       <c r="J4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>) 'Tá mé buartha fán trioblóid uilig ach tabhair maithiúnas domh... 'Tá mé cinnte gur baineadh scanradh asat,' arsa Peadar. [UD_Irish-IDT 456, CC BY-SA 3.0]
 Caithfidh foirne úsáid a bhaint as na huimhreacha 4-15. [UD_Irish-IDT 466, CC BY-SA 3.0]
 Eascróidh na teicníochtaí measúnaithe a mbainfear leas astu go nádúrtha as an teagasc agus as an bhfoghlaim agus beidh a n-éifeacht ag brath ar chomh hinniúil agus a bheidh an múinteoir ar bhreathnóireacht, ar éisteacht, ar idirghníomhú leis na daltaí agus ar thorthaí a dtascanna foghlama san eolaíocht a mhionscrúdú. [UD_Irish-IDT 790, CC BY-SA 3.0]
 Ar mhaith leat triail a bhaint as? = Would you like to give it a try? [Tatoeba 6319315, CC BY 2.0 FR]
 Ba mhaith linn thú taitneamh a bhaint as. = We want you to have a good time. [Tatoeba 6319300, CC BY 2.0 FR]
-Bhain mé as, agus dhá mbeadh eochair na bhflaitheas in mo phóca, ní fhéadfadh níos mó luthgháire a bheith orm. [UD_Irish-Cadhan deoraidheacht-1933, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+Bhain mé as, agus dhá mbeadh eochair na bhflaitheas in mo phóca, ní fhéadfadh níos mó luthgháire a bheith orm. [UD_Irish-Cadhan deoraidheacht-1933, pre-standard, CC BY-SA 4.0]
+Do dhruid an t-asal i leith taoibh agus do ghluais an capal cogaidh thairis amach ar cos anáirde agus teine chreasa aige d’á bhaint as na clochaibh. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Níor mharbhadh ann é acht do baineadh an tsúil as. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bain_as#Irish
 https://tatoeba.org/en/sentences/show/6319315
 https://tatoeba.org/en/sentences/show/6319300
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
 https://www.teanglann.ie/en/fgb/bain</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -764,28 +806,38 @@
       <c r="J5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Dar leis an Ríordánach sa dán Teitheadh, is cosúla an fhilíocht le sacraimint eile, an fhaoistin, ná le comaoineach naofa; agus tugann sé peaca ar an dán dá réir: Do rugas liom don eaglais Mo chnuasach nuapheacaí, Do chuireas iad in eagar Don fhoilsitheoir a bhíonn Ag cló-dhearmhad peacaí. [UD_Irish-IDT 506, CC BY-SA 3.0]
 Thug na páistí ruaig amháin ar an siopa sin. [UD_Irish-IDT 553, CC BY-SA 3.0]
 Díríodh lá amháin den tseimineár seo ar fhorbairt an tionscnaimh, SCÉAL, agus ag labhairt anseo bhí an Stiúrthóir Marial Hannon, a thug léargas ar bhunús agus todhchaí an tionscnaimh, an léiritheoir teilifíse, Concubhar Ó Liatháin a léirigh mar a raibh an scéim fite fuaite le traidisiún scéalaíochta na hÉireann agus An Dr. Pádraig Ó Criomhthainn ó Choláiste na hOllscoile, Baile Átha Cliath, a mhínigh conas mar a d'fhéadfaí córais nua teileachumarsáide, an Internet mar shampla, a úsáid chun SCÉAL a insint ar fud an domhain. [UD_Irish-IDT 567, CC BY-SA 3.0]
 Níor thug mé freagra ar litir Tom go fóill. = I haven't replied to Tom's letter yet. [Tatoeba 2936185, CC BY 2.0 FR]
 Nuair a thugaim bia do na boicht, tugtar naomh orm. Nuair a chuirim an cheist, cén fáth nach bhfuil bia ag na boicht, tugtar cumannaí orm. = When I give food to the poor, they call me a saint. When I ask why the poor have no food, they call me a communist. [Tatoeba 3081772, CC BY 2.0 FR]
-Bhamar ag tabhairt mine buidhe amach andiu ar tri leath-phinginighe an pota: ta spirid na nGaodhal briste sios go mor: trosga. [UD_Irish-Cadhan cinlae-143, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+Bhamar ag tabhairt mine buidhe amach andiu ar tri leath-phinginighe an pota: ta spirid na nGaodhal briste sios go mor: trosga. [UD_Irish-Cadhan cinlae-143, pre-standard, CC BY-SA 4.0]
+Do thárla, roimis amach ag gabháil an bóthar céadna, asal bocht agus é tuirseach agus ualach trom air. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Féuchaint d’á dtug an machtíre ar mhuineál an ghadhair chonaic sé rud éigin. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tabhair_ar#Irish
 https://tatoeba.org/en/sentences/show/2936185
 https://tatoeba.org/en/sentences/show/3081772
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
 https://www.teanglann.ie/en/fgb/tabhair</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -828,24 +880,34 @@
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Ach, ina dhiaidh sin féin, bíonn contúirt bhreise ag baint leis an iomarca meáchain, go háirithe má bhíonn míbhuntáistí eile sláinte ag an duine. [UD_Irish-IDT 558, CC BY-SA 3.0]
 Baineann an riail seo leis an gcomórtas le foirne 11. [UD_Irish-IDT 716, CC BY-SA 3.0]
 Bhí piseog ag baint leis nach cóir duit é a bhaint. [UD_Irish-IDT 728, CC BY-SA 3.0]
-Ní fheadar an í bainrioghan na bruighne do thóg an stoirm, agus chuir an fraoch feargach so ar aigheadh neimhe, i ttaobh me baint le caonach a leapthann, agus bolgan beicighe a h-iomhadh. [UD_Irish-Cadhan cinlae-303, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+Ní fheadar an í bainrioghan na bruighne do thóg an stoirm, agus chuir an fraoch feargach so ar aigheadh neimhe, i ttaobh me baint le caonach a leapthann, agus bolgan beicighe a h-iomhadh. [UD_Irish-Cadhan cinlae-303, pre-standard, CC BY-SA 4.0]
+Isé a bhuac gan baint leis. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]
+Agus anuáir dochonnairc sé nach deacuidh aige air, do bhean sé re log a laghairce, agus dobhí log laghairce Iácob as alt, mar dobhí ag spáirn ris. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bain_le#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/bain</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -888,28 +950,38 @@
       <c r="J7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Déantar ar an gcaoi sin den fhéar suaithinseach an paiste slán i lár na ndriseacha agus na bhfiailí inar luigh slán an 'abhlainn bheannaithe a thit uainn fadó', siombail na glaineachta agus na neamhurchóide agus an bhearna trína dtiocfar ar an mbeatha spioradálta atá ionann is ceilte agus plúchta ag na fiailí, ar mar a chéile iad agus an ghné aimrid de nádúr an duine. [UD_Irish-IDT 505, CC BY-SA 3.0]
 A mhná uaisle agus a uaisle go léir, níl sé i gceist agam am a chur amú chun teacht ar réiteach na faidhbe seo... dhein Bricriú iarracht bob a bhualadh oraibh, ach níor éirigh leis. [UD_Irish-IDT 508, CC BY-SA 3.0]
 Bheadh spochadh agus saighdeadh agus argóintí acu, ach nuair a thiocfadh an crú ar an tairne d'fhéadfaí brath orthu. [UD_Irish-IDT 511, CC BY-SA 3.0]
 Buíochas le Dia gur tháinig tú orm. = Thank God you found me. [Tatoeba 5516931, CC BY 2.0 FR]
 D'fhéach Tomás agus Máire ar a chéile agus tháinig meangadh gáire orthu. = Tom and Mary looked at each other and smiled. [Tatoeba 4062775, CC BY 2.0 FR]
-Thangas abhaile air mo socracht. [UD_Irish-Cadhan cinlae-17, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+Thangas abhaile air mo socracht. [UD_Irish-Cadhan cinlae-17, pre-standard, CC BY-SA 4.0]
+Tháinig an dá ghaisgídheach ar an láthair catha agus isé arm a bhí ag gach gaisgídheach acu ’ná brobh maith láidir luachra agus bior air. [Wikisource: Aesop a tháinig go h-Éirinn/An Fhiolar agus an Mada Ruadh, pre-standard, public domain]
+Tháinig machtíre lá ar gabhar, agus uan ’ghá deól. [Wikisource: Aesop a tháinig go h-Éirinn/An Luch Tuatha agus Luch an Bhaile Mhóir, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tar_ar#Irish
 https://tatoeba.org/en/sentences/show/5516931
 https://tatoeba.org/en/sentences/show/4062775
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Fhiolar_agus_an_Mada_Ruadh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Luch_Tuatha_agus_Luch_an_Bhaile_Mh%C3%B3ir
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -952,27 +1024,37 @@
       <c r="J8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>A mhná uaisle agus a uaisle go léir, níl sé i gceist agam am a chur amú chun teacht ar réiteach na faidhbe seo... dhein Bricriú iarracht bob a bhualadh oraibh, ach níor éirigh leis. [UD_Irish-IDT 508, CC BY-SA 3.0]
 'De réir phobalbhreith an Galway Advertiser, an tseachtain seo caite, tá gach seans ann go n-éireoidh le FF an tríú suíochán a bhaint amach i nGaillimh Thiar (slán leat, a Bhobby Molloy? [UD_Irish-IDT 548, CC BY-SA 3.0]
 chomh maith leis na tionscnaimh atá liostaithe faoi straitéis 2, trí chistiú a chur ar fáil do chompántais ceoldrámaíochta atá ag iarraidh ardchaighdeán ealaíonta agus/nó nuálachais a bhaint amach nó a n-éiríonn leo na caighdeáin seo a bhaint amach cheana féin agus trí chistiú a chur ar fáil chun ceoldrámaí nua agus tionscnaimh ceoldrámaíochta a choimisiúnú. [UD_Irish-IDT 637, CC BY-SA 3.0]
 D’éirigh leis an obair. = The work was successful. [Tatoeba 874930, CC BY 2.0 FR]
-D’éirigh liom san obair. = I succeeded in the work. [Tatoeba 874926, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+D’éirigh liom san obair. = I succeeded in the work. [Tatoeba 874926, CC BY 2.0 FR]
+Níor éirigh liom Gaedhilg d’fhagháil ar , dá mhéad dár chuardaigheas, acht dá mbeadh Gaedhilg air, is dócha gur “Cill Bhoth” a bheadh ann, acht nuair nach fuaras ughdarthás ná baránta leis sin, do leigeas dó. [Wikisource: Alasdair Mac Colla/Brollach, pre-standard, public domain]
+An oidhche dheire chuadhas an bealach, mé féin agus mo charrín asail, acht níor éirigh liom dhul isteach ar an tsráid-bhaile mar a raibh mo thriall. [Wikisource: An Crann Géagach/Crann na Croiche, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/éirigh_le#Irish
 https://tatoeba.org/en/sentences/show/874930
 https://tatoeba.org/en/sentences/show/874926
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Brollach
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Crann_na_Croiche
 https://www.teanglann.ie/en/fgb/éirigh</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1015,25 +1097,35 @@
       <c r="J9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>'De réir phobalbhreith an Galway Advertiser, an tseachtain seo caite, tá gach seans ann go n-éireoidh le FF an tríú suíochán a bhaint amach i nGaillimh Thiar (slán leat, a Bhobby Molloy? [UD_Irish-IDT 548, CC BY-SA 3.0]
 chomh maith leis na tionscnaimh atá liostaithe faoi straitéis 2, trí chistiú a chur ar fáil do chompántais ceoldrámaíochta atá ag iarraidh ardchaighdeán ealaíonta agus/nó nuálachais a bhaint amach nó a n-éiríonn leo na caighdeáin seo a bhaint amach cheana féin agus trí chistiú a chur ar fáil chun ceoldrámaí nua agus tionscnaimh ceoldrámaíochta a choimisiúnú. [UD_Irish-IDT 637, CC BY-SA 3.0]
 chomh maith leis na tionscnaimh atá liostaithe faoi straitéis 2, trí chistiú a chur ar fáil do chompántais ceoldrámaíochta atá ag iarraidh ardchaighdeán ealaíonta agus/nó nuálachais a bhaint amach nó a n-éiríonn leo na caighdeáin seo a bhaint amach cheana féin agus trí chistiú a chur ar fáil chun ceoldrámaí nua agus tionscnaimh ceoldrámaíochta a choimisiúnú. [UD_Irish-IDT 637, CC BY-SA 3.0]
-Bhain siad an ceann scríbe amach. = They reached their destination. [Tatoeba 5648268, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+Bhain siad an ceann scríbe amach. = They reached their destination. [Tatoeba 5648268, CC BY 2.0 FR]
+Colla Uais, iomorro, do bhain amach Cúigeadh Uladh ó Chlannaibh Rudhraighe, is uaidh do shíolruigh an Chlann Domhnaill seo ag a raibh Inse Gall agus seacht dtuatha na nGlinne i nDáil Riada fá n-a smacht ar feadh na gcéadta mbliadhan. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, I, pre-standard, public domain]
+Tharraing an bhean píosa coróineach amach agus thug dom é. [Wikisource: An Mháthair agus Sgéalta Eile/An Bhean Chaointe, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bain_amach#Irish
 https://tatoeba.org/en/sentences/show/5648268
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_I
+https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/An_Bhean_Chaointe
 https://www.teanglann.ie/en/fgb/bain</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1072,22 +1164,32 @@
       <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Thug siad faoina chéile go crua dána. [UD_Irish-IDT 517, CC BY-SA 3.0]
 Le bliain nó dhó anuas amháin a thosaigh sé ag tabhairt na difríochta faoi deara. [UD_Irish-IDT 23, CC BY-SA 3.0]
-Duine fíorthuisceanach é Ciarán a thug faoi deara go luath buanna Chaitlín Maude. [UD_Irish-IDT 179, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+Duine fíorthuisceanach é Ciarán a thug faoi deara go luath buanna Chaitlín Maude. [UD_Irish-IDT 179, CC BY-SA 3.0]
+Acht le méid a bhfuath d’á chéile agus le méid a ngúbha do’n chómhrac níor thugadar fé ndeara an seabhac. [Wikisource: Aesop a tháinig go h-Éirinn/An Fhiolar agus an Mada Ruadh, pre-standard, public domain]
+Fé dheire thug an t-aodhre fé ndeara é. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aodhre agus an Fharge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Fhiolar_agus_an_Mada_Ruadh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-Aodhre_agus_an_Fharge
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1126,26 +1228,36 @@
       <c r="J11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Is é an rud a dúirt an tIndiach leis an Iosánach ansin: 'Níl a fhios agat cad tá á rá agat; foghlaim conas labhairt agus éisteoimid leat. [UD_Irish-IDT 875, CC BY-SA 3.0]
 Troideadh an cás i nGaeilge os comhair an Bhreithimh Peter Kelly agus cheadaigh seisean toirmeasc a chuireann cosc ar Stiúrthóir na nIonchúiseamh Poiblí, atá ag glacadh an cháis thar ceann an Gharda, a chuireann cosc air an cás a chur chun na Cúirte Dúiche go dtí go n-éistfear leis an chás iomlán san Ard-Chúirt. [UD_Irish-IDT 110, CC BY-SA 3.0]
 'Éist leis. [UD_Irish-IDT 199, CC BY-SA 3.0]
 An bhfuil tú ag éisteacht le ceol? = Are you listening to music? [Tatoeba 4001480, CC BY 2.0 FR]
-Bhí Eimíle ag éisteacht le ceol. = Emily was listening to music. [Tatoeba 3467393, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+Bhí Eimíle ag éisteacht le ceol. = Emily was listening to music. [Tatoeba 3467393, CC BY 2.0 FR]
+D’ fhanadar-san ag féuchaint ar an luasgadh agus ag éisteacht leis an mbúirtheach. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]
+Anois uimesin, a mhic, éist rem ghlórsa, do réir an neithe aitéonus mé dhíot. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/4001480
 https://tatoeba.org/en/sentences/show/3467393
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/éist</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1188,24 +1300,34 @@
       <c r="J12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Bhainfinn díom mo chuid éadaí agus stróicfinn di a cuid sise agus ghabhfainn caol díreach ar mo ghlúine roimpi go bpógfainn le mire chuile mhiongán orlaigh di. [UD_Irish-IDT 846, CC BY-SA 3.0]
 A luaithe is a shroicheamar an stad bhí fear óg scafánta amach go dtí muid lenár dtrealamh bagáiste a bhaint dínn. [UD_Irish-IDT 370, CC BY-SA 3.0]
 Níos práinní ná sin chaithfeadh sé déanamh cinnte nach mbainfí de iad. [UD_Irish-IDT 411, CC BY-SA 3.0]
-Boicht an tshaogail ima seach dhíot as beite dhóibh buidheach ní thabhra ní dhóibh dot mhaoin 'sní bhena diobh do chomhmaoin. [UD_Irish-Cadhan bardic_1387-9, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+Boicht an tshaogail ima seach dhíot as beite dhóibh buidheach ní thabhra ní dhóibh dot mhaoin 'sní bhena diobh do chomhmaoin. [UD_Irish-Cadhan bardic_1387-9, pre-standard, CC BY-SA 4.0]
+Ba dhóich liom dá mbainfí dhíom í gurabh amhlaidh a bhéadh gach aoinne ag feuchaint orm a d’ iaraidh a dhéanamh amach ciacu mada ruadh mé nó banabh muice. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+trap nó inniol nó fiacal gadhair ’ghá bhaint díom, is mór an sásamh aigne liom a fhios do bheith agam uaitse go bhfuil na maithasaí úd go léir am chóir. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bain_de#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
 https://www.teanglann.ie/en/fgb/bain</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1248,28 +1370,38 @@
       <c r="J13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Buailimid leis an bhfeiniméan céanna, 'sé sin le rá meascadh síol na croise leis an síol atá á chur san earrach, i gcuntas suntasach ó Chontae Loch Garman:. [UD_Irish-IDT 609, CC BY-SA 3.0]
 'Dia dhuit, a Mhíchíl,' a deir Sándra leis, 'tá áthas orm bualadh leat. [UD_Irish-IDT 640, CC BY-SA 3.0]
 Agus bhuail lacha bhuí leo. [UD_Irish-IDT 145, CC BY-SA 3.0]
 An bhfuil tú ag bualadh le duine éigin anseo? = Are you meeting someone here? [Tatoeba 752751, CC BY 2.0 FR]
 Ba mhaith liom bualadh léi arís. = I want to meet her again. [Tatoeba 10317100, CC BY 2.0 FR]
-Bhíos ag cuimilt mo shúl agus ag ceapadh néal beag eile bheith agam, nuair a buaileadh an fhuinneóg a bhí lem' ais go haireach le slait. [UD_Irish-Cadhan deoraidheacht-2492, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+Bhíos ag cuimilt mo shúl agus ag ceapadh néal beag eile bheith agam, nuair a buaileadh an fhuinneóg a bhí lem' ais go haireach le slait. [UD_Irish-Cadhan deoraidheacht-2492, pre-standard, CC BY-SA 4.0]
+Fear a buaileadh le buidéal, fear eile le cloich. [Wikisource: An t-Oileánach/10, pre-standard, public domain]
+Do bhuail Liam liom i dtigh leanna, tigh Mhuirisín Bháin. [Wikisource: An t-Oileánach/14, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/buail_le#Irish
 https://tatoeba.org/en/sentences/show/752751
 https://tatoeba.org/en/sentences/show/10317100
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/10
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/14
 https://www.teanglann.ie/en/fgb/buail</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1308,26 +1440,36 @@
       <c r="J14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Ag an am sin, thug McCarthy le fios d'oifigeach nó beirt as an FAI go n-éireodh sé as an phost ach anois, áfach, ní dhéanfaidh. [UD_Irish-IDT 1194, CC BY-SA 3.0]
 Bhíodh sí dá shamhlú dó gach áit - an seibineach de ghiorria a d'éiríodh as a leaba dhearg - an t-éan ag ceiliúr ar an gcraobh - an bradán san abhainn, an breac sa loch - gach rud beo dearfa ba ar Mháirín a smaoiníodh sé nuair a d'fheicfeadh sé iad. [UD_Irish-IDT 1310, CC BY-SA 3.0]
 (2) Féadfidh cigire gach clár atá á chimeád do réir an ailt seo do scrúdú aon uair le linn tráthanna oifige chun aon chríche eireos as an Acht so no as aon rialachán a déanfar fé no a eireos de bharr ceachtar acu agus, ar a iarraidh sin don chigire, beidh sé de dhualgas ar únaer chláruithe an áitreibh ina bhfuil an clár san á chimeád an clár san do thaisbeáint, chun go scrúdóidh an cigire sin é, agus fós gach billín, nóta consighneachta, admháil, agus scríbhinn eile (ar a n-áirítear cóipeanna dhíobh i gcás gan iad féin a bheith ar fáil) a iarrfidh an cigire sin go réasúnta chun féachaint an fíor aon iontráil áirithe sa chlár san no cad fé ndeár éinní áirithe d'fhágaint amach as. [UD_Irish-IDT 1375, CC BY-SA 3.0]
 Chomhairligh an dochtúir é éirí as an ól. = The doctor advised him to give up drinking. [Tatoeba 5228133, CC BY 2.0 FR]
-Chomhairligh an dochtúir leis gur fearr éirí as an deoch. = The doctor advised him that it would be better to give up the drink. [Tatoeba 5168215, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+Chomhairligh an dochtúir leis gur fearr éirí as an deoch. = The doctor advised him that it would be better to give up the drink. [Tatoeba 5168215, CC BY 2.0 FR]
+Do éirigh Alasdair as an teint amach agus ráinic an lóisdín ina rabha Domhnall agus do ráidh ris: “A Dhomhnaill, a mhic,” ar sé, “déin ullmhughadh do mhuinntre do chum creach do thabhairt don champa agus bídís réidh agad go gluasacht ar maidin amárach agus ní racha leat acht do mhuinntir féin agus lucht eoluis don tír dá mbí ar n-ordughadh.” Do fuaradar a n-ordughadh ar maidin ’na diaidh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Éirigh amach as an Áirc, tú féin agus do bhean, agus do mhic, agus mná do mhac leachd. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/5228133
 https://tatoeba.org/en/sentences/show/5168215
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/éirigh</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1370,25 +1512,35 @@
       <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Táthar á rá gurb í is ciontach le galar nua ar a dtugtar 'bréagthochtán' - tinneas a chuireann isteach ar pháistí go háirithe. [UD_Irish-IDT 419, CC BY-SA 3.0]
 Is féidir le haon soláthraí ar mian leis a bheith ar an bpainéal cur isteach air. [UD_Irish-IDT 3927, CC BY-SA 3.0]
 Más mian leo breis is trí mhí a chaitheamh ann, tá dualgas orthu cur isteach ar cheadúnas cónaithe, a chruthú go bhfuil árachas sláinte sásúil acu, agus nach mbeidh siad ag brath ar an gcóras leasa shóisialaigh sa bhallstát sin. [UD_Irish-IDT 4503, CC BY-SA 3.0]
-Chuirfeadh sibh isteach ar an phost sin. = You would apply for that job. [Tatoeba 3090973, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+Chuirfeadh sibh isteach ar an phost sin. = You would apply for that job. [Tatoeba 3090973, CC BY 2.0 FR]
+nó mada ruadh, áracht aeir nó olphiast talmhan, ag cur isteach oraibh, mise do throidfadh iad, agus d’ imreóchadh bás le gob a’s le h-ingnibh ortha, nó thabharfadh a leithéid sin de sgeimhle agus d’anfa dhoibh, ’ghá ruagadh agus ’ghá ndíbirt, nár bhaoghal go bhfíllfidís.” [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]
+Níor chuireas isteach uirri. [Wikisource: An Crann Géagach/An bhean bhí ag an bhfuinneóig, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cuir_isteach_ar#Irish
 https://tatoeba.org/en/sentences/show/3090973
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_bhean_bh%C3%AD_ag_an_bhfuinne%C3%B3ig
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1427,22 +1579,32 @@
       <c r="J16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Bhí an Pluincéadach tar éis daoine a chur amach i gceartlár an gheimhridh agus i lár na doininne, agus bhí de dhánaíocht san fhear chéanna sin a rá gurbh easpag é ar aon dul le Naomh Pól - ba é Easpag an fhíona is na gcearc fraoigh é. [UD_Irish-IDT 533, CC BY-SA 3.0]
 Rinne Íosa iarracht ar shólás a thabhairt dóibh: 'Chuir mé amach sa saol sibh gan sparán, ná mála, ná bróga - an raibh aon rud de dhíth oraibh? [UD_Irish-IDT 599, CC BY-SA 3.0]
-Chuiridís oilithrigh amach go dtí Compostela mar ionadaithe thar cionn a muintire go léir agus bhailítí airgead chuige sin sa Chladach. [UD_Irish-IDT 941, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cuir</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+Chuiridís oilithrigh amach go dtí Compostela mar ionadaithe thar cionn a muintire go léir agus bhailítí airgead chuige sin sa Chladach. [UD_Irish-IDT 941, CC BY-SA 3.0]
+Chuir sé sgéala amach gur mhaith leis a chómharsain go léir do theacht chuige ar aon láthair, i lios áirighthe a bhí i lár coille. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+Do cuireadh amach a harm an ríogh cuideachta agus Mághnus mac an Ghiolla Dhuibh Í Chatháin rompa, agus do cuireadh cuideachta eile ’na n-aghaidh as arm Mhic Cailín agus Giolla-Easbuig mac Giolla-Easbuig Óig, tighearna na bPingingeadh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://www.teanglann.ie/en/fgb/cuir</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1485,25 +1647,35 @@
       <c r="J17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Sa meathdhorchadas sin d'fhéadas an stáitse a dhéanamh amach ar éigean faoina shoilse fanna néoin. [UD_Irish-IDT 193, CC BY-SA 3.0]
 Anois, áfach, iontaím thart an seanchreideamh sin a raibh tacaíocht an tí iomláin leis, agus déanaim amach.... [UD_Irish-IDT 1233, CC BY-SA 3.0]
 Déan amach bosca mar seo i do leabhar agus cuir na briathra seo a leanas sna háiteanna cearta. [UD_Irish-IDT 1714, CC BY-SA 3.0]
-Ní raibh muid in ann déanamh amach ceard a bhí Paul ag iarraidh a dhéanamh. = We couldn't figure out what Paul wanted to do. [Tatoeba 5015996, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+Ní raibh muid in ann déanamh amach ceard a bhí Paul ag iarraidh a dhéanamh. = We couldn't figure out what Paul wanted to do. [Tatoeba 5015996, CC BY 2.0 FR]
+Ansan dob áil le Bhénus a dhéanamh amach ar athruig aigne an chait fé mar athruig a gné. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Do theip ortha a dhéanamh amach sa pháirc, áit ba dhóichíghe ’ná a chéile chum an airgid do bheith ann. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aodhre agus an Fharge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/déan_amach#Irish
 https://tatoeba.org/en/sentences/show/5015996
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-Aodhre_agus_an_Fharge
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1546,25 +1718,35 @@
       <c r="J18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Rinne sé comhréiteach éigin leis féin, ag ligean a uillinne ar chathaoir, agus ag cromadh go tútach le go sílfí gur ar a ghlúine a bhí sé, nó, ar a laghad, go dtuigfí nach ina shuí a bhí sé. [UD_Irish-IDT 221, CC BY-SA 3.0]
 Ach ní ligeadh siad orthu féin le chéile fá na smaointíocha sin. [UD_Irish-IDT 2514, CC BY-SA 3.0]
 Níl sé oiriúnach dar linn leabhair áirithe a ligean ar iasacht don phobal. [UD_Irish-IDT 3343, CC BY-SA 3.0]
-lig mé air go raibh tinneas nímneach orm. = I pretended I had pneumonia. [Tatoeba 11841359, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+lig mé air go raibh tinneas nímneach orm. = I pretended I had pneumonia. [Tatoeba 11841359, CC BY 2.0 FR]
+Acht chum a leigint air go raibh sé ag ithe d’aimsigh sé dias cruithneachtan agus bhí sé ’ghá piocadh. [Wikisource: Aesop a tháinig go h-Éirinn/An Luch Tuatha agus Luch an Bhaile Mhóir, pre-standard, public domain]
+Do leig sé é féin ar a leath ghlúin chum an urchair do chaitheamh. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aṫair Níṁe agus an Portán, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/lig_ar#Irish
 https://tatoeba.org/en/sentences/show/11841359
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Luch_Tuatha_agus_Luch_an_Bhaile_Mh%C3%B3ir
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-A%E1%B9%ABair_N%C3%AD%E1%B9%81e_agus_an_Port%C3%A1n
 https://www.teanglann.ie/en/fgb/lig</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1603,26 +1785,36 @@
       <c r="J19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Seasaim le balla trasna uathu dá bhféachaint nóiméad. [UD_Irish-IDT 601, CC BY-SA 3.0]
 An Domhnach seo ar Pháirc an Chrócaigh caithfidh siad féin agus Francis Bellew seasamh guaille ar ghuaille leis an líne lántosach is mó clú a tháinig as Ciarraí ó bhí aimsir Sheehy, Liston agus Egan ann. [UD_Irish-IDT 1020, CC BY-SA 3.0]
 Seasadh leis an diúltú nuair a rinne sé achomharc. [UD_Irish-IDT 1180, CC BY-SA 3.0]
 Is féidir leat seasamh suas más maith leat. = You can stand up if you want to. [Tatoeba 6319317, CC BY 2.0 FR]
-Seasaim leis an Téaváin. = I stand with Taiwan. [Tatoeba 13249266, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+Seasaim leis an Téaváin. = I stand with Taiwan. [Tatoeba 13249266, CC BY 2.0 FR]
+Dá seasadh sé taobh leis, bhí a mhalairt de chrích ar an marcós. [Wikisource: Alasdair Mac Colla/Réimhsgéal, pre-standard, public domain]
+An bile sheas talamh le ocht gcéad bliadhan má’s fíor na seanchaidhthe agus lucht crann-eólais—agus táid ar aon fhocal—an bile maordha sin agus a bhileóg uachtarach buailte le talamh! [Wikisource: An Crann Géagach/Crann na Croiche, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/6319317
 https://tatoeba.org/en/sentences/show/13249266
+https://wikisource.org/wiki/Alasdair_Mac_Colla/R%C3%A9imhsg%C3%A9al
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Crann_na_Croiche
 https://www.teanglann.ie/en/fgb/seas</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1665,23 +1857,33 @@
       <c r="J20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Labhair sí liom ar na bealaí a bhí ag údaráis na scoile brú a chur ar na daltaí a gcuid teangacha a thabhairt suas. [UD_Irish-IDT 6, CC BY-SA 3.0]
 Agus gan a thuilleadh a rá thug an Bainisteoir a aghaidh suas an staighre. [UD_Irish-IDT 84, CC BY-SA 3.0]
-Thug muid do na bonnachaí é suas abhaile. [UD_Irish-IDT 1836, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+Thug muid do na bonnachaí é suas abhaile. [UD_Irish-IDT 1836, CC BY-SA 3.0]
+Agus anuáir do chríochnuigh Iácob aitheanta do thabhairt dá chloinn, do chruinnigh súas a chosa san leabuigh agus do fáeidh a spiorad súas, agus do chruinniughadh chum a dhaóine féin é. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Tuairim leath-slí thug muc Dhiarmaid suas. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tabhair_suas#Irish
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
 https://www.teanglann.ie/en/fgb/tabhair</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1720,23 +1922,33 @@
       <c r="J21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Nuair a tógadh na scadáin ar bord fuair duine den chriú an slibire seo agus gob fada air. [UD_Irish-IDT 1188, CC BY-SA 3.0]
 Déanfar an t-árus do thabhairt suas, le cimeád ar iontaoibh don Chomhairle Chontae, don Ord Rialta san a thógfidh air féin an Teaghlach Contae sin do Leanbhaí do ghlaca féna chúram, agus san ar pé téarmaí agus coiníollacha a réiteofar idir an Ord san agus an Coiste Feidhmiúcháin. [UD_Irish-IDT 2230, CC BY-SA 3.0]
 Bronnadh an conradh chun ionad ilfheidhmeach seirbhísí agus fiontair a thógáil ar chostas €1.6m ar Eastát Tionscal Charna. [UD_Irish-IDT 4008, CC BY-SA 3.0]
-Gach uile oidhche ar an am chéadna, ar an naoi 'e chlog, ar an dó-dhéag, ar an trí, thógadh siad ceól oidhche, cantán uaigneach neamh-shaoghalta, agus ní iarrfadh Buck dhe phléisiúr ach cuidiú leó. [UD_Irish-Cadhan scairt-554, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+Gach uile oidhche ar an am chéadna, ar an naoi 'e chlog, ar an dó-dhéag, ar an trí, thógadh siad ceól oidhche, cantán uaigneach neamh-shaoghalta, agus ní iarrfadh Buck dhe phléisiúr ach cuidiú leó. [UD_Irish-Cadhan scairt-554, pre-standard, CC BY-SA 4.0]
+“Feuch!” ar seisean, “a dhuine mhuínteartha, ná tóg orm é má dhéinim dánaídheacht ort. [Wikisource: Aesop a tháinig go h-Éirinn/An Luch Tuatha agus Luch an Bhaile Mhóir, pre-standard, public domain]
+Agus tárla anuáir do reitheadh an áirnéis gur thóg misi mo shúile súas ar an áirnéis go rabhadur síoghach bhallach, measctha. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Luch_Tuatha_agus_Luch_an_Bhaile_Mh%C3%B3ir
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1775,22 +1987,32 @@
       <c r="J22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>'An gcoinneochaidh tú do shúil ar an fhuinneog sin thiar? [UD_Irish-IDT 2751, CC BY-SA 3.0]
 Coinneofar Parlaimint na hEorpa agus na Parlaimintí náisiúnta ar an eolas faoina himeachtaí. [UD_Irish-IDT 3545, CC BY-SA 3.0]
-Ba í anuraidh an bhliain ab fhearr ó 1998 do chruthú fostaíochta sa Ghaeltacht de thairbhe gur cruthaíodh 1,186 post úrnua agus gur coinníodh srian ar chaillteanas post, rud a d’fhág go raibh gnóthachan glan de 295 post ann ar an iomlán. [UD_Irish-IDT 4019, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/coinnigh</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+Ba í anuraidh an bhliain ab fhearr ó 1998 do chruthú fostaíochta sa Ghaeltacht de thairbhe gur cruthaíodh 1,186 post úrnua agus gur coinníodh srian ar chaillteanas post, rud a d’fhág go raibh gnóthachan glan de 295 post ann ar an iomlán. [UD_Irish-IDT 4019, CC BY-SA 3.0]
+Agus do ionnuil a aghuidh, agus dochúaidh amach, agus do chonnuimh air féin, agus adubhairt, cuir arán annso. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Is beag nár choinnigh mé orm mo chuid éadaigh, bhí mé chomh sgáthmhar sin! [Wikisource: An Crann Géagach/An Dúiseacht, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_D%C3%BAiseacht
+https://www.teanglann.ie/en/fgb/coinnigh</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1829,22 +2051,32 @@
       <c r="J23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Ligfeadh sé dó éalú ón saol seo. [UD_Irish-IDT 1044, CC BY-SA 3.0]
 Ba chóir machnamh a dhéanamh ar spreagadh airgeadais chun ligean do níos mó scoláirí páirt a ghlacadh i scoileanna samhraidh Gaeilge. [UD_Irish-IDT 1103, CC BY-SA 3.0]
-- siombailí caighdeánacha a úsáid chun rithim agus tuinairde shimplí a bhreacadh síos - a fhionnachtain mar is féidir foinn pheinteatonacha (bunaithe ar chúig nóta: d, r, m, s, l) a léamh, a chanadh agus a sheinm in doh G, doh C, nó doh F fonn coitianta - bealaí éagsúla a aimsiú chun cnaguirlisí agus uirlisí séiseacha a sheinm - ligean don bhata preabadh ar an mbarra clingíní chun fuaim fhada thonnchreathach a chruthú fuaim an triantáin a mhúchadh trí lámh a leagan air - druma a scríobadh nó a bhualadh roinnt de na poill ar fheadóg stáin a chlúdach chun deireadh a chur le fuaimeanna díoscánacha. [UD_Irish-IDT 1499, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/lig</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+- siombailí caighdeánacha a úsáid chun rithim agus tuinairde shimplí a bhreacadh síos - a fhionnachtain mar is féidir foinn pheinteatonacha (bunaithe ar chúig nóta: d, r, m, s, l) a léamh, a chanadh agus a sheinm in doh G, doh C, nó doh F fonn coitianta - bealaí éagsúla a aimsiú chun cnaguirlisí agus uirlisí séiseacha a sheinm - ligean don bhata preabadh ar an mbarra clingíní chun fuaim fhada thonnchreathach a chruthú fuaim an triantáin a mhúchadh trí lámh a leagan air - druma a scríobadh nó a bhualadh roinnt de na poill ar fheadóg stáin a chlúdach chun deireadh a chur le fuaimeanna díoscánacha. [UD_Irish-IDT 1499, CC BY-SA 3.0]
+D’iar sé ar an lucht coimeádta leigint dó focal do labhairt léi. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]
+Acht níor leig a chroidhe dhó fuireach ó’n troid agus do chuaidh amach i n-aghaidh na nGall. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://www.teanglann.ie/en/fgb/lig</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1883,24 +2115,34 @@
       <c r="J24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Ba leor an teoiric seo i gcúrsaí eolaíochta agus teicneolaíochta ar feadh dhá chéad bliain ach bhí sí fabhtach chun cur síos ar ghluaisní le luas gar do luas an tsolais nó le feiniméin ar scála idir-réaltach. [UD_Irish-IDT 166, CC BY-SA 3.0]
 na difríochtaí ó thaobh airíonna de a tharlaíonn laistigh de speiceas áirithe; mar shampla, bíonn daoine difriúil ó thaobh dath a gcuid gruaige, a súl agus a gcraicne de agus bíonn siad difriúil ó thaobh méid de freisin athrú gáis go leacht de thoradh fuaraithe: mar shampla, athraíonn an ghal ó chiteal atá ar fiuchadh ina leacht nuair a bhuaileann sí le balla fuar cistine comhthionól ball a thiomáineann fuil ar fud an choirp; is é ráta cuisle duine fhásta ná thart ar 70 buille in aghaidh an nóiméid, ach bíonn sí i bhfad níos tapúla ag leanbh; trí ghréasán d'fhéitheanna a ghluaiseann an fhuil; fágann an fhuil an croí trí artairí agus filleann sí ar an gcroí trí fhéitheanna achar beag, thart ar mhéadar cearnach de ghnáth, a léiríonn na plandaí go léir a fhásann sa réimse sin; is féidir ceann a dhéanamh as píosaí sreinge, corda nó adhmaid an ráta ar a gcuirtear obair i gcrích, is é sin, an méid oibre a dhéantar in aghaidh an tsecoind; is é an watt (W) an t-aonad cumhachta rud ar bith a ghlacann spás agus a bhfuil mais aige; is féidir mais a thabhairt ar gach uile shubstaint agus ábhar; úsáidtear na téarmaí solad, leacht agus gás chun cur síos ar thrí staid ábhair; is féidir staid amháin a thiontú go staid eile trí théamh nó fhuarú dath príomhúil is iad dathanna príomhúla an tsolais ná dearg, uaine agus gorm; faightear solas geal nuair a mheasctar na trí chineál le chéile go cionchothrom; nuair a mheasctar dhá dhath phríomhúla le chéile faightear ceann de na dathanna tánaisteacha, leithéidí buí, cian agus magenta; is iad dathanna príomhúla péinte ná dearg, buí agus gorm. [UD_Irish-IDT 951, CC BY-SA 3.0]
 Déanann freagraí ar fhiosrúcháin, agus ábhar na bhfiosrúchán siúd, agus cáipéisí faoi na fiosrúcháin siúd, nó atá ar fáil ón láithreán seo, cur síos ar scéimeanna agus seirbhísí chomh simplí agus is féidir. [UD_Irish-IDT 2943, CC BY-SA 3.0]
-Is téarma é seo a chuireann síos ar théamh domhanda, rud atá ina thoradh na dé-ocsaíde carbóin san atmaisféar atá ag dul i méid i gcónaí. = This is a term used to describe the warming of the earth, due to growing amounts of carbon dioxide in the atmosphere. [Tatoeba 6319336, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+Is téarma é seo a chuireann síos ar théamh domhanda, rud atá ina thoradh na dé-ocsaíde carbóin san atmaisféar atá ag dul i méid i gcónaí. = This is a term used to describe the warming of the earth, due to growing amounts of carbon dioxide in the atmosphere. [Tatoeba 6319336, CC BY 2.0 FR]
+Cuiream síos ar dtús geinealach an fhir seo do réir mar fuaramar romhainn é. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, I, pre-standard, public domain]
+Cuirfidh sé síos ar an mBreac dhuit, ar a thoirt, ar a mheadhchan, ar a chlisteacht—cuirfead geall leat go gcloisfidh tú sgéalta faoi Bhreac na hAibhne Móire a sháróchas aon sgéal iasgaireachta atá sna leabhraibh.... [Wikisource: An Crann Géagach/An Breac atá san Abhainn Mhóir, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/6319336
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_I
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Breac_at%C3%A1_san_Abhainn_Mh%C3%B3ir
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1939,24 +2181,34 @@
       <c r="J25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>D'fhan sé ansin le fiche bliain. [UD_Irish-IDT 785, CC BY-SA 3.0]
 'Ní bheidh mé in ann fanacht istigh leat anocht, Tá cabhair ag teastáil ó Liam, an fear bocht. [UD_Irish-IDT 1292, CC BY-SA 3.0]
 Bíonn gach éinne deas agus béasach lena chéile ach tríd is tríd fanann siad lena dream féin. [UD_Irish-IDT 1993, CC BY-SA 3.0]
-Ba ghá dom fanacht le Tomás go gcríochnódh sé. = I had to wait for Tom to finish. [Tatoeba 4521486, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+Ba ghá dom fanacht le Tomás go gcríochnódh sé. = I had to wait for Tom to finish. [Tatoeba 4521486, CC BY 2.0 FR]
+strapadóireacht sna creagáin cloch ar thóir na gcineál nach bhfaca tú go minic cheana, acht fanfaidh mise liom féin leath-taobh an bhóthair ’mo luidhe sa bhféar, ag féachaint i n‑áirde ar na néaltaibh móra ómracha ghá sguabadh treasna na spéire ag an ngaoith, nó ag cur aithne níos feárr ar shaothar na seangán, nó ag déanamh iongantais de’n tsíol lispín sa lochán le m’ais. [Wikisource: An Crann Géagach/Cuireadh, pre-standard, public domain]
+“Gread leat go diair agus faigh ullamh iad agus fanfaidh an bád leat,” ar sé. [Wikisource: An t-Oileánach/14, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/4521486
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Cuireadh
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/14
 https://www.teanglann.ie/en/fgb/fan</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1995,22 +2247,32 @@
       <c r="J26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Nuair a bhí mé tamall ag amharc orthu ba é an smaointiú a tháinig chugam gur a leithéid seo de lorg láimhe a d'fhágfadh fear ina dhiaidh a nochtfadh a chuid peacaí le hart an dathadóra. [UD_Irish-IDT 311, CC BY-SA 3.0]
 An mhaidin dar gcionn, dhúisigh mé go tobann agus d'amharc mé timpeall orm. [UD_Irish-IDT 925, CC BY-SA 3.0]
-@user155 amhairc ar mo phictúir nua! Nach bhfuil sé gálanta? http://t.co/3hL4k8R2 [UD_Irish-TwittIrish LTC_734, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/amharc</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+@user155 amhairc ar mo phictúir nua! Nach bhfuil sé gálanta? http://t.co/3hL4k8R2 [UD_Irish-TwittIrish LTC_734, CC BY-SA 4.0]
+Cuid aca ag iarraidh amharc fhagháil orm féin thríd an siúnt­achaibh atá idir clár­achaibh an bhotha. [Wikisource: Deoraidheacht/10, pre-standard, public domain]
+gur dh’ amharc air throid ⁊ air choraigheacht [Wikisource: Irisleabhar na Gaedhilge/Imleabhar 4/Uimhir 48/Díorfach Dúin-Alt, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Deoraidheacht/10
+https://wikisource.org/wiki/Irisleabhar_na_Gaedhilge/Imleabhar_4/Uimhir_48/D%C3%ADorfach_D%C3%BAin-Alt
+https://www.teanglann.ie/en/fgb/amharc</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2053,21 +2315,31 @@
       <c r="J27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Má tá boird stáit agus comhlachtai stáir in Éirinn ag dul ag fógairt mar 'phacáiste' ar leith d'Éirinn, má tá RTÉ ag dul i gcomhar le Sky maidir le dáileadh na mbealach teilifís Éireannach ar bhosca digiteach Sky ar fud na tíre (cinneadh atá tar éis an-gheit a bhaint as oifig an Aire de Valera, deirtear linn) níor cheart cur suas leis an neamhaird ar leith a dhéananna meáin na Sasasanach ar Éirinn de ghnáth. [UD_Irish-IDT 938, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Má tá boird stáit agus comhlachtai stáir in Éirinn ag dul ag fógairt mar 'phacáiste' ar leith d'Éirinn, má tá RTÉ ag dul i gcomhar le Sky maidir le dáileadh na mbealach teilifís Éireannach ar bhosca digiteach Sky ar fud na tíre (cinneadh atá tar éis an-gheit a bhaint as oifig an Aire de Valera, deirtear linn) níor cheart cur suas leis an neamhaird ar leith a dhéananna meáin na Sasasanach ar Éirinn de ghnáth. [UD_Irish-IDT 938, CC BY-SA 3.0]
+B’éigean dúinn cur suas leis agus a bheith sásta. [Wikisource: An t-Oileánach/20, pre-standard, public domain]
+Agus chuir sé suas le n‑a mbéasaibh ar feadh dachad blian sa bhfásach. [Wikisource: Gníomhartha na n-Aspol, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cuir_suas_le#Irish
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/20
+https://wikisource.org/wiki/Gn%C3%ADomhartha_na_n-Aspol
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2110,21 +2382,31 @@
       <c r="J28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Níor ghlac na Curdaigh leis an gcinneadh sin agus leanadar ag éirí amach go ceann fiche bliain go dtí go raibh ar a gcinnire, Mustafa Barzaní, teicheadh. [UD_Irish-IDT 128, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Níor ghlac na Curdaigh leis an gcinneadh sin agus leanadar ag éirí amach go ceann fiche bliain go dtí go raibh ar a gcinnire, Mustafa Barzaní, teicheadh. [UD_Irish-IDT 128, CC BY-SA 3.0]
+Annsoin do ghluais sé roimhe soir fá’n tír go rángadar Báideanach i gcríochaibh Cloinne Catáin gur éirigh cách amach leó. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]
+Do éirigh Alasdair as an teint amach agus ráinic an lóisdín ina rabha Domhnall agus do ráidh ris: “A Dhomhnaill, a mhic,” ar sé, “déin ullmhughadh do mhuinntre do chum creach do thabhairt don champa agus bídís réidh agad go gluasacht ar maidin amárach agus ní racha leat acht do mhuinntir féin agus lucht eoluis don tír dá mbí ar n-ordughadh.” Do fuaradar a n-ordughadh ar maidin ’na diaidh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/éirigh_amach#Irish
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/éirigh</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2163,23 +2445,33 @@
       <c r="J29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Ar ámharaí an domhain mar sin, b'fhéidir, bhuail scata daoine isteach an doras ag an bpointe áirithe sin, iad gealgháireach, cainteach, agus gach cosúlacht air gur chustaiméirí iad a thagadh isteach go rialta go ndéanfaidís dreas suilt agus malartú nuachta. [UD_Irish-IDT 2504, CC BY-SA 3.0]
 @user613 ag an #nationalcraftsanddesignfair in @user976 an tseachtain seo- buail isteach chucu! #DéantaiMaighEo https://t.co/XL13LfQ1HW [UD_Irish-TwittIrish NTC_703, CC BY-SA 4.0]
 RT @user1053: Oíche eolais CAO ar siúl i DCU ar an Déardaoin seo , 17ú Eanáir. Buail isteach againn chun labhairt faoi bunchéimeanna Fiontar. [UD_Irish-TwittIrish LTC_81, CC BY-SA 4.0]
-Bhí seómra mór millteach ar cíos aige, agus bhí cead ag Éireannach ar bith bualadh isteach ann. [UD_Irish-Cadhan deoraidheacht-2958, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/buail</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
+Bhí seómra mór millteach ar cíos aige, agus bhí cead ag Éireannach ar bith bualadh isteach ann. [UD_Irish-Cadhan deoraidheacht-2958, pre-standard, CC BY-SA 4.0]
+Do buaileadh isteach fén saidhne í, agus do bhí a lán go smeig ann. [Wikisource: An t-Oileánach/11, pre-standard, public domain]
+Lá breagh insa tseachtain ’n‑a dhiaidh sin do bhuail mo shean-úncail isteach chugham ar maidin—an t‑úncail úd gur chuas ’on chúntúirt mhór ’á shaoradh i bpoll na róinte an uair a bhris an téad. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/11
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://www.teanglann.ie/en/fgb/buail</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2222,21 +2514,31 @@
       <c r="J30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>féuch, adeirim ribh, tógbhuidh suás bhur súile, agus féuchuidh na reghíon: oír atáid siád geal cheáná dochum an fhoghamhair. [UD_Irish-Cadhan eoin-156, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>féuch, adeirim ribh, tógbhuidh suás bhur súile, agus féuchuidh na reghíon: oír atáid siád geal cheáná dochum an fhoghamhair. [UD_Irish-Cadhan eoin-156, pre-standard, CC BY-SA 4.0]
+Agus do thóg Lot a shuile súas, agus dochonnairc réiteach Jordán uile, go raibh uisge go maith ar gach éun taóbh suil do sgrios an tighearna Sodom agus Gomorrah, eadhon amhuil gháirdín an tighearna, cosmhuil re talamh na Heigipte mar thigh tú go Soar: [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus do thóg a shúile súas, agus damharc sé, agus féuch dochonnairc sé tríur fear na seasamh láimh ris, agus anuáir dochonnairc sé íad do rith na gcoinne ó dhorus na puible, agus do chlaón é féin go talamh. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tóg_suas#Irish
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/tóg</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2275,20 +2577,28 @@
       <c r="J31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>@user600 nach iontach é. Coinnigh suas an obair maith [UD_Irish-TwittIrish LTC_570, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/coinnigh</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>@user600 nach iontach é. Coinnigh suas an obair maith [UD_Irish-TwittIrish LTC_570, CC BY-SA 4.0]
+Coinnigh suas cuideachta shuairc [Wikisource: Eachtradh Eibhlís i dTír na nIongantas/X, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Eachtradh_Eibhl%C3%ADs_i_dT%C3%ADr_na_nIongantas/X
+https://www.teanglann.ie/en/fgb/coinnigh</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2327,20 +2637,26 @@
       <c r="J32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>(2) Féadfidh cigire gach clár atá á chimeád do réir an ailt seo do scrúdú aon uair le linn tráthanna oifige chun aon chríche eireos as an Acht so no as aon rialachán a déanfar fé no a eireos de bharr ceachtar acu agus, ar a iarraidh sin don chigire, beidh sé de dhualgas ar únaer chláruithe an áitreibh ina bhfuil an clár san á chimeád an clár san do thaisbeáint, chun go scrúdóidh an cigire sin é, agus fós gach billín, nóta consighneachta, admháil, agus scríbhinn eile (ar a n-áirítear cóipeanna dhíobh i gcás gan iad féin a bheith ar fáil) a iarrfidh an cigire sin go réasúnta chun féachaint an fíor aon iontráil áirithe sa chlár san no cad fé ndeár éinní áirithe d'fhágaint amach as. [UD_Irish-IDT 1375, CC BY-SA 3.0]</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>https://www.teanglann.ie/en/fgb/fág</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2379,20 +2695,30 @@
       <c r="J33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Agus muid ag ithe bonnóga an Europa, labhair muid faoi chúrsaí bia don té a chaithfeadh mairstin in ifrinn shaolta agus sléacht ag titim amach ar achan taobh. [UD_Irish-IDT 541, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tit</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="K33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Agus muid ag ithe bonnóga an Europa, labhair muid faoi chúrsaí bia don té a chaithfeadh mairstin in ifrinn shaolta agus sléacht ag titim amach ar achan taobh. [UD_Irish-IDT 541, CC BY-SA 3.0]
+D’innseadar dúinn mar thuit amach dóibh agus nárbh’ fhiú coróin a raibh d’earraí innti mar gur ghaibh an fhairrge mhór lastuas díobh agus mara mbeadh go raibh an cuan sroichte aca roimis an scríb ná feicfí aon duine aca go deo arís. [Wikisource: An t-Oileánach/14, pre-standard, public domain]
+“Conus a thuit san amach?” arsa mise; ach má bhíos aineolasach le linn na ceiste do chur dom ní rabhas mar sin ’n-a dhiaidh sin, mar nár mhór an t-imníomh a bhí ar an bhfile gan san d’innsint dom agus a bholg anáirde le gréin aige. [Wikisource: An t-Oileánach/17, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/14
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/17
+https://www.teanglann.ie/en/fgb/tit</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2431,16 +2757,22 @@
       <c r="J34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2479,16 +2811,29 @@
       <c r="J35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fan</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>fan uaim amach!” arsa ’n crúsca. [Wikisource: Aesop a tháinig go h-Éirinn/An Sean Duine agus an Bás, pre-standard, public domain]
+Fan uaim amach a deirim leat!” [Wikisource: Aesop a tháinig go h-Éirinn/An Sean Duine agus an Bás, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Sean_Duine_agus_an_B%C3%A1s
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Sean_Duine_agus_an_B%C3%A1s
+https://www.teanglann.ie/en/fgb/fan</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2527,16 +2872,29 @@
       <c r="J36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/lig</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Átha Cliath ag iarraidh ortha Cóilín a leigean amach chuici, gur cinnte go leigfidhe amach é. [Wikisource: An Mháthair agus Sgéalta Eile/An Bhean Chaointe, pre-standard, public domain]
+An uair a leigeadh amach lár an lae sinn: [Wikisource: An t-Oileánach/6, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/An_Bhean_Chaointe
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/6
+https://www.teanglann.ie/en/fgb/lig</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2575,16 +2933,29 @@
       <c r="J37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="K37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Anuáir tugadh amach í, do chuir sí fios chum a hathar cleamhna dá rádh, ón té lér leis íadso atáimsi torrach: agus adubhairt sisi, guidhim thú, meas cía lear leis íadso, an séula, agus na bráisléid agus an bata. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+agus na mná óga am’ thabhairt amach mar do bhí rinnce maith go leór agam san am san. [Wikisource: An t-Oileánach/10, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/10
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2619,27 +2990,37 @@
       <c r="J38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="n">
+        <v>884</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>) 'Tá mé buartha fán trioblóid uilig ach tabhair maithiúnas domh... 'Tá mé cinnte gur baineadh scanradh asat,' arsa Peadar. [UD_Irish-IDT 456, CC BY-SA 3.0]
 D'ainneoin fíoch na filíochta idir an bheirt thug fear Ceann Tíre isteach an strainséir agus thug béile aráin rósta dó agus im tíre air a thug a bhean anall ón Chill san Cheann Deas. [UD_Irish-IDT 526, CC BY-SA 3.0]
 B'fhéidir gur aingeal í anois atá ag tabhairt aire dhuit ach tá 'fhios ag Mac Dé go bhfaca mise í. [UD_Irish-IDT 546, CC BY-SA 3.0]
 An féidir leat cupán caife a thabhairt dom? = Can you bring me a cup of coffee? [Tatoeba 11609618, CC BY 2.0 FR]
 Cé go raibh an aimsir tirim, thug mé mo chóta dó nuair a bhí sé ag dul amach. = Even though the weather was fine, I gave him my coat as he was going out. [Tatoeba 5154139, CC BY 2.0 FR]
-Seo suas Ó Ceallaigh, agus, o nach raibh 'fhios aige cia bhuail é, chrom se ag rúsgadh gac nduine thárla 'na shlighe, agus thug sé leadhab do Sean Ó Athiaruin, duine uasal óg, noch do thug liudradh breagh dó 'n-a ionad, ag cur preabán dubh ar a shúilín easóige. [UD_Irish-Cadhan cinlae-275, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
+Seo suas Ó Ceallaigh, agus, o nach raibh 'fhios aige cia bhuail é, chrom se ag rúsgadh gac nduine thárla 'na shlighe, agus thug sé leadhab do Sean Ó Athiaruin, duine uasal óg, noch do thug liudradh breagh dó 'n-a ionad, ag cur preabán dubh ar a shúilín easóige. [UD_Irish-Cadhan cinlae-275, pre-standard, CC BY-SA 4.0]
+bhéarfainn póg don chailín óg a bhéarfadh a hóighe dhom, [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]
+Thug beach tabharthas do Iupiter, .i. [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/11609618
 https://tatoeba.org/en/sentences/show/5154139
+https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
 https://www.teanglann.ie/en/fgb/tabhair</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr"/>
       <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2674,23 +3055,33 @@
       <c r="J39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Ó shin i leith bhí beirt Aire Gaeltachta againn anseo i nGaillimh a chuir peann le pár - Máire Geoghegan-Quinn, a scríobh The Green Diamond, agus Michael D. Ó hUiginn. [UD_Irish-IDT 512, CC BY-SA 3.0]
 Chomh maith leis sin chuir sé eagar ar 'Bruíon Chaorthainn' agus ar 'Bodach an Chóta Lachna'. [UD_Irish-IDT 672, CC BY-SA 3.0]
 Deirtear gurb é Francesco Petrarca (1304-'74), file Iodálach, a chuir tús leis an Renaissance. [UD_Irish-IDT 876, CC BY-SA 3.0]
-Bhí seisear madadh i gcomhnaidhe 'sa' bhuidhin, le cois na beirte a cuireadh isteach leó ag Rink Rapids ar an astar ghasta adaí, Tíoc agus Cúna, agus d'fhág an seisear úra seo anois ceithre mhadadh dhéag 'sa' bhuidhin. [UD_Irish-Cadhan scairt-992, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cuir</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+Bhí seisear madadh i gcomhnaidhe 'sa' bhuidhin, le cois na beirte a cuireadh isteach leó ag Rink Rapids ar an astar ghasta adaí, Tíoc agus Cúna, agus d'fhág an seisear úra seo anois ceithre mhadadh dhéag 'sa' bhuidhin. [UD_Irish-Cadhan scairt-992, pre-standard, CC BY-SA 4.0]
+An fhaid a chuirfidh sibh le chéile ní fhéadfaidh aoinne an lámh uachtair d’ fhághail oraibh, acht má thagan fuath agus mioscais eadraibh, agus má thugan sibh druím lámha le n-a chéile, gheabhfar an lámh uachtair láithreach oraibh.” [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]
+Ná cuir thu féin i gcomórtas le rígh, muna rígh thu. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
+https://www.teanglann.ie/en/fgb/cuir</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2725,27 +3116,37 @@
       <c r="J40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="n">
+        <v>656</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Gabhaim fíorbhuíochas le daoine a raibh baint dhíreach acu leis na Cluichí Oilimpeacha agus a rinne agallaimh liom: - An Tiarna Killanin, Uachtarán Oinigh Saoil den COI agus de COÉ. [UD_Irish-IDT 704, CC BY-SA 3.0]
 Fiú má fhanann siad ag baile, is trí mheán an Bhéarla a bheidh orthu a ngnó a dhéanamh le seirbhísí poiblí agus le seirbhísí príobháideacha sa Ghaeltacht. [UD_Irish-IDT 45, CC BY-SA 3.0]
 Aonach a' Phoic Duine a bheadh ag ceannach capaill ní dhéanfadh sé margadh le tincéirí ar eagla go mbuailfí bob air faoi mar a buaileadh ar Phádraig Bán ar Aonach a' Phoic i gCill Orglan uair. [UD_Irish-IDT 121, CC BY-SA 3.0]
 Déanaim é mar is maith liom é a dhéanamh. = I do it because I like to do it. [Tatoeba 7705877, CC BY 2.0 FR]
 Ní thaitníonn an bia a dhéanann Bríd léi. = She doesn't enjoy the food that Bríd makes for her. [Tatoeba 871665, CC BY 2.0 FR]
-Déna an t-inchreachadh dhlighe o thús go eirr th'aimsire sgrúd a bhfuair tú gach tan 'sa ndearnais ris san saoghal. [UD_Irish-Cadhan bardic_1387-39, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
+Déna an t-inchreachadh dhlighe o thús go eirr th'aimsire sgrúd a bhfuair tú gach tan 'sa ndearnais ris san saoghal. [UD_Irish-Cadhan bardic_1387-39, pre-standard, CC BY-SA 4.0]
+Is é an ní a deir cách le do dheartháir Cáthal, [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]
+Ní dóich liom gur baoghal d’ aoinne go ngeabhair de chosaibh ann indiu, munab ionan agus an lá úd!” [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/7705877
 https://tatoeba.org/en/sentences/show/871665
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2780,25 +3181,35 @@
       <c r="J41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Dar leis an Ríordánach sa dán Teitheadh, is cosúla an fhilíocht le sacraimint eile, an fhaoistin, ná le comaoineach naofa; agus tugann sé peaca ar an dán dá réir: Do rugas liom don eaglais Mo chnuasach nuapheacaí, Do chuireas iad in eagar Don fhoilsitheoir a bhíonn Ag cló-dhearmhad peacaí. [UD_Irish-IDT 506, CC BY-SA 3.0]
 Má chuir an íomhá i gcuimhne di buachaill beag ramhar ag stánadh ar an ghealach úr, scríobh sí síos nach bhfaca sí ach leathanach smálaithe gan bhrí gan chiall. [UD_Irish-IDT 520, CC BY-SA 3.0]
 chomh maith leis na tionscnaimh atá liostaithe faoi straitéis 2, trí chistiú a chur ar fáil do chompántais ceoldrámaíochta atá ag iarraidh ardchaighdeán ealaíonta agus/nó nuálachais a bhaint amach nó a n-éiríonn leo na caighdeáin seo a bhaint amach cheana féin agus trí chistiú a chur ar fáil chun ceoldrámaí nua agus tionscnaimh ceoldrámaíochta a choimisiúnú. [UD_Irish-IDT 637, CC BY-SA 3.0]
 Cuir in iúl dom cad é atá tú ag iarraidh a dhéanamh. = Let me know what you want to do. [Tatoeba 6319257, CC BY 2.0 FR]
-Is uime do mheas Hanmer Breathnach do dhéanamh do Chomhghall, do bhrígh gurab é Comhghall do thógaibh Mainistir Bheannchair i n-Áird Uladh, fá máthair do mhainistreachaibh Eorpa uile, agus gur thógaibh mainistir eile i Sacsaibh, láimh re Uestchester, d'á ngairthear Bangor: agus dá dteagmhadh do Hanmer a chur i gcéill do'n léaghthóir gur Bhreathnach Comhghall, go gcuirfeadh d'á réir sin i gcéill, gach oirdhearcas d'á bhfuil ar mhainistir Bheannchair Uladh do dhul i gclú do Bhreathnachaibh a los Chomhghaill do bheith dhíobh, nó gach clú d'ár thuill Beannchar Uladh go gcuirfidhe i leith na mainistreach atá i Sacsaibh darab ainm Bangor í. [UD_Irish-Cadhan forasfeasa-125, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
+Is uime do mheas Hanmer Breathnach do dhéanamh do Chomhghall, do bhrígh gurab é Comhghall do thógaibh Mainistir Bheannchair i n-Áird Uladh, fá máthair do mhainistreachaibh Eorpa uile, agus gur thógaibh mainistir eile i Sacsaibh, láimh re Uestchester, d'á ngairthear Bangor: agus dá dteagmhadh do Hanmer a chur i gcéill do'n léaghthóir gur Bhreathnach Comhghall, go gcuirfeadh d'á réir sin i gcéill, gach oirdhearcas d'á bhfuil ar mhainistir Bheannchair Uladh do dhul i gclú do Bhreathnachaibh a los Chomhghaill do bheith dhíobh, nó gach clú d'ár thuill Beannchar Uladh go gcuirfidhe i leith na mainistreach atá i Sacsaibh darab ainm Bangor í. [UD_Irish-Cadhan forasfeasa-125, pre-standard, CC BY-SA 4.0]
+Do chuir, agus do pósadh í féin agus an t-óigfhear. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Níor chuir sí cor dí, nídh nách iongna. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/6319257
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2837,28 +3248,38 @@
       <c r="J42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>'Bhí ár léiritheoir sraithe Trevor Ó Clochartaigh ag obair le Fair City anuraidh agus aithne aige ar an bhfoireann ar fad, mar sin cheap mé go mba dheas an smaoineamh é dá dtiocfadh an dá dhream le chéile chun rud fiúntach a dhéanamh ar son charthanacht faoi leith'. [UD_Irish-IDT 746, CC BY-SA 3.0]
 Sa deireadh, smaointigh sé gurbh é a b'fhearr a dtiocfadh leis a dhéanamh cupla béic chreathnaitheach a ligean as a tharraingeodh air bunadh an tí agus, nuair a d'fhosclófaí an doras, go dtiocfadh leis éaló amach sula bhfaighfí greim air. [UD_Irish-IDT 873, CC BY-SA 3.0]
 Sa deireadh, smaointigh sé gurbh é a b'fhearr a dtiocfadh leis a dhéanamh cupla béic chreathnaitheach a ligean as a tharraingeodh air bunadh an tí agus, nuair a d'fhosclófaí an doras, go dtiocfadh leis éaló amach sula bhfaighfí greim air. [UD_Irish-IDT 873, CC BY-SA 3.0]
 An dtiocfaidh tú liom go dtí an cheolchoirm? = Will you come with me to the concert? [Tatoeba 3944677, CC BY 2.0 FR]
 Tar éis an dinnéir, crochaim liom ar an dtrá. = After dinner, I take a walk on the beach. [Tatoeba 4521060, CC BY 2.0 FR]
-Bhí a bpus iadhta, is a n-anál ag teacht anuas trí phollaibh a srón le racht siubhail. [UD_Irish-Cadhan peig-2176, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
+Bhí a bpus iadhta, is a n-anál ag teacht anuas trí phollaibh a srón le racht siubhail. [UD_Irish-Cadhan peig-2176, pre-standard, CC BY-SA 4.0]
+“Tar,” arsan gualadóir leis an úcaire, ”agus déinimís aontígheas. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Tar amach agus troid liom mar fhear! [Wikisource: Aistriúchán:Tar Amach, a Dúchrónaigh (Behan, Béarla), pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tar_le#Irish
 https://tatoeba.org/en/sentences/show/3944677
 https://tatoeba.org/en/sentences/show/4521060
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Aistri%C3%BAch%C3%A1n%3ATar_Amach%2C_a_D%C3%BAchr%C3%B3naigh_%28Behan%2C_B%C3%A9arla%29
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr"/>
       <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2893,27 +3314,37 @@
       <c r="J43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Ar shíl sé go ndéanfadh ARDFHEAR CAM dochar don fheachtas i bhfabhar Nice? [UD_Irish-IDT 542, CC BY-SA 3.0]
 Táimid uilig sa tír seo, thuaidh agus theas, seanchleachtach ar an dochar a dhéanann cailleadh acmhainní den chineál seo do mheanma pobail. [UD_Irish-IDT 641, CC BY-SA 3.0]
 Tá New Bedford, anois, ionad iascaireachta traidisiúnta le 350 bliain anuas, Cháin sé go dian, freisin, an truailliú atá á dhéanamh don dúlra ag na comhlachtaí ollmhóra ilnáisiúnacha. [UD_Irish-IDT 759, CC BY-SA 3.0]
 Ba mhaith liom áirithint a dhéanamh do dhuine amháin. = I would like to make a reservation for one person. [Tatoeba 10926501, CC BY 2.0 FR]
 Bhí Tom ag iarraidh mé gar a dhéanamh dó. = Tom wanted me to do him a favor. [Tatoeba 6319283, CC BY 2.0 FR]
-Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
+Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]
+Gheall sé d’Apolo agus d’Aesculapius go ndéanfadh sé ídhbirt míle damh chúcha acht é leigheas. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Déineadh taibhreamh dó. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10926501
 https://tatoeba.org/en/sentences/show/6319283
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2952,28 +3383,38 @@
       <c r="J44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>(4) Maidir le hordú atá i bhfeidhm faoi fho-alt (2) - (a) más rud é gur faoi fho-alt (2) (a) a rinneadh é, is fianaise é gur Stát Conarthach aon stát lena mbaineann an dearbhú, agus (b) más rud é gur faoi fho-alt (2) (b) a rinneadh é, is fianaise é go ndearnadh an dearbhú de bhun Airteagal IV nó gur cuireadh an scéala in iúl de bhun Airteagal VI agus is fianaise é ar a bhfuil ann. [UD_Irish-IDT 49, CC BY-SA 3.0]
 Ach chonacthas iad ag dul thart i gcúl Uaighe agus rinneadh trí charraig díobh. [UD_Irish-IDT 87, CC BY-SA 3.0]
 cineál ainmhí a chaitheann cuid dá shaolré in uisce agus cuid eile ar talamh; é fuarfhuilteach, le cnámh droma orgánaigh ar nós baictéar agus fungas; dianscaoileann siad taisí orgánacha marbha go ndéanann substaintí níos simplí díobh, rudaí a sheoltar ar ais isteach san ithir díleá. [UD_Irish-IDT 1206, CC BY-SA 3.0]
 Cén fáth a ndearna tú botún den sórt sin? = Why did you make that sort of mistake? [Tatoeba 12353418, CC BY 2.0 FR]
 Rinne a bhua laoch de. = His victory made him a hero. [Tatoeba 10925703, CC BY 2.0 FR]
-Ar anadhbharsin an uáir do d'aithin Iósa gu raibhe fúthasan teachd agus breith air dochum riogh dho dhéunamh dhé dochúaidh sé dhá leaththáoibh arís ar an sliabh ina áonar. [UD_Irish-Cadhan eoin-238, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
+Ar anadhbharsin an uáir do d'aithin Iósa gu raibhe fúthasan teachd agus breith air dochum riogh dho dhéunamh dhé dochúaidh sé dhá leaththáoibh arís ar an sliabh ina áonar. [UD_Irish-Cadhan eoin-238, pre-standard, CC BY-SA 4.0]
+”Ní dhéanfadh Éire dhíot acht cat!” agus chuir sí ’na riocht féin airís í. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Ní raibh de ghnó ná d’ obair ná de chúram ortha, ó mhaidin go h-oídhche acht bheith ag snámh anonn ’s anall tríd an uisge, nó ag caitheamh trí léim táiliúra de dhruim achéile, nó ’gá n-iomlosg féin sa ghlóthaig. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/déan_de#Irish
 https://tatoeba.org/en/sentences/show/12353418
 https://tatoeba.org/en/sentences/show/10925703
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3008,25 +3449,35 @@
       <c r="J45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Cuir i gcomparáid ansin é lena dtugann Fíor 70.3 le fios. [UD_Irish-IDT 507, CC BY-SA 3.0]
 A bhó chairdiúil A bhó chairdiúil, buí is bán, Le grá di, tá mo chroíse lán, Tugann sí uachtar go flaithiúil, Le n-ithe le mo thoirtín úll. [UD_Irish-IDT 524, CC BY-SA 3.0]
 Mar a thug clár teilifíse sa Bhreatain le fios le déanaí, tá fadhb mhór ann sna hospidéil maidir le 'sárvíreas' a ionsaíonn othair tar éis dóibh dul faoi scian. [UD_Irish-IDT 756, CC BY-SA 3.0]
 Nuair a thugaim cuairt ar mo gharmhac, tugaim rud éigin liom dó i gcónaí. = When I go to see my grandson, I always give him something. [Tatoeba 6319355, CC BY 2.0 FR]
-Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
+Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]
+”Gheabhair do choileán.” Thug sí léi anuas an coileán láithreach agus chuir sí uaithi é, slán foláin, ag bruach na pluaise, mar a bhfuair sí é. [Wikisource: Aesop a tháinig go h-Éirinn/An Fhiolar agus an Mada Ruadh, pre-standard, public domain]
+D’imthig an giolla agus d’aimsigh sé sail mhór ghiúise agus thug sé leis í agus chaith sé chúcha isteach í, i lár an locha. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/6319355
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Fhiolar_agus_an_Mada_Ruadh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
 https://www.teanglann.ie/en/fgb/tabhair</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3061,25 +3512,35 @@
       <c r="J46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Chuir an Síneach isteach sa chomhrá go tapa. [UD_Irish-IDT 183, CC BY-SA 3.0]
 Táthar á rá gurb í is ciontach le galar nua ar a dtugtar 'bréagthochtán' - tinneas a chuireann isteach ar pháistí go háirithe. [UD_Irish-IDT 419, CC BY-SA 3.0]
 Chuir sé cuid acu isteach chuig an Derry Journal. [UD_Irish-IDT 1565, CC BY-SA 3.0]
 Chuirfeadh sibh isteach ar an phost sin. = You would apply for that job. [Tatoeba 3090973, CC BY 2.0 FR]
-Gach uile dhuine ag cur a ladair fhéin isteach. [UD_Irish-Cadhan deoraidheacht-3097, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+Gach uile dhuine ag cur a ladair fhéin isteach. [UD_Irish-Cadhan deoraidheacht-3097, pre-standard, CC BY-SA 4.0]
+nó mada ruadh, áracht aeir nó olphiast talmhan, ag cur isteach oraibh, mise do throidfadh iad, agus d’ imreóchadh bás le gob a’s le h-ingnibh ortha, nó thabharfadh a leithéid sin de sgeimhle agus d’anfa dhoibh, ’ghá ruagadh agus ’ghá ndíbirt, nár bhaoghal go bhfíllfidís.” [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]
+faillighe agus fuaire an ughdair féin i n-a dhéantúsaíbh ar chuma nár chuir sé riamh isteach iad le haghaidh a gclóbhuailte — tá an locht mór sain air fós go dtí an lá atá indiu ann agus a rádh go bhfuilid fromhtha a dhá dhéantús i n-a sheilbh gus an am so i láthair agus nár smaoin sé riamh ar a gcur thar a n-ais chugainn ceartuighthe pioctha sgiomartha ó n-a láimh oilte féin! [Wikisource: Alasdair Mac Colla/Brollach, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/3090973
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Brollach
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3114,25 +3575,35 @@
       <c r="J47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Ní mór aird a thabhairt ar phointe a léirigh tuarascáil Chonradh na Náisiún i 1922 mar seo: Bhí Edward Sapir (1887-1939) ar na daoine a chuir bonn faoi theangeolaíocht an lae inniu. [UD_Irish-IDT 576, CC BY-SA 3.0]
 (5) Ní bheidh d'éifeacht uathoibríoch le hachomharc a dhéanamh i gcoinne fógra toirmisc de réir fho-alt (4) oibriú an fhógra a fhionraí, ach féadfaidh an t-achomharcóir iarratas a dhéanamh chuig an gCúirt lena chur faoi deara oibriú an fhógra a fhionraí go dtí go ndéanfar an t-achomharc a chur de láimh agus féadfaidh an Chúirt, más cuí léi sin a dhéanamh, a ordú go bhfionrófar oibriú an fhógra dá réir sin. [UD_Irish-IDT 619, CC BY-SA 3.0]
 Is fíor gur láidre Fianna Fáil ag cosaint na neodrachta ná Fine Gael faoi láthair agus go fiú i bhFine Gael tá maolú tagtha ag na ceisteanna a chuireann a cheannairí faoin bpolasaí náisiúnta seo. [UD_Irish-IDT 21, CC BY-SA 3.0]
 Ní chuireann an eochair an doras faoi ghlas i gceart. = The key doesn't lock the door correctly. [Tatoeba 10926464, CC BY 2.0 FR]
-Nir eirigh neach thiar no thoir ar druim do rotha a shaoghail nach é [a] dheireadh iar gach sódh a chur faoi an roth fa dhubrón. [UD_Irish-Cadhan bardic_1387-8, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
+Nir eirigh neach thiar no thoir ar druim do rotha a shaoghail nach é [a] dheireadh iar gach sódh a chur faoi an roth fa dhubrón. [UD_Irish-Cadhan bardic_1387-8, pre-standard, CC BY-SA 4.0]
+Chuir sé saighead fé shraíng a bhogha. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aṫair Níṁe agus an Portán, pre-standard, public domain]
+Agus do chuir an searbhfhoghantuigh a lámh faói shlíasuid Abraham a mhaighistir, agus tug a mhionna dhó a ttaóibh na cúisisin. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10926464
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-A%E1%B9%ABair_N%C3%AD%E1%B9%81e_agus_an_Port%C3%A1n
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr"/>
       <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3159,7 +3630,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>1</v>
@@ -3167,25 +3638,35 @@
       <c r="J48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Tagann sé seo ó choinníoll de Chlárlann na Talún nach ndéantar Ordú Deighilte mura bhfuil na sciarshealbhóirí ina n-úinéirí cláraithe. [UD_Irish-IDT 853, CC BY-SA 3.0]
 Bhí ráfla ann go mb'fhéidir go dtiocfadh Pat An Cóp Ó Gallchóir ar ais ón Eoraip le polaitíocht na Dála a imirt arís. [UD_Irish-IDT 1095, CC BY-SA 3.0]
 Tháinig an maoiniú ó fhoinsí difriúla: IRP192,000 ó Belfast Regeneration Office; IRP119,000 ón Childhood Fund; IRP60,000 ó Chiste Síochána agus Athmhuintearais (fríd an Roinn Oideachais), IRP70,000 ó Bhord Oideachais agus Leabharlainne Bhéal Feirste agus IRP50,000 ó Fhoras na Gaeilge. [UD_Irish-IDT 1441, CC BY-SA 3.0]
 Cathain a bheidh siad ag teacht ar ais ón saoire? = When are they coming back from vacation? [Tatoeba 11247807, CC BY 2.0 FR]
-Ag so an dara comhartha dorinne Iósa arís, an tan taínig sé ón Iudéa don Ghalilé. [UD_Irish-Cadhan eoin-177, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
+Ag so an dara comhartha dorinne Iósa arís, an tan taínig sé ón Iudéa don Ghalilé. [UD_Irish-Cadhan eoin-177, pre-standard, CC BY-SA 4.0]
+“B’fhéidir,” arsa Iupiter, “dá olcas é go dtiocfadh rígh ba mheasa ’ná é ’na dhiaigh chúghaibh.” [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]
+Táinic Eóin Múideórdach ón Chaislén Tirim d’ionnsaighe an champa sin Mhic Cailín ar iarradas Mhic Cailín, óir fá dóigh le Mac Cailín go n-éirgheadh Eóin Múideórdach agus Clann Raghnaill leis ’na arm féin i n-aghaidh airm an ríogh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/11247807
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr"/>
       <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3220,25 +3701,35 @@
       <c r="J49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>(5) Ní bheidh d'éifeacht uathoibríoch le hachomharc a dhéanamh i gcoinne fógra toirmisc de réir fho-alt (4) oibriú an fhógra a fhionraí, ach féadfaidh an t-achomharcóir iarratas a dhéanamh chuig an gCúirt lena chur faoi deara oibriú an fhógra a fhionraí go dtí go ndéanfar an t-achomharc a chur de láimh agus féadfaidh an Chúirt, más cuí léi sin a dhéanamh, a ordú go bhfionrófar oibriú an fhógra dá réir sin. [UD_Irish-IDT 619, CC BY-SA 3.0]
 Gan dochar d'inniúlachtaí an Chomhphobail, cuirfidh Ballstáit an Aontais Eorpaigh cúnamh frithpháirteach ar fáil dá chéile agus comhoibreoidh siad le chéile trína riaracháin chustaim d'fhonn: - sáruithe ar fhorálacha náisiúnta custaim a chosc agus a bhrath, agus - sáruithe ar fhorálacha custaim an Chomhphobail agus forálacha náisiúnta custaim a ionchúiseamh agus a phionósú. [UD_Irish-IDT 645, CC BY-SA 3.0]
 (4) Maidir le hordú atá i bhfeidhm faoi fho-alt (2) - (a) más rud é gur faoi fho-alt (2) (a) a rinneadh é, is fianaise é gur Stát Conarthach aon stát lena mbaineann an dearbhú, agus (b) más rud é gur faoi fho-alt (2) (b) a rinneadh é, is fianaise é go ndearnadh an dearbhú de bhun Airteagal IV nó gur cuireadh an scéala in iúl de bhun Airteagal VI agus is fianaise é ar a bhfuil ann. [UD_Irish-IDT 49, CC BY-SA 3.0]
 Chuir sé é féin den saol leis an ól. = He drank himself to death. [Tatoeba 10317440, CC BY 2.0 FR]
-Nuair a shíl sí sin a dhéanamh (ní raibh fhios agam-sa go raibh sí le n-a dhéanamh mar bhí na súile dúnta agam), chuireas cosamhlacht fhíochmhar orm féin, leigeas dhá bhúirt uathbhásach' asam, mar leigfeadh tarbh agus an sgian ar a sgórnach, agus thosuigheas ag cur na gcor dhíom ar nós eascon a bheadh i ngreim glaice ag duine. [UD_Irish-Cadhan deoraidheacht-906, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
+Nuair a shíl sí sin a dhéanamh (ní raibh fhios agam-sa go raibh sí le n-a dhéanamh mar bhí na súile dúnta agam), chuireas cosamhlacht fhíochmhar orm féin, leigeas dhá bhúirt uathbhásach' asam, mar leigfeadh tarbh agus an sgian ar a sgórnach, agus thosuigheas ag cur na gcor dhíom ar nós eascon a bheadh i ngreim glaice ag duine. [UD_Irish-Cadhan deoraidheacht-906, pre-standard, CC BY-SA 4.0]
+Níor cuireadh aon duine dhíobh so chum báis, siúd is gur gnáthach leis na Gallaibh fá’n am soin an uile Éireannach dá ngabhaidís ar muir do chaitheamh gan spás san bhfairrge. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, I, pre-standard, public domain]
+Chuir mé a raibh de bhiadh agam isteach sa mála go cúramach. [Wikisource: An Crann Géagach/An Sean-choiléar, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10317440
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_I
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Sean-choil%C3%A9ar
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3273,22 +3764,32 @@
       <c r="J50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Chaith Alan a chloigeann san aer agus rinne gáire faoina ndúirt Learaí leis. [UD_Irish-IDT 891, CC BY-SA 3.0]
 Nuair a chuir sé aithne ar Bhreandán Ó hEithir ní raibh aon easpa ábhar cainte orthu - Sonny ag fiafraí de Bhreandán an raibh aithne aige ar a leithéid seo nó siúd agus Breandán ag inseacht dó: Thug foilsiú Lig Sinn i gCathú seanchairde Bhreandáin i nGaillimh le chéile agus rinneadh go leor cainte faoi na seanáiteanna atá luaite sa leabhar ach atá imithe ó shin. [UD_Irish-IDT 186, CC BY-SA 3.0]
-(1A) Aon duine a sháróidh, gan leithscéal réasúnach, aon rialachán arna dhéanamh faoin alt seo, féadfaidh an Bord aon chead gealltóireachta cúrsa a bheidh deonaithe dó a fhionraí nó a chulghairm. [UD_Irish-IDT 240, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/déan</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
+(1A) Aon duine a sháróidh, gan leithscéal réasúnach, aon rialachán arna dhéanamh faoin alt seo, féadfaidh an Bord aon chead gealltóireachta cúrsa a bheidh deonaithe dó a fhionraí nó a chulghairm. [UD_Irish-IDT 240, CC BY-SA 3.0]
+“Téimís,” ar sise airís leó, “agus bainimís an ceann dé agus loitfidh san anois féin é.” Níor dheineadar acht bheith ag magadh fúithi agus ag glaodhach “áinle an fheasa” uirthi. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]
+Ó shin aleith séanan an áinle na coillte agus na craobhcha agus déinean sí a nead fé dhíonaibh agus fé shlíngibh agus fé sgibhéalaibh na dteach, i n-áit nách baoghal dí líonta. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
+https://www.teanglann.ie/en/fgb/déan</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr"/>
       <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3323,24 +3824,34 @@
       <c r="J51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Bhí sí ag súil go dtiocfadh sé slán as cibé trioblóid ina raibh sé thall, ach níor thuig sí riamh cén fáth nár íoc sé an liúntas míosúil lena bhean chéile tríd an mbanc in áit seic a scríobh chuile mhí i ndiaidh a chéile. [UD_Irish-IDT 498, CC BY-SA 3.0]
 D'imigh Bríd na mBróg in am trátha freisin, súilfhéachaint siar aici ar an sagart Sandeman is dúil aici nach dtiocfadh sé as treo éigin ar a bealach chun a botháin ag cúl halla an bhaile. [UD_Irish-IDT 866, CC BY-SA 3.0]
 Sé deacracht a bhíodh agam teacht amach as an saol san agus plé le gnáthchúrsaí an tsaoil ina rabhas ag maireachtaint. [UD_Irish-IDT 200, CC BY-SA 3.0]
-Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
+Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]
+Tángadar as sin don Chaislén Tirim. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Táinic tighearna Achaidh na mBreac as Éirinn chuca agus do ghabh mire agus dásacht é mar fuair sé ar n-a losgadh agus ar n-a creachadh a dhúthaigh ar a chionn. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/752762
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr"/>
       <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3379,23 +3890,33 @@
       <c r="J52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Cailín deas ab fhearr liom a bheith ar láimh liom thar a bhfeacaíos riamh, 'Gus dá bpósfainn cailleach ghránna mo lánchreach ná mairfinn bliain, Ach phósfainn thusa, a ghrá ghil, a chúil fáinneach na dtrioplaí siar, Is do bhainfinnse binse breá duit chomh hálainn is a chonaic tú ariamh. [UD_Irish-IDT 1183, CC BY-SA 3.0]
 Bhí máthair Jamesie ag éirí ar mire gur tubaist éigin trom a bhain dóibh. [UD_Irish-IDT 1349, CC BY-SA 3.0]
-Tuigeann Muire dóibh go maith, agus bainfidh sí aontacht na hEaglaise amach dóibh ar chuma nach síleann siad - gan dochar dá honóir féin. [UD_Irish-IDT 2421, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
+Tuigeann Muire dóibh go maith, agus bainfidh sí aontacht na hEaglaise amach dóibh ar chuma nach síleann siad - gan dochar dá honóir féin. [UD_Irish-IDT 2421, CC BY-SA 3.0]
+Agus cuirfi misi námhadus eadrad agus an bhean, agus eidir do shíol agus a síolsan; brúighfidh sé do cheannsa, agus brúighfidh tusa a shálsan. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Ach riotsa daingneóchaidh mé mo chunnradh, agus tiucfa tú asteach sa-Náirc thú féin agus do mhic agus do bhean, agus mná do mhac maille riot. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bain_do#Irish
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/bain</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr"/>
-      <c r="N52" s="3" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr"/>
       <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3434,26 +3955,36 @@
       <c r="J53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Ba leor an teoiric seo i gcúrsaí eolaíochta agus teicneolaíochta ar feadh dhá chéad bliain ach bhí sí fabhtach chun cur síos ar ghluaisní le luas gar do luas an tsolais nó le feiniméin ar scála idir-réaltach. [UD_Irish-IDT 166, CC BY-SA 3.0]
 na difríochtaí ó thaobh airíonna de a tharlaíonn laistigh de speiceas áirithe; mar shampla, bíonn daoine difriúil ó thaobh dath a gcuid gruaige, a súl agus a gcraicne de agus bíonn siad difriúil ó thaobh méid de freisin athrú gáis go leacht de thoradh fuaraithe: mar shampla, athraíonn an ghal ó chiteal atá ar fiuchadh ina leacht nuair a bhuaileann sí le balla fuar cistine comhthionól ball a thiomáineann fuil ar fud an choirp; is é ráta cuisle duine fhásta ná thart ar 70 buille in aghaidh an nóiméid, ach bíonn sí i bhfad níos tapúla ag leanbh; trí ghréasán d'fhéitheanna a ghluaiseann an fhuil; fágann an fhuil an croí trí artairí agus filleann sí ar an gcroí trí fhéitheanna achar beag, thart ar mhéadar cearnach de ghnáth, a léiríonn na plandaí go léir a fhásann sa réimse sin; is féidir ceann a dhéanamh as píosaí sreinge, corda nó adhmaid an ráta ar a gcuirtear obair i gcrích, is é sin, an méid oibre a dhéantar in aghaidh an tsecoind; is é an watt (W) an t-aonad cumhachta rud ar bith a ghlacann spás agus a bhfuil mais aige; is féidir mais a thabhairt ar gach uile shubstaint agus ábhar; úsáidtear na téarmaí solad, leacht agus gás chun cur síos ar thrí staid ábhair; is féidir staid amháin a thiontú go staid eile trí théamh nó fhuarú dath príomhúil is iad dathanna príomhúla an tsolais ná dearg, uaine agus gorm; faightear solas geal nuair a mheasctar na trí chineál le chéile go cionchothrom; nuair a mheasctar dhá dhath phríomhúla le chéile faightear ceann de na dathanna tánaisteacha, leithéidí buí, cian agus magenta; is iad dathanna príomhúla péinte ná dearg, buí agus gorm. [UD_Irish-IDT 951, CC BY-SA 3.0]
 ''Ach níorbh í allar na caróige, dhá scrútaighthe áithbhéalta dhá raibh sí, a chuir an spiacán as a láimh, síos amach go talamh. [UD_Irish-IDT 2009, CC BY-SA 3.0]
 Is téarma é seo a chuireann síos ar théamh domhanda, rud atá ina thoradh na dé-ocsaíde carbóin san atmaisféar atá ag dul i méid i gcónaí. = This is a term used to describe the warming of the earth, due to growing amounts of carbon dioxide in the atmosphere. [Tatoeba 6319336, CC BY 2.0 FR]
-Ta cios, cana, deachmhadh, sraith contae agus teampuill róthrom, agus ni fuláir a mbeith an faid bheidh an fiach righe, .i. an fiac Sasanach, .i. an fiach do thosadh Rig Uilliam do chur ar an righeacht chum an creidimh gallda do chongbhail suas, agus an creidimh caitliceach do chur sios. [UD_Irish-Cadhan cinlae-244, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
+Ta cios, cana, deachmhadh, sraith contae agus teampuill róthrom, agus ni fuláir a mbeith an faid bheidh an fiach righe, .i. an fiac Sasanach, .i. an fiach do thosadh Rig Uilliam do chur ar an righeacht chum an creidimh gallda do chongbhail suas, agus an creidimh caitliceach do chur sios. [UD_Irish-Cadhan cinlae-244, pre-standard, CC BY-SA 4.0]
+Cuiream síos ar dtús geinealach an fhir seo do réir mar fuaramar romhainn é. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, I, pre-standard, public domain]
+Cuirfidh sé síos ar an mBreac dhuit, ar a thoirt, ar a mheadhchan, ar a chlisteacht—cuirfead geall leat go gcloisfidh tú sgéalta faoi Bhreac na hAibhne Móire a sháróchas aon sgéal iasgaireachta atá sna leabhraibh.... [Wikisource: An Crann Géagach/An Breac atá san Abhainn Mhóir, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cuir_síos#Irish
 https://tatoeba.org/en/sentences/show/6319336
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_I
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Breac_at%C3%A1_san_Abhainn_Mh%C3%B3ir
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr"/>
-      <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3488,22 +4019,32 @@
       <c r="J54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Cur amú óige na cruinne a bhí sa dá chogadh dhomhanda a d'fhág a lorg fuilteach ar na mílte a chuaigh chun troda i bpáirceanna an áir san Eoraip agus níos mó faide ón bhaile. [UD_Irish-IDT 470, CC BY-SA 3.0]
 'Níor cheart go mbeadh eagla orainn ár lorg féin a fhágáil ar an timpeallacht agus ailtireacht a bhaineann lenár n-aimsir féin a fhorbairt. [UD_Irish-IDT 341, CC BY-SA 3.0]
-'Níor cheart do na polaiteoirí aislingí a chumadh agus an pobal a fhágáil ar an ngannchuid maidir lena bhfíorú. [UD_Irish-IDT 1048, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fág</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
+'Níor cheart do na polaiteoirí aislingí a chumadh agus an pobal a fhágáil ar an ngannchuid maidir lena bhfíorú. [UD_Irish-IDT 1048, CC BY-SA 3.0]
+“Cá’r fhág tú Eibhlín?” ar sise—agus tháinic áthas croidhe orm go raibh fhios agam cé’n t‑ainm bhí ar an mnaoi áluinn sin n‑ar chuir mé an spéis mhór. [Wikisource: An Crann Géagach/Beirt faoi chrann, pre-standard, public domain]
+n‑a chrann sul ar fhág Normánach cos ar thalamh na nÉireann... [Wikisource: An Crann Géagach/Crann na Croiche, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Beirt_faoi_chrann
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Crann_na_Croiche
+https://www.teanglann.ie/en/fgb/fág</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr"/>
       <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3538,25 +4079,35 @@
       <c r="J55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>D'ainneoin fíoch na filíochta idir an bheirt thug fear Ceann Tíre isteach an strainséir agus thug béile aráin rósta dó agus im tíre air a thug a bhean anall ón Chill san Cheann Deas. [UD_Irish-IDT 526, CC BY-SA 3.0]
 Gan dabht chun iad a chur ar an sráid, bheadh orthu iad a thabhairt isteach sa chathair ar dtúis. [UD_Irish-IDT 794, CC BY-SA 3.0]
 'Caithfidh tú brath ar na himreoirí áitiúla nuair atá tú i Roinn 1 agus ansin cúpla duine eile a thabhairt isteach má thagann an t-ardú céime. [UD_Irish-IDT 417, CC BY-SA 3.0]
 Thug mé isteach. = I gave up. [Tatoeba 10317400, CC BY 2.0 FR]
-Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
+Teidheadh an smólach amach gach la agus tugadh asteach lei i n-a gob brobh feir, tar eis e thomadh i rianán uisge, bhí laimh leis an ttigh, agus do rinn an nidín cluthar cruinn di fein san feoilchiste, ait a mbiodh sbrúileach agus blodhairighe arain le fail aici. [UD_Irish-Cadhan cinlae-211, pre-standard, CC BY-SA 4.0]
+Agus tug an tóglach na daóine asteach go tigh Ióseph, agus tug uisge dhóibh, agus do nígheadur a ccossa, agus tug bíadh da nassaluibh [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus tug Ióseph Iácob a athair asteach, agus do shuighidh é as choinne Pháraó, agus do bheannuigh Iácob Pháraó. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10317400
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/tabhair</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3591,24 +4142,34 @@
       <c r="J56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Sé deacracht a bhíodh agam teacht amach as an saol san agus plé le gnáthchúrsaí an tsaoil ina rabhas ag maireachtaint. [UD_Irish-IDT 200, CC BY-SA 3.0]
 Le gairid amach thángthas ar chruthú a léirigh go dtógtar litreacha le seoltaí i nGaeilge orthu i leataobh, go ngream-aítear lipéid bhreise leo ag 'aistriú' na seoltaí go Béarla nó go Gaeilge thruaillithe (Dublin sa chás seo). [UD_Irish-IDT 1571, CC BY-SA 3.0]
 Ceann de na moltaí a tháinig amach as an ghrúpa oibre go raibh gá le foireann lánaimseartha lena chinntiú go raibh leanúnachas ann. [UD_Irish-IDT 1774, CC BY-SA 3.0]
-Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
+Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]
+Tar amach, a Dúchrónaigh! [Wikisource: Aistriúchán:Tar Amach, a Dúchrónaigh (Behan, Béarla), pre-standard, public domain]
+Tar amach agus troid liom mar fhear! [Wikisource: Aistriúchán:Tar Amach, a Dúchrónaigh (Behan, Béarla), pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/752762
+https://wikisource.org/wiki/Aistri%C3%BAch%C3%A1n%3ATar_Amach%2C_a_D%C3%BAchr%C3%B3naigh_%28Behan%2C_B%C3%A9arla%29
+https://wikisource.org/wiki/Aistri%C3%BAch%C3%A1n%3ATar_Amach%2C_a_D%C3%BAchr%C3%B3naigh_%28Behan%2C_B%C3%A9arla%29
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr"/>
       <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3643,27 +4204,37 @@
       <c r="J57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>'Tagann an t-am do'n phréamh féin nuair ná fanann inti cur aisti níos sia. [UD_Irish-IDT 892, CC BY-SA 3.0]
 Don bhliain 2002, tháinig luach na dtáillí pleanála in iomláine go 1.3 Dorchadas. [UD_Irish-IDT 1494, CC BY-SA 3.0]
 Pointe suimiúil a luaigh sé ná go dtagann sé níos nádúrtha do mhná labhairt faoi scéalta pearsanta spioradálta, cuir i gcás ag grúpaí urnaí, agus go mbíonn fir amscaí nó cúthaileach faoin a leithéid. [UD_Irish-IDT 2034, CC BY-SA 3.0]
 An ndéanfaidh tú staidéar tar éis teacht abhaile duit? = Will you study after you come home? [Tatoeba 3944972, CC BY 2.0 FR]
 Gheibh thu leabhar innteanach ma thig thu do Chomhairle nan Leabhraichean! = You will get an interesting book if you go to Comhairle nan Leabhraichean. [Tatoeba 5897274, CC BY 2.0 FR]
-Ag teacht abhaile dhom tar Droichead na nGabhar chualas air gach taoib díom an smolach, an fuiseog, agus gac einín bin eile ag ceileabhradh da cheile. [UD_Irish-Cadhan cinlae-46, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+Ag teacht abhaile dhom tar Droichead na nGabhar chualas air gach taoib díom an smolach, an fuiseog, agus gac einín bin eile ag ceileabhradh da cheile. [UD_Irish-Cadhan cinlae-46, pre-standard, CC BY-SA 4.0]
+Is do chnámha sínte tar éis do ghrinn, [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]
+Tiocfaidh do phárdún ón bPápa is ón Róimh anoir [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/3944972
 https://tatoeba.org/en/sentences/show/5897274
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
+https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="3" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3698,22 +4269,32 @@
       <c r="J58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Bhí togha na Gaeilge aici; thóg sí léi í óna seanmháthair agus d'fhoghlaim sise í óna hathair siúd. [UD_Irish-IDT 727, CC BY-SA 3.0]
 Tithe ceann tuí a bhí iontu a tógadh le clocha le seomra leapa amháin laistiar den tine. [UD_Irish-IDT 980, CC BY-SA 3.0]
-Le gairid amach thángthas ar chruthú a léirigh go dtógtar litreacha le seoltaí i nGaeilge orthu i leataobh, go ngream-aítear lipéid bhreise leo ag 'aistriú' na seoltaí go Béarla nó go Gaeilge thruaillithe (Dublin sa chás seo). [UD_Irish-IDT 1571, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="3" t="inlineStr"/>
+Le gairid amach thángthas ar chruthú a léirigh go dtógtar litreacha le seoltaí i nGaeilge orthu i leataobh, go ngream-aítear lipéid bhreise leo ag 'aistriú' na seoltaí go Béarla nó go Gaeilge thruaillithe (Dublin sa chás seo). [UD_Irish-IDT 1571, CC BY-SA 3.0]
+Agus do thóg a dearbhráithre leis, agus do lean é aistior sheachd lá, agus rugadur air ar shlíabh Gíleadh. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus do thóg Esau leis a mhná, agus a mhic, agus a ingheana, agus an uile phearsa dá theaghlach, agus a áirnéis, agus a uile ainmhintighe, agus a shubstaint uile, noch fúair sé a ttír Chánaain; agus dochuáidh fan tír, ó aghuidh a dhearbhrathair Iácob. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="3" t="inlineStr"/>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3748,22 +4329,32 @@
       <c r="J59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>A mhná uaisle agus a uaisle go léir, níl sé i gceist agam am a chur amú chun teacht ar réiteach na faidhbe seo... dhein Bricriú iarracht bob a bhualadh oraibh, ach níor éirigh leis. [UD_Irish-IDT 508, CC BY-SA 3.0]
 Aonach a' Phoic Duine a bheadh ag ceannach capaill ní dhéanfadh sé margadh le tincéirí ar eagla go mbuailfí bob air faoi mar a buaileadh ar Phádraig Bán ar Aonach a' Phoic i gCill Orglan uair. [UD_Irish-IDT 121, CC BY-SA 3.0]
-Aonach a' Phoic Duine a bheadh ag ceannach capaill ní dhéanfadh sé margadh le tincéirí ar eagla go mbuailfí bob air faoi mar a buaileadh ar Phádraig Bán ar Aonach a' Phoic i gCill Orglan uair. [UD_Irish-IDT 121, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/buail</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="3" t="inlineStr"/>
+Aonach a' Phoic Duine a bheadh ag ceannach capaill ní dhéanfadh sé margadh le tincéirí ar eagla go mbuailfí bob air faoi mar a buaileadh ar Phádraig Bán ar Aonach a' Phoic i gCill Orglan uair. [UD_Irish-IDT 121, CC BY-SA 3.0]
+Agus do éug Huram, agus Hádad mhac Bédad, noch do bhuáil Mídian air mhagh Móab, fá rígh na áit: agus dobé ainm a chaithreach Abhit. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Do cheapfá gur buille do buaileadh uirthi. [Wikisource: An Mháthair agus Sgéalta Eile/An Bhean Chaointe, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/An_Bhean_Chaointe
+https://www.teanglann.ie/en/fgb/buail</t>
+        </is>
+      </c>
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3798,22 +4389,32 @@
       <c r="J60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Faoi mar a tharla, is oth liom go raibh triúr de na comhaltaí nach bhféadfainnse glacadh leis an dearcadh a bhí acu agus, sna cúinsí uile, ní raibh dul as agam ach iad a chur as oifig. [UD_Irish-IDT 787, CC BY-SA 3.0]
 'Tagann an t-am do'n phréamh féin nuair ná fanann inti cur aisti níos sia. [UD_Irish-IDT 892, CC BY-SA 3.0]
-Cuireann Paul Ó Braoin as Baile Átha Luain an píosa seo chugainn, ar aistriúchán é ar alt a foilsíodh in eagrán Aibreáin den iris Irish Computer agus a athfoilsítear anseo le caoin-chead eagarthóra na hirise sin, Declan McColgan. [UD_Irish-IDT 1359, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cuir</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr"/>
-      <c r="N60" s="3" t="inlineStr"/>
+Cuireann Paul Ó Braoin as Baile Átha Luain an píosa seo chugainn, ar aistriúchán é ar alt a foilsíodh in eagrán Aibreáin den iris Irish Computer agus a athfoilsítear anseo le caoin-chead eagarthóra na hirise sin, Declan McColgan. [UD_Irish-IDT 1359, CC BY-SA 3.0]
+Do stadadh a anál, agus ba bheag ná go dtuiteadh an t-anam as, i n-aghaidh gach ulfairte d’á gcuireadh an gadhar mór as. [Wikisource: Aesop a tháinig go h-Éirinn/An Fhiolar agus an Mada Ruadh, pre-standard, public domain]
+Do stadadh a anál, agus ba bheag ná go dtuiteadh an t-anam as, i n-aghaidh gach ulfairte d’á gcuireadh an gadhar mór as. [Wikisource: Aesop a tháinig go h-Éirinn/An Luch Tuatha agus Luch an Bhaile Mhóir, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Fhiolar_agus_an_Mada_Ruadh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Luch_Tuatha_agus_Luch_an_Bhaile_Mh%C3%B3ir
+https://www.teanglann.ie/en/fgb/cuir</t>
+        </is>
+      </c>
       <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3848,23 +4449,33 @@
       <c r="J61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Tá trácht sa dán ar mheath an chreidimh: A bhuíochas ar an dán sin agus na scoláirí, na scríobhaithe, a chuir slán ó ghlúin go glúin é, d'fhan an tuiscint don stair beo agus don aigne shinseartha. [UD_Irish-IDT 860, CC BY-SA 3.0]
 Ó 1996, áfach, cuireadh tús le roinnt cúrsaí iarchéime. [UD_Irish-IDT 374, CC BY-SA 3.0]
 Beidh Cúldoras ann 'agus de réir mar a bheidh an samhradh á chaitheamh beidh an ríomhaire ag cur foirne ó bhealach sa gcaoi agus nuair a shroichfear mí Mheán Fómhair nach mbeidh fanta san iomaíocht ach dhá chontae sa bpeil agus dhá chontae eile san iománaíocht. [UD_Irish-IDT 949, CC BY-SA 3.0]
-Ní ar a sonsan amháin doním guidhe, achd mar an gcéudna ar son na ndáoine chreidfios ionnam, tré na mbreithirsean: Dochum gu mbéidís uile ná náon, mar atá tusa a athuir ionnamsa, agus meisi ionnadsa: dochum gu mbéidision mar an gcédna na naon ionnuinne: dochum gu gcreidfeadh an sáoghal, gurab tusa dho chuir uáit mhé. [UD_Irish-Cadhan eoin-785, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cuir</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr"/>
+Ní ar a sonsan amháin doním guidhe, achd mar an gcéudna ar son na ndáoine chreidfios ionnam, tré na mbreithirsean: Dochum gu mbéidís uile ná náon, mar atá tusa a athuir ionnamsa, agus meisi ionnadsa: dochum gu mbéidision mar an gcédna na naon ionnuinne: dochum gu gcreidfeadh an sáoghal, gurab tusa dho chuir uáit mhé. [UD_Irish-Cadhan eoin-785, pre-standard, CC BY-SA 4.0]
+Go dtéidhir slán!” Do léim sé thar claidh agus chuir sé an réidh ó thuaidh dé. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Do chuir Montrós an coirnéal Mághnus Ó Catháin agus Fir na Craoibhe i n-úrthosach an chatha agus ba ghearr a mhoill orra muintir Mhic Ailín [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://www.teanglann.ie/en/fgb/cuir</t>
+        </is>
+      </c>
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3903,27 +4514,37 @@
       <c r="J62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>na difríochtaí ó thaobh airíonna de a tharlaíonn laistigh de speiceas áirithe; mar shampla, bíonn daoine difriúil ó thaobh dath a gcuid gruaige, a súl agus a gcraicne de agus bíonn siad difriúil ó thaobh méid de freisin athrú gáis go leacht de thoradh fuaraithe: mar shampla, athraíonn an ghal ó chiteal atá ar fiuchadh ina leacht nuair a bhuaileann sí le balla fuar cistine comhthionól ball a thiomáineann fuil ar fud an choirp; is é ráta cuisle duine fhásta ná thart ar 70 buille in aghaidh an nóiméid, ach bíonn sí i bhfad níos tapúla ag leanbh; trí ghréasán d'fhéitheanna a ghluaiseann an fhuil; fágann an fhuil an croí trí artairí agus filleann sí ar an gcroí trí fhéitheanna achar beag, thart ar mhéadar cearnach de ghnáth, a léiríonn na plandaí go léir a fhásann sa réimse sin; is féidir ceann a dhéanamh as píosaí sreinge, corda nó adhmaid an ráta ar a gcuirtear obair i gcrích, is é sin, an méid oibre a dhéantar in aghaidh an tsecoind; is é an watt (W) an t-aonad cumhachta rud ar bith a ghlacann spás agus a bhfuil mais aige; is féidir mais a thabhairt ar gach uile shubstaint agus ábhar; úsáidtear na téarmaí solad, leacht agus gás chun cur síos ar thrí staid ábhair; is féidir staid amháin a thiontú go staid eile trí théamh nó fhuarú dath príomhúil is iad dathanna príomhúla an tsolais ná dearg, uaine agus gorm; faightear solas geal nuair a mheasctar na trí chineál le chéile go cionchothrom; nuair a mheasctar dhá dhath phríomhúla le chéile faightear ceann de na dathanna tánaisteacha, leithéidí buí, cian agus magenta; is iad dathanna príomhúla péinte ná dearg, buí agus gorm. [UD_Irish-IDT 951, CC BY-SA 3.0]
 Níos measa fós níor thacaigh an cheannaireacht le hiarrachtaí oifigigh sa Daingean agus i gConamara aonaid lán-Ghaeilge a dhéanamh as a gcomplachtaí. [UD_Irish-IDT 1643, CC BY-SA 3.0]
 Déantar astuithe CH4 agus N2O araon as stóráil agus as leasú aoileach na n-ainmhithe. [UD_Irish-IDT 3990, CC BY-SA 3.0]
 Déan é as do neart féin. = Do it out of your own strength. [Tatoeba 7799813, CC BY 2.0 FR]
-Déantar plúr as cruithneacht. = Flour is made from wheat. [Tatoeba 9158361, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
+Déantar plúr as cruithneacht. = Flour is made from wheat. [Tatoeba 9158361, CC BY 2.0 FR]
+“Ní thugaim dul as d’ éunaibh,” arsa ’n eas. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]
+“Ní thugaim dul as do luchaibh,” arsa’ n eas. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/déan_as#Irish
 https://tatoeba.org/en/sentences/show/7799813
 https://tatoeba.org/en/sentences/show/9158361
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
 https://www.teanglann.ie/en/fgb/déan</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3958,24 +4579,34 @@
       <c r="J63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Is Gaeilgeoirí ó dhúchas isteach is amach ar dheich faoin gcéad de na mic léinn a thagann isteach go Coláiste Phádraig, Droim Conrach gach bliain. [UD_Irish-IDT 803, CC BY-SA 3.0]
 Tháinig beirt fhathach isteach sa chúige agus bhí siad ag creachadh na dúiche gan stad gan staonadh. [UD_Irish-IDT 198, CC BY-SA 3.0]
 Ach i gcónaí nuair a rachadh sí a bhuaileadh thiocfadh bean de chuid na comharsa isteach agus shuighfeadh sí sa chlúdaigh ag comhrá léithe agus nuair a bheadh an bainne buailte d'imeochadh sí léithe chun an bhaile. [UD_Irish-IDT 1007, CC BY-SA 3.0]
-Tar isteach. = Come in. [Tatoeba 7801398, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
+Tar isteach. = Come in. [Tatoeba 7801398, CC BY 2.0 FR]
+Do fógradar do mhuinntir na tíre sin teacht isteach i n-arm an ríogh nó go loisgfeadh agus go gcreachfadh an tír do taisbeánadh an t-ordughadh dhóibh agus do thógbhadar leis an ordughadh sin Clann Mhuireadhaigh Bháideineach agus caiptín agus ceann feadhna maith dá bhfuil féin rómpa .i. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Sir Tómós Do ghluaiseadar ó Chill Chuimín tar Láirc Thurraid agus isteach go Gleann Ruaidh agus tairis an Sbeathain agus tárla pártaigh don námhaid dhóibh ann soin agus do leansad iad agus do marbhadh a n-urmhór agus an droig do chuaidh as díobh tugadar sgéala don champa agus do bhí anmoch Dia Sathrainn ar dteacht ortha an tráth rángadar ar chomhair a námhad. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/7801398
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr"/>
-      <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4010,23 +4641,33 @@
       <c r="J64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Liobairt mhaith de'n teangaidh a bhí in áithrid dó ag a' siopadóir, a's sé a dtug sé d'áirleacan dó, noiméad a' chloig le crapadh leis as a siopa, nó go gcuirfeadh sé na póilíos in a dhiaidh. [UD_Irish-IDT 561, CC BY-SA 3.0]
 I gceantar Anagaire mar shampla tá ar a laghad deich mbaile fearainn nach dtugtar aitheantas díobhtha i seoladh an vótóra rud a chiallaíonn go mbíonn an seoladh poist céanna ag na vótóirí uilig. [UD_Irish-IDT 635, CC BY-SA 3.0]
 (4) Aon duine a thabharfaidh faisnéis bhréagach go feasach de bhun iarrata faoin alt seo, beidh sé nó sí ciontach i gcion. [UD_Irish-IDT 2887, CC BY-SA 3.0]
-Tug d'Fhidheach mac Féigh, d'fhearaibh na craoibhe, ó Fhidhic go Luimneach. [UD_Irish-Cadhan forasfeasa-303, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr"/>
-      <c r="N64" s="3" t="inlineStr"/>
+Tug d'Fhidheach mac Féigh, d'fhearaibh na craoibhe, ó Fhidhic go Luimneach. [UD_Irish-Cadhan forasfeasa-303, pre-standard, CC BY-SA 4.0]
+"Is mór an náire dúinn an t-aon duine ag tabhairt ár gclú dhínn do ghnáth, mar bhristear ar an uile námhaid rómhainn; ag sin Alasdair ar mbreith buadha ar an mhuinntir do bhí ós a chomhair féin don chath agus tugaidh-se an adbhansa go gléasda grod-athlamh." [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Agus tug Lamech días ban, aon díobh darbhainm Sillah. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="3" t="inlineStr"/>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4061,22 +4702,32 @@
       <c r="J65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>D'ainneoin fíoch na filíochta idir an bheirt thug fear Ceann Tíre isteach an strainséir agus thug béile aráin rósta dó agus im tíre air a thug a bhean anall ón Chill san Cheann Deas. [UD_Irish-IDT 526, CC BY-SA 3.0]
 Ó am go chéile thugadh Ljúbín leis go dtí a theach féin é. [UD_Irish-IDT 822, CC BY-SA 3.0]
-Is mian linn ár mbuíochas a chur in iúl go háirithe do Sheán Ó Gallchóir, Stiúrthóir Ginearálta an Fhorais Riaracháin, a thug lántacaíocht ó thús don ghnó. [UD_Irish-IDT 43, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr"/>
-      <c r="N65" s="3" t="inlineStr"/>
+Is mian linn ár mbuíochas a chur in iúl go háirithe do Sheán Ó Gallchóir, Stiúrthóir Ginearálta an Fhorais Riaracháin, a thug lántacaíocht ó thús don ghnó. [UD_Irish-IDT 43, CC BY-SA 3.0]
+Is dómhsa is ceart an chómhairle sin do thabhairt uaim ar tá fios dá thaoibh an sgéil agam ó baineadh an t-earbal díom féin. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+Fé mar a neartuigh sé sa n-aois do chruaidh sé sa ghaduígheacht agus thug sé a lán neithe ba dhaoíre ’ná a chéile chum a mháthar. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr"/>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4115,22 +4766,32 @@
       <c r="J66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>Má tá boird stáit agus comhlachtai stáir in Éirinn ag dul ag fógairt mar 'phacáiste' ar leith d'Éirinn, má tá RTÉ ag dul i gcomhar le Sky maidir le dáileadh na mbealach teilifís Éireannach ar bhosca digiteach Sky ar fud na tíre (cinneadh atá tar éis an-gheit a bhaint as oifig an Aire de Valera, deirtear linn) níor cheart cur suas leis an neamhaird ar leith a dhéananna meáin na Sasasanach ar Éirinn de ghnáth. [UD_Irish-IDT 938, CC BY-SA 3.0]
-D'athraigh sé go millteanach, déarfainnse gur bhfurast smacht a chur ar pháistí suas go dtí naoi gcéad déag is a seachtmhadh, nó mar sin - go dtí go dtáinig an curriculum úr isteach. [UD_Irish-IDT 2871, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
+D'athraigh sé go millteanach, déarfainnse gur bhfurast smacht a chur ar pháistí suas go dtí naoi gcéad déag is a seachtmhadh, nó mar sin - go dtí go dtáinig an curriculum úr isteach. [UD_Irish-IDT 2871, CC BY-SA 3.0]
+Agus do chuir altóir suas annsin, agus do ghoir ar ainm an tighearna, agus do shuighidh a phubuil annsin: agus do thochladar seirbhísigh Isaac tobar ann. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus dochonnairc aisling, agus féuch dréimre arna chur súas ar an talamh, agus ráinic a bhárr go flaitheamhnus: agus féuch, aingil Dé ag dul ag teachd ansúas ann. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cuir_suas#Irish
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/cuir</t>
         </is>
       </c>
-      <c r="M66" s="3" t="inlineStr"/>
-      <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="3" t="inlineStr"/>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4165,39 +4826,49 @@
       <c r="J67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Agus ar an drochuair thit sí féin as a seasamh i bproinnteach agus iad ar a mbealach ó dheas. [UD_Irish-IDT 296, CC BY-SA 3.0]
 Má thiteann tuismitheoir/céile/páirtí sibhialta ar gcúl le híocaíochtaí mar a mbíonn ordú cothabhála i bhfeidhm, is féidir iarratas a dhéanamh sa chúirt ar thoghairm astú tuillimh. [UD_Irish-IDT 3621, CC BY-SA 3.0]
 Titeann do bhronntanas ar lár, nó ní bhíonn feidhm aige níos mó, má fhaigheann an dílseánach beinifíse bás romhat. [UD_Irish-IDT 4868, CC BY-SA 3.0]
-Sleamhnaigh mé agus thit mé ar an trasrian, díreach nuair a chas an solas chuig dearg. = I slipped and fell on the crosswalk, just when the light turned red. [Tatoeba 4062767, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
+Sleamhnaigh mé agus thit mé ar an trasrian, díreach nuair a chas an solas chuig dearg. = I slipped and fell on the crosswalk, just when the light turned red. [Tatoeba 4062767, CC BY 2.0 FR]
+DO ThUIT AR AN MAChAIRE SIN DhÁ MhÍLE GALL, AGUS NÍOR CAILLEADh OIREAD AGUS DUINE DE’N ARM GhAEDhEALACh. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]
+Cuid d’adhbharaibh na gcreach sin do thuit air tar daoinibh oile, do bhíodh mórán do Ghaoidhealaibh oile do churthaoi do thógbháil chreach ag imtheacht leis na creachaibh do-nídís d’ionnsaighe a dtíreadh féin gan chead dá nginiral. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/4062767
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/tit</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="inlineStr"/>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>seas ar</t>
+          <t>tar amach as</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>seas</t>
+          <t>tar</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>amach as</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4217,29 +4888,39 @@
       <c r="J68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Tá sí ina suí ar fhiacail na mbeann suas le trí chéad troigh os cionn na farraige agus nádúr tarraingteach aici a mheallann corrdhuine ceanndána eachtrúil chun seasamh nó suí uirthi. [UD_Irish-IDT 883, CC BY-SA 3.0]
-Nuair a bhí sé ag goil síos ón bpier síos go dtí an bád, sheas sé ar thaobh na curraigh agus d'iontaigh sé an currach sa gcéibh. [UD_Irish-IDT 1695, CC BY-SA 3.0]
-@user27 @user241 @user1743 5'10, seansfaidh mé ar mo bharraicíní [UD_Irish-TwittIrish NTC_20963, CC BY-SA 4.0]
-Sheas sí ar an díon. = She stood on the roof. [Tatoeba 10926397, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/10926397
-https://www.teanglann.ie/en/fgb/seas</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr"/>
-      <c r="N68" s="3" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Sé deacracht a bhíodh agam teacht amach as an saol san agus plé le gnáthchúrsaí an tsaoil ina rabhas ag maireachtaint. [UD_Irish-IDT 200, CC BY-SA 3.0]
+Ceann de na moltaí a tháinig amach as an ghrúpa oibre go raibh gá le foireann lánaimseartha lena chinntiú go raibh leanúnachas ann. [UD_Irish-IDT 1774, CC BY-SA 3.0]
+Nuair a tháinig mé amach as an teach óstán bhí an tráthnóna grianmhar agus mheas mé gurbh iontach an radharc a bhí ón teach ósta agus ar an bhealach go Ceann na Creige (Kennacraig) ar Loch Iarthar Tairbeairt. [UD_Irish-IDT 2739, CC BY-SA 3.0]
+Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]
+Agus dodhéuna mé ro thórrthach thú, agus dodhéuna mé cinidheacha dhíot, agus tiocfaid ríghthe asad amach. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus do thaisbéin Día arís é féin do Iácob anuáir tháinic sé amach as Pádan-Aram, agus do bheannuigh sé é. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/752762
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tar</t>
+        </is>
+      </c>
       <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="3" t="inlineStr"/>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>tar amach as</t>
+          <t>tar de</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4249,7 +4930,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>amach as</t>
+          <t>de</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4261,37 +4942,46 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Sé deacracht a bhíodh agam teacht amach as an saol san agus plé le gnáthchúrsaí an tsaoil ina rabhas ag maireachtaint. [UD_Irish-IDT 200, CC BY-SA 3.0]
-Ceann de na moltaí a tháinig amach as an ghrúpa oibre go raibh gá le foireann lánaimseartha lena chinntiú go raibh leanúnachas ann. [UD_Irish-IDT 1774, CC BY-SA 3.0]
-Nuair a tháinig mé amach as an teach óstán bhí an tráthnóna grianmhar agus mheas mé gurbh iontach an radharc a bhí ón teach ósta agus ar an bhealach go Ceann na Creige (Kennacraig) ar Loch Iarthar Tairbeairt. [UD_Irish-IDT 2739, CC BY-SA 3.0]
-Tháinig mé amach as an tacsaí. = I got out of the taxi. [Tatoeba 752762, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/752762
+        <v>0</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Dá dtagadh de chorr san sa tsaol, áireoinn na thoirbhirt deonta ó Dhia é. [UD_Irish-IDT 1629, CC BY-SA 3.0]
+Tháinig a chothrom de luisne i mo leicne féin, agus bhraith an bheirt againn go rabhamar ar comhscéal le chéile. [UD_Irish-IDT 2546, CC BY-SA 3.0]
+Chomh maith leis sin, b'Fheisirí nua i bParlaimint na hEorpa 60% de na Feisirí, agus tháinig 168 díobh ó na 10 mBallstát nua. [UD_Irish-IDT 3167, CC BY-SA 3.0]
+Tanaig Iosa trenar ccoir do nimh a-nuas on Athoir 'sdo dhoirt fuil a chuirp uile air ar ngradh tre thrócuire. [UD_Irish-Cadhan bardic_1387-18, pre-standard, CC BY-SA 4.0]
+Tháinig sluagh mór de Ghallaibh ’na n-aghaidh agus b’éigean do Mhontrós géilleadh rómpa agus dul ar ais isna Garbh- Chríochaibh. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]
+Táinig dhe sin Muntrós do dhul as an ríoghacht d’iarraidh conganta ar ríoghaibh agus ar phrionnsaíbh oile do chongnamh le Rígh Séarlus agus ar bhfilleadh dó ón turus sin do milleadh go heasonórach le Comhairle na hAlban leis na Coibhineantairsi é féin agus Marcós Hunntlí agus mórán d’uaislibh oile do bhí ar thaobh an ríogh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/tar</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>tar de</t>
+          <t>tar faoi</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4301,7 +4991,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>faoi</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4316,43 +5006,52 @@
         <v>4</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Dá dtagadh de chorr san sa tsaol, áireoinn na thoirbhirt deonta ó Dhia é. [UD_Irish-IDT 1629, CC BY-SA 3.0]
-Tháinig a chothrom de luisne i mo leicne féin, agus bhraith an bheirt againn go rabhamar ar comhscéal le chéile. [UD_Irish-IDT 2546, CC BY-SA 3.0]
-Chomh maith leis sin, b'Fheisirí nua i bParlaimint na hEorpa 60% de na Feisirí, agus tháinig 168 díobh ó na 10 mBallstát nua. [UD_Irish-IDT 3167, CC BY-SA 3.0]
-Tanaig Iosa trenar ccoir do nimh a-nuas on Athoir 'sdo dhoirt fuil a chuirp uile air ar ngradh tre thrócuire. [UD_Irish-Cadhan bardic_1387-18, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tar</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr"/>
-      <c r="N70" s="3" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Tá áthas orm gur tharla mo sheirbhís i gCathaoir Pheadair sa tréimhse iar-Chomhairleach, agus bonn tathagach ag teacht faoin inspioráid a threoraigh Nostra Aetate. [UD_Irish-IDT 687, CC BY-SA 3.0]
+Tháinig borradh breise faoin iarracht de dheasca na bhfíricí faoi pholasaí nua an INTO in aghaidh na Gaeilge a foilsíodh, go heisiach, ar ANOIS an deireadh seachtaine seo caite. [UD_Irish-IDT 742, CC BY-SA 3.0]
+'Creidimidne, mar thoradh ar INTRA, go bhforbraíonn na mic léinn a gcuid tuisceana ar shaol proifisiúnta na tionsclaíochta agus go dtagann borradh faoina bhféinmhuinín, a n-aibíocht agus a gcuid scileanna caidrimh dhaonna,' a deir an Dr. Caoilfhionn Nic Pháidín, Stiúrthóir Fiontar. [UD_Irish-IDT 977, CC BY-SA 3.0]
+Sé an chéad rud a chonnac ag teacht fém’ dhéin ná Oscar agus níorbh’ fhada gur bhain amach me agus ba dhóigh [Wikisource: An t-Oileánach/12, pre-standard, public domain]
+Tháinig mór-chuid ó’n dtuaith fé dhéin an iongantais agus breac-chara agus beagán airgid ’n‑a phóca aige chun lámhaidheacht do thabhairt le h‑iad d’fhuascailt. [Wikisource: An t-Oileánach/18, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/12
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/18
+https://www.teanglann.ie/en/fgb/tar</t>
+        </is>
+      </c>
       <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>tar faoi</t>
+          <t>éist ar</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>éist</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4372,37 +5071,47 @@
       <c r="J71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Tá áthas orm gur tharla mo sheirbhís i gCathaoir Pheadair sa tréimhse iar-Chomhairleach, agus bonn tathagach ag teacht faoin inspioráid a threoraigh Nostra Aetate. [UD_Irish-IDT 687, CC BY-SA 3.0]
-Tháinig borradh breise faoin iarracht de dheasca na bhfíricí faoi pholasaí nua an INTO in aghaidh na Gaeilge a foilsíodh, go heisiach, ar ANOIS an deireadh seachtaine seo caite. [UD_Irish-IDT 742, CC BY-SA 3.0]
-'Creidimidne, mar thoradh ar INTRA, go bhforbraíonn na mic léinn a gcuid tuisceana ar shaol proifisiúnta na tionsclaíochta agus go dtagann borradh faoina bhféinmhuinín, a n-aibíocht agus a gcuid scileanna caidrimh dhaonna,' a deir an Dr. Caoilfhionn Nic Pháidín, Stiúrthóir Fiontar. [UD_Irish-IDT 977, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tar</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="3" t="inlineStr"/>
+      <c r="K71" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>(4) Féadfaidh an Chúirt imeachtaí nó cuid d'imeachtaí faoin alt seo a éisteacht ar shlí seachas go poiblí. [UD_Irish-IDT 1632, CC BY-SA 3.0]
+Féadfaidh na coistí inniúla de chuid Pharlaimint na hEorpa Uachtarán an Bhainc Cheannais Eorpaigh agus comhaltaí eile an Bhord Feidhmiúcháin a éisteacht arna iarraidh sin do Pharlaimint na hEorpa nó don Uachtarán agus do na comhaltaí ar a dtionscnamh féin. [UD_Irish-IDT 3013, CC BY-SA 3.0]
+Éist le 'As Gaeilge' anois ar @user1191 [UD_Irish-TwittIrish NTC_109, CC BY-SA 4.0]
+“Éist!” ar seisean, “labhair go réidh adeirim! [Wikisource: An Crann Géagach/M’asal beag dubh, pre-standard, public domain]
+“Éist, a dhailtín,” ar seisean, “deineadh cipíní beaga de’n árthach úd an tráthnóna céadna age Fiach an Fhirtéaraigh. [Wikisource: An t-Oileánach/6, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Crann_G%C3%A9agach/M%E2%80%99asal_beag_dubh
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/6
+https://www.teanglann.ie/en/fgb/éist</t>
+        </is>
+      </c>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="inlineStr"/>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>éist ar</t>
+          <t>bain amach do</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>éist</t>
+          <t>bain</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>amach do</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4414,7 +5123,7 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>0</v>
@@ -4422,37 +5131,47 @@
       <c r="J72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>(4) Féadfaidh an Chúirt imeachtaí nó cuid d'imeachtaí faoin alt seo a éisteacht ar shlí seachas go poiblí. [UD_Irish-IDT 1632, CC BY-SA 3.0]
-Féadfaidh na coistí inniúla de chuid Pharlaimint na hEorpa Uachtarán an Bhainc Cheannais Eorpaigh agus comhaltaí eile an Bhord Feidhmiúcháin a éisteacht arna iarraidh sin do Pharlaimint na hEorpa nó don Uachtarán agus do na comhaltaí ar a dtionscnamh féin. [UD_Irish-IDT 3013, CC BY-SA 3.0]
-Éist le 'As Gaeilge' anois ar @user1191 [UD_Irish-TwittIrish NTC_109, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/éist</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="3" t="inlineStr"/>
+      <c r="K72" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Tuigeann Muire dóibh go maith, agus bainfidh sí aontacht na hEaglaise amach dóibh ar chuma nach síleann siad - gan dochar dá honóir féin. [UD_Irish-IDT 2421, CC BY-SA 3.0]
+Tá mé cinnte go gcinnteoidh ár dtiomantas don chaomhnú réamhghníomhach, d'iarrachtaí eolaíochta agus don oideachas ar mhaithe le húsáid inbhuanaithe na bithéagsúlchta go mbainfear na torthaí is fearr amach d'Anaclann Bhithsféir UNESCO Chiarraí. [UD_Irish-IDT 4433, CC BY-SA 3.0]
+Tá an bhéim den chuid is mó ar mhaolú ar an mí-bhuntáiste sa soláthar oideachais/oiliúna Gaeltachta, ar chothromaíocht deiseanna a bhaint amach don Ghaeltacht agus ar an Ghaeilge mar mheán teagaisc san oideachas Gaeltachta a threisiú. [UD_Irish-IDT 4784, CC BY-SA 3.0]
+“Gaibhim párdún agaibh, ’fheara,” ar seisean, agus níor stad gur bhain amach me agus do bhain seacht gcrothadh as mo láimh. [Wikisource: An t-Oileánach/13, pre-standard, public domain]
+Dob’ éigean dúinn tarrac suas agus an talamh a bhaint amach; agus do lean sinn an fhaid a bhí dhá fheadh uisce aige. [Wikisource: An t-Oileánach/23, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/23
+https://www.teanglann.ie/en/fgb/bain</t>
+        </is>
+      </c>
       <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="3" t="inlineStr"/>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>bain amach do</t>
+          <t>déan ó</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>bain</t>
+          <t>déan</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>amach do</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4472,37 +5191,47 @@
       <c r="J73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Tuigeann Muire dóibh go maith, agus bainfidh sí aontacht na hEaglaise amach dóibh ar chuma nach síleann siad - gan dochar dá honóir féin. [UD_Irish-IDT 2421, CC BY-SA 3.0]
-Tá mé cinnte go gcinnteoidh ár dtiomantas don chaomhnú réamhghníomhach, d'iarrachtaí eolaíochta agus don oideachas ar mhaithe le húsáid inbhuanaithe na bithéagsúlchta go mbainfear na torthaí is fearr amach d'Anaclann Bhithsféir UNESCO Chiarraí. [UD_Irish-IDT 4433, CC BY-SA 3.0]
-Tá an bhéim den chuid is mó ar mhaolú ar an mí-bhuntáiste sa soláthar oideachais/oiliúna Gaeltachta, ar chothromaíocht deiseanna a bhaint amach don Ghaeltacht agus ar an Ghaeilge mar mheán teagaisc san oideachas Gaeltachta a threisiú. [UD_Irish-IDT 4784, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bain</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="3" t="inlineStr"/>
+      <c r="K73" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Déantar slad ar bhuíon de na Sherwood Foresters ag droichead Shráid an Mhóta agus iad ag iarraidh a mbealach a dhéanamh isteach go lár na cathrach ó Dhún Laoghaoire, áit ar thángadar i dtír. [UD_Irish-IDT 56, CC BY-SA 3.0]
+Déanfaidh an Roinn seo gach iarracht freagra a thabhairt ar d'iarratas AIE laistigh de mhí amháin ó dháta faighte an iarratais. [UD_Irish-IDT 2995, CC BY-SA 3.0]
+. @user733 @user263 bheinn ar son fórsa dlí a thabhairt do na treoirlínte. Trua nár rinneadh i bhfad ó shin sin. [UD_Irish-TwittIrish LTC_41, CC BY-SA 4.0]
+Ní fheadradar ó thalamh an domhain cad é an fuadar a bhí féi, nó cad air go raibh sé ag teacht. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+Do theip ortha a dhéanamh amach sa pháirc, áit ba dhóichíghe ’ná a chéile chum an airgid do bheith ann. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aodhre agus an Fharge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-Aodhre_agus_an_Fharge
+https://www.teanglann.ie/en/fgb/déan</t>
+        </is>
+      </c>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="inlineStr"/>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>déan ó</t>
+          <t>seas ar</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>déan</t>
+          <t>seas</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4514,30 +5243,41 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Déantar slad ar bhuíon de na Sherwood Foresters ag droichead Shráid an Mhóta agus iad ag iarraidh a mbealach a dhéanamh isteach go lár na cathrach ó Dhún Laoghaoire, áit ar thángadar i dtír. [UD_Irish-IDT 56, CC BY-SA 3.0]
-Déanfaidh an Roinn seo gach iarracht freagra a thabhairt ar d'iarratas AIE laistigh de mhí amháin ó dháta faighte an iarratais. [UD_Irish-IDT 2995, CC BY-SA 3.0]
-. @user733 @user263 bheinn ar son fórsa dlí a thabhairt do na treoirlínte. Trua nár rinneadh i bhfad ó shin sin. [UD_Irish-TwittIrish LTC_41, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/déan</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Tá sí ina suí ar fhiacail na mbeann suas le trí chéad troigh os cionn na farraige agus nádúr tarraingteach aici a mheallann corrdhuine ceanndána eachtrúil chun seasamh nó suí uirthi. [UD_Irish-IDT 883, CC BY-SA 3.0]
+@user27 @user241 @user1743 5'10, seansfaidh mé ar mo bharraicíní [UD_Irish-TwittIrish NTC_20963, CC BY-SA 4.0]
+Sheas sí ar an díon. = She stood on the roof. [Tatoeba 10926397, CC BY 2.0 FR]
+Sheas mé ar mhullach carraige ag féachaint i n‑áirde uaim sna spéarthaibh ar an éan cáinteach bhí ag dul ó léargus orm, agus ag innseacht dhí céard thug an bealach mé.... [Wikisource: An Crann Géagach/Cnoc mo Chroidhe, pre-standard, public domain]
+Ar sheasamh ar bharra an chalaith dhom do ghaibh Diarmaid aníos tar éis cliabh éisc a chur go dtí an t‑uisce dho. [Wikisource: An t-Oileánach/14, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/10926397
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Cnoc_mo_Chroidhe
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/14
+https://www.teanglann.ie/en/fgb/seas</t>
+        </is>
+      </c>
       <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="3" t="inlineStr"/>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4572,23 +5312,33 @@
       <c r="J75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>Agus a bhuí d'urraíocht ó ghnónna an cheantair, tugtar IRP26,000 amach chun cuidiú le costais chúrsaí do mhic léinn. [UD_Irish-IDT 2157, CC BY-SA 3.0]
 (3) Tuigfar gur ordú feidhmiúcháin de réir bhrí an Achta um Fheidhmiú Orduithe Cúirte, 1926, ordú chun seilbh d'fháil a tabharfar amach fén alt so. [UD_Irish-IDT 2601, CC BY-SA 3.0]
 Tabharfaimid amach an comóratas arís go luath.  Bí ag éisteacht!  @user235 @user423 @user288 [UD_Irish-TwittIrish LTC_670, CC BY-SA 4.0]
-Bhamar ag tabhairt mine buidhe amach andiu ar tri leath-phinginighe an pota: ta spirid na nGaodhal briste sios go mor: trosga. [UD_Irish-Cadhan cinlae-143, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr"/>
-      <c r="N75" s="3" t="inlineStr"/>
+Bhamar ag tabhairt mine buidhe amach andiu ar tri leath-phinginighe an pota: ta spirid na nGaodhal briste sios go mor: trosga. [UD_Irish-Cadhan cinlae-143, pre-standard, CC BY-SA 4.0]
+Agus tug Melchisedec Rígh Sálem amach arán agus fíon; agus dobé sagart an Dé roáird é. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus tug leis amach é, agus adubhairt; féuch annois air neamh, áirimh na réulta más éidir leachd a náireamh: agus adubhairt sé ris, as marso bhías do shíol. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="3" t="inlineStr"/>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4623,22 +5373,32 @@
       <c r="J76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>toiliú an Aire Airgeadais, féadfaidh an tAire, as airgead a sholáthróidh an tOireachtas, deontais a thabhairt d'údaráis phleanála i leith aon cheann nó gach ceann dá bhfeidhmeanna faoin Acht seo, lena n-áirítear deontais chun go nglanfar an caiteachas iomlán nó cuid den chaiteachas a bheidh tabhaithe acu (a) le linn cúnamh le daoine ar a seirbheáiltear fógra faoi alt 10(1) nó 11(2) agus oibreacha á ndéanamh acu de réir an fhógra, agus (b) le linn cúnamh le haon duine eile agus oibreacha á ndéanamh aige nó aici ar dhéanmhais chosanta de réir cibé coinníollacha a shonróidh údarás pleanála chun cúnamh den sórt sin a fháil. [UD_Irish-IDT 717, CC BY-SA 3.0]
 Tugann an sliocht gearr seo thíos as aiste ar 'Wildgoose Lodge' le T.G.F. Paterson, MRIA (1888-1971), iarchoimeádaí ar Iarsmalann Ard Mhacha, léas léargais dúinn ar staid eacnamaíoch agus sóisialta an chontae san am a bhfuilimid ag trácht air. [UD_Irish-IDT 2442, CC BY-SA 3.0]
-As 29 iarratas tugadh tacaíocht do sé ealaíontóir déag faoin scéim seo. [UD_Irish-IDT 4148, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="3" t="inlineStr"/>
+As 29 iarratas tugadh tacaíocht do sé ealaíontóir déag faoin scéim seo. [UD_Irish-IDT 4148, CC BY-SA 3.0]
+Tug Alasdair a dhaoine as an gharrdha, an mhéid do bhí infheadhma dhíobh; gidheadh, do fhágaibh seacht bhfir dhéag do bhí buailte, istigh, dá dhaoinibh uaisle nár fhéad teacht amach tairis ar marbhadh díobh. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Agus do mharbhadur Hámor, agus Sechem a mhac le faóbhar an chloidhimh, agus tugadar Dínah as tigh Shechem, agus dochúadur amach. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="3" t="inlineStr"/>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4673,22 +5433,32 @@
       <c r="J77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>'Thit an tóin as mo mhála plaisteach agus thit na buidéil as leis. [UD_Irish-IDT 714, CC BY-SA 3.0]
 'Thit an tóin as mo mhála plaisteach agus thit na buidéil as leis. [UD_Irish-IDT 714, CC BY-SA 3.0]
-Agus faoi 1262, nuair a bhí an náisiún ag titim as a chéile, a bhuíochas do laige thuasluaite an Althing, d'iarr na taoisigh ar rí Hákon na hIorua a ladhar a chur sa scéal agus cosc a chur ar an ainriail. [UD_Irish-IDT 1991, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tit</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="3" t="inlineStr"/>
+Agus faoi 1262, nuair a bhí an náisiún ag titim as a chéile, a bhuíochas do laige thuasluaite an Althing, d'iarr na taoisigh ar rí Hákon na hIorua a ladhar a chur sa scéal agus cosc a chur ar an ainriail. [UD_Irish-IDT 1991, CC BY-SA 3.0]
+“Dar ndóigh níor báthadh aenne ’ca nuair a thuit an tón as an sean-árthach ortha nó cad a shábháil iad?” [Wikisource: An t-Oileánach/6, pre-standard, public domain]
+Corcán thuit anuas as an mbád uaim ó chianaibh, agus [Wikisource: Cnuasacht trágha/An Baile fá an bhFairrge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/6
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/An_Baile_f%C3%A1_an_bhFairrge
+https://www.teanglann.ie/en/fgb/tit</t>
+        </is>
+      </c>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4727,17 +5497,30 @@
       <c r="J78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Acht do thuiteadar isteach chum cainte le n-a [Wikisource: Cnuasacht trágha/An Baile fá an bhFairrge, pre-standard, public domain]
+Acht do thuiteadar isteach chum cainte le n-a [Wikisource: Cnuasacht trágha/Taidhbhreamh ar Airgead, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/tit_isteach_le#Irish
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/An_Baile_f%C3%A1_an_bhFairrge
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/Taidhbhreamh_ar_Airgead
 https://www.teanglann.ie/en/fgb/tit</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="3" t="inlineStr"/>
+      <c r="Q78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4772,23 +5555,33 @@
       <c r="J79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>Tabharfaidh mé ort titim i ngrá liom tar éis dúinn pósadh. [UD_Irish-IDT 659, CC BY-SA 3.0]
 Le Teitheadh na nIarlaí thit an tóin as an chóras Ghaelach agus fágadh na Gaeil gan cumhacht pholaitiúil ná eacnamaíoch. [UD_Irish-IDT 1192, CC BY-SA 3.0]
-Thit Peter i ngrá leis an cailín. = Peter fell in love with the girl. [Tatoeba 3120370, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
+Thit Peter i ngrá leis an cailín. = Peter fell in love with the girl. [Tatoeba 3120370, CC BY 2.0 FR]
+Dhá ualach sean-asail de mhóin níor thuit le Tomás bocht an lán san go raibh an saothar mór beartaithe aige le déanamh; agus do bhí an lá úd ar na chéad laetheannta riamh gur bhraitheas an saoghal ag teacht im’ choinnibh, mar ’seadh bhí lá liom agus cúig lá im’ choinnibh as san amach. [Wikisource: An t-Oileánach/10, pre-standard, public domain]
+Le borradh agus le tuitim agus le súghadh an tarraic insa pholl do bhí sé ag dul dian orainn é tharrac chun an droichid. [Wikisource: An t-Oileánach/12, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/3120370
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/10
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/12
 https://www.teanglann.ie/en/fgb/tit</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr"/>
-      <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="3" t="inlineStr"/>
+      <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4823,22 +5616,32 @@
       <c r="J80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Déantar ar an gcaoi sin den fhéar suaithinseach an paiste slán i lár na ndriseacha agus na bhfiailí inar luigh slán an 'abhlainn bheannaithe a thit uainn fadó', siombail na glaineachta agus na neamhurchóide agus an bhearna trína dtiocfar ar an mbeatha spioradálta atá ionann is ceilte agus plúchta ag na fiailí, ar mar a chéile iad agus an ghné aimrid de nádúr an duine. [UD_Irish-IDT 505, CC BY-SA 3.0]
 Is beag nár thit an píosa dealbhóireachta uathu, bhíodar sna trithí chomh mór sin. [UD_Irish-IDT 1315, CC BY-SA 3.0]
-@user241 @user1747 Thug duine anaithnid do phóilín ar an tsráid é. An-amhrasach go deo gur thit sé slán go talamh ó eitleán scriosta [UD_Irish-TwittIrish NTC_78, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tit</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="inlineStr"/>
-      <c r="N80" s="3" t="inlineStr"/>
+@user241 @user1747 Thug duine anaithnid do phóilín ar an tsráid é. An-amhrasach go deo gur thit sé slán go talamh ó eitleán scriosta [UD_Irish-TwittIrish NTC_78, CC BY-SA 4.0]
+Thuit an sgian ó n‑a láimh. [Wikisource: Deoraidheacht/10, pre-standard, public domain]
+Cár thuit sé uaim ní fheadar?” [Wikisource: Eachtradh Eibhlís i dTír na nIongantas/IV, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Deoraidheacht/10
+https://wikisource.org/wiki/Eachtradh_Eibhl%C3%ADs_i_dT%C3%ADr_na_nIongantas/IV
+https://www.teanglann.ie/en/fgb/tit</t>
+        </is>
+      </c>
       <c r="O80" s="3" t="inlineStr"/>
       <c r="P80" s="3" t="inlineStr"/>
+      <c r="Q80" s="3" t="inlineStr"/>
+      <c r="R80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4873,22 +5676,32 @@
       <c r="J81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Tógann sé amach biro dearg) MAIDHC: (Á stopadh. [UD_Irish-IDT 930, CC BY-SA 3.0]
 'Ansin thóg sé amach a uirlisí obráide agus leag ar a chóngar iad; agus ba é an rud deireanach a tharraing sé amach, staic chruinn adhmaid a bhí idir dhá orlach go leith agus trí ar tiús, agus timpeall trí throigh ar fad. [UD_Irish-IDT 1323, CC BY-SA 3.0]
-Nuair a thógtar probháide amach ar uacht duine, is cáipéis phoiblí an cháipéis sin ina dhiaidh sin, agus is féidir le héinne cóip a fháil ón Oifig Phrobháide nó ón gClárlann Phrobháide Dhúiche chuí. [UD_Irish-IDT 4479, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="3" t="inlineStr"/>
+Nuair a thógtar probháide amach ar uacht duine, is cáipéis phoiblí an cháipéis sin ina dhiaidh sin, agus is féidir le héinne cóip a fháil ón Oifig Phrobháide nó ón gClárlann Phrobháide Dhúiche chuí. [UD_Irish-IDT 4479, CC BY-SA 3.0]
+Tógadh amach as an mbád ar an dtalamh é agus d’éag gan mhoill. [Wikisource: An t-Oileánach/2, pre-standard, public domain]
+arsaigh an Rí, ag tógaint a leabhair amach as a [Wikisource: Eachtradh Eibhlís i dTír na nIongantas/XII, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/2
+https://wikisource.org/wiki/Eachtradh_Eibhl%C3%ADs_i_dT%C3%ADr_na_nIongantas/XII
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="3" t="inlineStr"/>
+      <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4923,23 +5736,33 @@
       <c r="J82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Ó a Rí na trua, tóg dínn an ghannchuid seo, Go mbeimis id shamhailt gach uair den Lá. [UD_Irish-IDT 501, CC BY-SA 3.0]
 'Ach thóg na leitreacha sin cian díom - na leitreacha a scríobh mé chomh maith leis na rudaí a scríobhadh chugam. [UD_Irish-IDT 962, CC BY-SA 3.0]
-Cad a thóg tú pictiúr de? = What did you take a picture of? [Tatoeba 10317089, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
+Cad a thóg tú pictiúr de? = What did you take a picture of? [Tatoeba 10317089, CC BY 2.0 FR]
+Mar tógann sé tuirse ’gus brón dínn [Wikisource: An t-Oileánach/15, pre-standard, public domain]
+Tógadh chúig cinn de thighthe nua insan Oileán. [Wikisource: An t-Oileánach/24, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10317089
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/15
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/24
 https://www.teanglann.ie/en/fgb/tóg</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="3" t="inlineStr"/>
       <c r="O82" s="3" t="inlineStr"/>
       <c r="P82" s="3" t="inlineStr"/>
+      <c r="Q82" s="3" t="inlineStr"/>
+      <c r="R82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4974,22 +5797,32 @@
       <c r="J83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Tógaimis an 'ceardaí' ina shampla ón scéal 'Ná lig sinn i gcathú'. [UD_Irish-IDT 1673, CC BY-SA 3.0]
 Ní raibh na tachráin leis le bheith ag déanamh iontais d'oiread sin rudaí is lena aird a thógáil óna bhuaireamh. [UD_Irish-IDT 2596, CC BY-SA 3.0]
-Ó 'chruinniú bunreachta' Thionól Parlaiminteach na hEorpa an 19 Márta 1958 in Strasbourg, thóg sé 21 bliain go dtí gur toghadh Parlaimint na hEorpa go díreach den chéad uair, rud a chur ar chumas na saoránach tionchar a imirt ar leibhéal na hEorpa. [UD_Irish-IDT 3084, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr"/>
-      <c r="N83" s="3" t="inlineStr"/>
+Ó 'chruinniú bunreachta' Thionól Parlaiminteach na hEorpa an 19 Márta 1958 in Strasbourg, thóg sé 21 bliain go dtí gur toghadh Parlaimint na hEorpa go díreach den chéad uair, rud a chur ar chumas na saoránach tionchar a imirt ar leibhéal na hEorpa. [UD_Irish-IDT 3084, CC BY-SA 3.0]
+Do liúghdar ar Iupiter an phiast do thógáilt uatha. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]
+Duine do bhlais é agus beirt nár thóg deoir uaim. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O83" s="3" t="inlineStr"/>
       <c r="P83" s="3" t="inlineStr"/>
+      <c r="Q83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5024,22 +5857,32 @@
       <c r="J84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Ní bhfuair sí de fhreagra uaithi ach í a fheiceáil ag éirí ón bhord. [UD_Irish-IDT 275, CC BY-SA 3.0]
 Ag éisteacht le meidhir na bhfuiseog idir aer agus uisce thaibhsigh do dhánta chugam thar thalamh eadrána na síoraíochta, líne ar líne, stadach, scáfar mar shaighdiúirí ó bhéal an áir agus bhain siad an gus asam lena gcuntas ar an uafás: as duibheagán dubh na dtrinsí, as dóchas daortha na n-óg, as ár agus anbhás, d'éirigh siad chugam as corrabhuais coinsiasa - mise nach raibh ariamh sa bhearna bhaoil, nach dtug ruathar marfach thar an mhullach isteach sa chreach, nár fhulaing i dtreascairt dhian na fola; nach bhfaca saighdiúirí óga mar bheadh sopóga ann, caite i gcuibhrinn mhéithe an áir, boladh bréan an bháis ag éirí ina phláigh ó bhláth feoite a n-óige; nach raibh ar maos i nglár is i gclábar bhlár an chatha, nár chaill mo mheabhair i bpléasc, nár mhothaigh an piléar mar bheach thapaidh the ag diúl mhil fhiáin m'óige. [UD_Irish-IDT 1582, CC BY-SA 3.0]
-Mar shampla, d'fhéadfadh leithcheal indíreach éirí ón gceangal idir cineálacha áirithe sochair le critéir mar stádas pósta nó clainne, agus nóisean an ceann teaghlaigh nó "an tsaothraí". [UD_Irish-IDT 4414, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/éirigh</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr"/>
-      <c r="N84" s="3" t="inlineStr"/>
+Mar shampla, d'fhéadfadh leithcheal indíreach éirí ón gceangal idir cineálacha áirithe sochair le critéir mar stádas pósta nó clainne, agus nóisean an ceann teaghlaigh nó "an tsaothraí". [UD_Irish-IDT 4414, CC BY-SA 3.0]
+Agus do éirigh Iácob súas ó Bheerséba, agus do iomchradar mic Israel a nathair Iácob, agus an aós óg, agus a mná, annsna carbuduibh chuir Pháraó dhá iomchur. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+D' éirigh Caoimhghín Ó Cearnaigh as an mhúinteoireacht sa [Wikisource: Caoimhghin Ó Cearnaigh/1, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/Caoimhghin_%C3%93_Cearnaigh/1
+https://www.teanglann.ie/en/fgb/éirigh</t>
+        </is>
+      </c>
       <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="3" t="inlineStr"/>
+      <c r="Q84" s="3" t="inlineStr"/>
+      <c r="R84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5074,36 +5917,46 @@
       <c r="J85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>RT @user283: 45 uaire a baineadh leabhair de mo chuid amach as leabharlanna sa 26 chontae i 2013. Ar a laghad tá i bhfad níos mó á gcea… [UD_Irish-TwittIrish LTC_1228, CC BY-SA 4.0]
-Baineadh sin amach as sna 1970í @user791 @user1133 @user1487 [UD_Irish-TwittIrish LTC_1232, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bain</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr"/>
-      <c r="N85" s="3" t="inlineStr"/>
+Baineadh sin amach as sna 1970í @user791 @user1133 @user1487 [UD_Irish-TwittIrish LTC_1232, CC BY-SA 4.0]
+Do bhain amach as an líon é agus do chuir an líon ar tinneall arís mar do bhí cheana. [Wikisource: An t-Oileánach/7, pre-standard, public domain]
+féin ’s a bhean amach as an g-cóiste, agus shuidh sé síos air [Wikisource: Le hAis na Teineadh/An Táiliúr agus na Trí Bheithigheach, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/7
+https://wikisource.org/wiki/Le_hAis_na_Teineadh/An_T%C3%A1ili%C3%BAr_agus_na_Tr%C3%AD_Bheithigheach
+https://www.teanglann.ie/en/fgb/bain</t>
+        </is>
+      </c>
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="3" t="inlineStr"/>
+      <c r="Q85" s="3" t="inlineStr"/>
+      <c r="R85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>bain ó</t>
+          <t>cuir isteach faoi</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>bain</t>
+          <t>cuir</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>isteach faoi</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5123,36 +5976,44 @@
       <c r="J86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>'Amaquatl,' arsa Xatlacan agus, ag baint a láimhe ó ghualainn Phóil, shiúil sé chuige. [UD_Irish-IDT 422, CC BY-SA 3.0]
-Comhdhéanta de speisialtóirí, tá sé mar aidhm ag an meitheal oibre seo na bealaí is éifeachtaí a fhiosrú chun na spriocanna náisiúnta agus idirnáisiúnta a bhaint amach sa Ghaeltacht ó thaobh fuinnimh inbhuanaithe agus inathnuaithe a chur chun cinn. [UD_Irish-IDT 4659, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bain</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr"/>
-      <c r="N86" s="3" t="inlineStr"/>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Níl aon táille iarratais iníoctha as iarratas ar fhaisnéis a chur isteach faoi na rialacháin AIE. [UD_Irish-IDT 3726, CC BY-SA 3.0]
+Cuireadh an clár seo isteach faoi INTERREG II nuair a socraíodh go mbeadh réigiúin a bhfuil teorainn mhuírí eatarthu in ann cúnamh airgeadais a lorg. [UD_Irish-IDT 4432, CC BY-SA 3.0]
+Chuireas isteach sa n-obair iad, fé mar a bhíodar oireamhnach chuige. [Wikisource: Mo Sgéal Féin/22, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Mo_Sg%C3%A9al_F%C3%A9in/22
+https://www.teanglann.ie/en/fgb/cuir</t>
+        </is>
+      </c>
       <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="3" t="inlineStr"/>
+      <c r="Q86" s="3" t="inlineStr"/>
+      <c r="R86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>cuir isteach faoi</t>
+          <t>déan amach ar</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>cuir</t>
+          <t>déan</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>isteach faoi</t>
+          <t>amach ar</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5172,36 +6033,46 @@
       <c r="J87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Níl aon táille iarratais iníoctha as iarratas ar fhaisnéis a chur isteach faoi na rialacháin AIE. [UD_Irish-IDT 3726, CC BY-SA 3.0]
-Cuireadh an clár seo isteach faoi INTERREG II nuair a socraíodh go mbeadh réigiúin a bhfuil teorainn mhuírí eatarthu in ann cúnamh airgeadais a lorg. [UD_Irish-IDT 4432, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cuir</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr"/>
-      <c r="N87" s="3" t="inlineStr"/>
+      <c r="K87" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Sa meathdhorchadas sin d'fhéadas an stáitse a dhéanamh amach ar éigean faoina shoilse fanna néoin. [UD_Irish-IDT 193, CC BY-SA 3.0]
+RT @user1015: Déanfar comóradh agus ceiliúradh ar Éirí Amach 1916 thar dhá lá i bParlaimint na hEorpa sa Bhruiséil an seachtain... h… [UD_Irish-TwittIrish NTC_167, CC BY-SA 4.0]
+Ansan dob áil le Bhénus a dhéanamh amach ar athruig aigne an chait fé mar athruig a gné. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+do dheineas beartú ar í bhriseadh amach mar do bhí sí ró-sheannda agus í neamh-thairbheach mar bhí sí agus as an bhfuadar a bhí fúm do chuireas romham a leath a bhriseadh insa mbliain sin agus an leath eile an bhliain do bhí chugham. [Wikisource: An t-Oileánach/18, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/18
+https://www.teanglann.ie/en/fgb/déan</t>
+        </is>
+      </c>
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="3" t="inlineStr"/>
+      <c r="Q87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>déan amach ar</t>
+          <t>fan faoi</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>déan</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>amach ar</t>
+          <t>faoi</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5221,36 +6092,44 @@
       <c r="J88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Sa meathdhorchadas sin d'fhéadas an stáitse a dhéanamh amach ar éigean faoina shoilse fanna néoin. [UD_Irish-IDT 193, CC BY-SA 3.0]
-RT @user1015: Déanfar comóradh agus ceiliúradh ar Éirí Amach 1916 thar dhá lá i bParlaimint na hEorpa sa Bhruiséil an seachtain... h… [UD_Irish-TwittIrish NTC_167, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/déan</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr"/>
-      <c r="N88" s="3" t="inlineStr"/>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>D'fhéadfaimis beirt toirc a fhiach san fhoraois, is istoíche d'fhanfaimis tirim faoi chaipíní sonais na nua-bheirithe. [UD_Irish-IDT 2126, CC BY-SA 3.0]
+Is iad na rialtais náisiúnta a ainmníonn na hAnaclanna bithsféir agus fanann siad faoi dhlínse ceannasach na stát ina bhfuil siad lonnaithe. [UD_Irish-IDT 3785, CC BY-SA 3.0]
+Ach fan go bhfaghadh sí féin fé n-a hiongain arís me . [Wikisource: Jimín Mháire Thaidhg/14, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Jim%C3%ADn_Mh%C3%A1ire_Thaidhg/14
+https://www.teanglann.ie/en/fgb/fan</t>
+        </is>
+      </c>
       <c r="O88" s="3" t="inlineStr"/>
       <c r="P88" s="3" t="inlineStr"/>
+      <c r="Q88" s="3" t="inlineStr"/>
+      <c r="R88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>fan faoi</t>
+          <t>fág as</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>fág</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5270,26 +6149,32 @@
       <c r="J89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>D'fhéadfaimis beirt toirc a fhiach san fhoraois, is istoíche d'fhanfaimis tirim faoi chaipíní sonais na nua-bheirithe. [UD_Irish-IDT 2126, CC BY-SA 3.0]
-Is iad na rialtais náisiúnta a ainmníonn na hAnaclanna bithsféir agus fanann siad faoi dhlínse ceannasach na stát ina bhfuil siad lonnaithe. [UD_Irish-IDT 3785, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fan</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr"/>
-      <c r="N89" s="3" t="inlineStr"/>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>(2) Féadfidh cigire gach clár atá á chimeád do réir an ailt seo do scrúdú aon uair le linn tráthanna oifige chun aon chríche eireos as an Acht so no as aon rialachán a déanfar fé no a eireos de bharr ceachtar acu agus, ar a iarraidh sin don chigire, beidh sé de dhualgas ar únaer chláruithe an áitreibh ina bhfuil an clár san á chimeád an clár san do thaisbeáint, chun go scrúdóidh an cigire sin é, agus fós gach billín, nóta consighneachta, admháil, agus scríbhinn eile (ar a n-áirítear cóipeanna dhíobh i gcás gan iad féin a bheith ar fáil) a iarrfidh an cigire sin go réasúnta chun féachaint an fíor aon iontráil áirithe sa chlár san no cad fé ndeár éinní áirithe d'fhágaint amach as. [UD_Irish-IDT 1375, CC BY-SA 3.0]
+'Et Ú-Ah - Paul McGrath - in Italia,' a dúirt an triú fear, agus é ag iarraidh a chinntiú nach bhfágfaí as an gcaint é. [UD_Irish-IDT 2516, CC BY-SA 3.0]</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.teanglann.ie/en/fgb/fág</t>
+        </is>
+      </c>
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>fág as</t>
+          <t>fág faoi</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5299,7 +6184,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>faoi</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5314,31 +6199,42 @@
         <v>2</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>(2) Féadfidh cigire gach clár atá á chimeád do réir an ailt seo do scrúdú aon uair le linn tráthanna oifige chun aon chríche eireos as an Acht so no as aon rialachán a déanfar fé no a eireos de bharr ceachtar acu agus, ar a iarraidh sin don chigire, beidh sé de dhualgas ar únaer chláruithe an áitreibh ina bhfuil an clár san á chimeád an clár san do thaisbeáint, chun go scrúdóidh an cigire sin é, agus fós gach billín, nóta consighneachta, admháil, agus scríbhinn eile (ar a n-áirítear cóipeanna dhíobh i gcás gan iad féin a bheith ar fáil) a iarrfidh an cigire sin go réasúnta chun féachaint an fíor aon iontráil áirithe sa chlár san no cad fé ndeár éinní áirithe d'fhágaint amach as. [UD_Irish-IDT 1375, CC BY-SA 3.0]
-'Et Ú-Ah - Paul McGrath - in Italia,' a dúirt an triú fear, agus é ag iarraidh a chinntiú nach bhfágfaí as an gcaint é. [UD_Irish-IDT 2516, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fág</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="inlineStr"/>
-      <c r="N90" s="3" t="inlineStr"/>
+      <c r="K90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Nuair a fhágtar cuid de na plaistigh faoi sholas díreach na gréine teipeann ar a gcuid solúbthachta agus is minic a scoilteann siad. [UD_Irish-IDT 532, CC BY-SA 3.0]
+Fágaimid faoin iasachtaí fásta é an t-ábhar léitheoireachta a roghnú dóibh féin; i gcás leanaí, is iad a dtuismitheoirí nó a gcaomhnóirí amháin atá freagrach as ábhar léitheoireachta a roghnú. [UD_Irish-IDT 3357, CC BY-SA 3.0]
+Anmann ceathrair ceart ro chinn, Dofhágaibh Dia fo dhílinn Fionntain, Fearón, Fors caomh cóir, Agus Andóid mac Eathóir. [UD_Irish-Cadhan forasfeasa-454, pre-standard, CC BY-SA 4.0]
+D’imthigh an dreóilín leis, a’ fágbháil an chairéire a’ smuaineadh fá n-a aimhleas agus fá ’n gcóir a chuir an dreóilín air, agus a’ machtnadh faoi mar ghlacfadh a mhaighistir leis ’nuair thiocfadh sé a bhaile. [Wikisource: Irisleabhar na Gaedhilge/Imleabhar 5/Uimhir 6, pre-standard, public domain]
+D’imthigh an dreóilín leis, a’ fágbháil an chairéire a’ smuaineadh fá n-a aimhleas agus fá ’n gcóir a chuir an dreóilín air, agus a’ machtnadh faoi mar ghlacfadh a mhaighistir leis ’nuair thiocfadh sé a bhaile. [Wikisource: Irisleabhar na Gaedhilge/Imleabhar 5/Uimhir 6/Bearna Dhiarmada, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Irisleabhar_na_Gaedhilge/Imleabhar_5/Uimhir_6
+https://wikisource.org/wiki/Irisleabhar_na_Gaedhilge/Imleabhar_5/Uimhir_6/Bearna_Dhiarmada
+https://www.teanglann.ie/en/fgb/fág</t>
+        </is>
+      </c>
       <c r="O90" s="3" t="inlineStr"/>
       <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr"/>
+      <c r="R90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>fág faoi</t>
+          <t>fág le</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5348,7 +6244,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5363,42 +6259,51 @@
         <v>2</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Nuair a fhágtar cuid de na plaistigh faoi sholas díreach na gréine teipeann ar a gcuid solúbthachta agus is minic a scoilteann siad. [UD_Irish-IDT 532, CC BY-SA 3.0]
-Fágaimid faoin iasachtaí fásta é an t-ábhar léitheoireachta a roghnú dóibh féin; i gcás leanaí, is iad a dtuismitheoirí nó a gcaomhnóirí amháin atá freagrach as ábhar léitheoireachta a roghnú. [UD_Irish-IDT 3357, CC BY-SA 3.0]
-Anmann ceathrair ceart ro chinn, Dofhágaibh Dia fo dhílinn Fionntain, Fearón, Fors caomh cóir, Agus Andóid mac Eathóir. [UD_Irish-Cadhan forasfeasa-454, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fág</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="inlineStr"/>
-      <c r="N91" s="3" t="inlineStr"/>
+      <c r="K91" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>D'fhág mé í le croí briste agus deora i mo shúile. [UD_Irish-IDT 744, CC BY-SA 3.0]
+Má tá galar intinne ar bith ort, tá sé tábhachtach go bhfágtar fianaise le d'uacht (mar shampla ó dhochtúir) a dhearbhaíonn go raibh tú ábalta go hintinneach nuair a rinne tú an uacht. [UD_Irish-IDT 3965, CC BY-SA 3.0]
+Do chuaidh Mac Cailín féin ’na luing agus do fhágaibh tighearna Achaidh na mBreac re haghaidh na hiorghaile, acht i bhfíor-thosach na maidne do cóirigheadh na catha i n-eagar agus i n-órdughadh Dia Domhnaigh Lá Fhéile Brighde an chéad lá d’earrach Anno Domini 1645. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Acht mé fhágáil annsin liom féin, i lár na coille craobhaighe, ag cur alluis mo cheithre cnámh ag iarraidh dá chrann toirteamhla a leagadh le sábh gan mhaith! [Wikisource: An Crann Géagach/Fleadh aoibhinn, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Fleadh_aoibhinn
+https://www.teanglann.ie/en/fgb/fág</t>
+        </is>
+      </c>
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr"/>
+      <c r="R91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>fág le</t>
+          <t>lig as</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>fág</t>
+          <t>lig</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5413,31 +6318,42 @@
         <v>2</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>D'fhág mé í le croí briste agus deora i mo shúile. [UD_Irish-IDT 744, CC BY-SA 3.0]
-Má tá galar intinne ar bith ort, tá sé tábhachtach go bhfágtar fianaise le d'uacht (mar shampla ó dhochtúir) a dhearbhaíonn go raibh tú ábalta go hintinneach nuair a rinne tú an uacht. [UD_Irish-IDT 3965, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/fág</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr"/>
-      <c r="N92" s="3" t="inlineStr"/>
+      <c r="K92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Sa deireadh, smaointigh sé gurbh é a b'fhearr a dtiocfadh leis a dhéanamh cupla béic chreathnaitheach a ligean as a tharraingeodh air bunadh an tí agus, nuair a d'fhosclófaí an doras, go dtiocfadh leis éaló amach sula bhfaighfí greim air. [UD_Irish-IDT 873, CC BY-SA 3.0]
+'Cá fhaid go ligfeadh madra glam aisti? [UD_Irish-IDT 2079, CC BY-SA 3.0]
+Uáidh sin suás dobadh mián lé Pilát a leigean fá sgáoil: achd do thógbhadar na Híudaidhe na gáirthe, agá rádh, má leigeann tú an fearso as, ní cara do Chesar thú. [UD_Irish-Cadhan eoin-862, pre-standard, CC BY-SA 4.0]
+Níor leigeadh a thuille cainte as, d’ éirig a leithéid sin d’ uail gháirídhe mór thímpal an leasa. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+Is beag nár leig sí sgread aisti an dara huair, acht ní dhearna acht í féin do bhrúghadh níos goire do’n bhalla. [Wikisource: An Mháthair agus Sgéalta Eile/Na Bóithre, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/Na_B%C3%B3ithre
+https://www.teanglann.ie/en/fgb/lig</t>
+        </is>
+      </c>
       <c r="O92" s="3" t="inlineStr"/>
       <c r="P92" s="3" t="inlineStr"/>
+      <c r="Q92" s="3" t="inlineStr"/>
+      <c r="R92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>lig as</t>
+          <t>lig le</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5447,7 +6363,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5462,42 +6378,51 @@
         <v>2</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Sa deireadh, smaointigh sé gurbh é a b'fhearr a dtiocfadh leis a dhéanamh cupla béic chreathnaitheach a ligean as a tharraingeodh air bunadh an tí agus, nuair a d'fhosclófaí an doras, go dtiocfadh leis éaló amach sula bhfaighfí greim air. [UD_Irish-IDT 873, CC BY-SA 3.0]
-'Cá fhaid go ligfeadh madra glam aisti? [UD_Irish-IDT 2079, CC BY-SA 3.0]
-Uáidh sin suás dobadh mián lé Pilát a leigean fá sgáoil: achd do thógbhadar na Híudaidhe na gáirthe, agá rádh, má leigeann tú an fearso as, ní cara do Chesar thú. [UD_Irish-Cadhan eoin-862, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/lig</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="inlineStr"/>
-      <c r="N93" s="3" t="inlineStr"/>
+      <c r="K93" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Ach anois agus arís ligeadh sé le fadhb a d'fhéadfaí a shamhlú. [UD_Irish-IDT 1470, CC BY-SA 3.0]
+Tógaimis beirt Phrotastúnach eile a bhí báúil i gceart leis an Chonradh agus a ligeadh síos siar leo féin nuair a tháinig an crú ar an tairne - an Canónach James Owen Hannay agus Seosamh Laoide. [UD_Irish-IDT 2335, CC BY-SA 3.0]
+Is fada an réim a léig mé léi ó inné 'dtí inniu, [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]
+do leigint leigean amach leis an taoide arís agus [Wikisource: Cnuasacht trágha/An Fear do ḃí ag Tráighteóireacht, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/An_Fear_do_%E1%B8%83%C3%AD_ag_Tr%C3%A1ighte%C3%B3ireacht
+https://www.teanglann.ie/en/fgb/lig</t>
+        </is>
+      </c>
       <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="3" t="inlineStr"/>
+      <c r="R93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>lig le</t>
+          <t>tabhair isteach ar</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>lig</t>
+          <t>tabhair</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>isteach ar</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5517,36 +6442,46 @@
       <c r="J94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Ach anois agus arís ligeadh sé le fadhb a d'fhéadfaí a shamhlú. [UD_Irish-IDT 1470, CC BY-SA 3.0]
-Tógaimis beirt Phrotastúnach eile a bhí báúil i gceart leis an Chonradh agus a ligeadh síos siar leo féin nuair a tháinig an crú ar an tairne - an Canónach James Owen Hannay agus Seosamh Laoide. [UD_Irish-IDT 2335, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/lig</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr"/>
-      <c r="N94" s="3" t="inlineStr"/>
+      <c r="K94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Gan dabht chun iad a chur ar an sráid, bheadh orthu iad a thabhairt isteach sa chathair ar dtúis. [UD_Irish-IDT 794, CC BY-SA 3.0]
+Seans gur thug sirtheoirí ar thóir an mhiotail an ealaín isteach leo ó thuaisceart na Spáinne agus ón bPortaingéil. [UD_Irish-IDT 2191, CC BY-SA 3.0]
+“Tugtar isteach í,” ar seisean. [Wikisource: Deoraidheacht/14, pre-standard, public domain]
+“Léan air, an rudín súigh!” ar sise, “b’olc an díol air é thabhairt isteach ar do theinteán. [Wikisource: Jimín Mháire Thaidhg/7, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Deoraidheacht/14
+https://wikisource.org/wiki/Jim%C3%ADn_Mh%C3%A1ire_Thaidhg/7
+https://www.teanglann.ie/en/fgb/tabhair</t>
+        </is>
+      </c>
       <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="3" t="inlineStr"/>
+      <c r="Q94" s="3" t="inlineStr"/>
+      <c r="R94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>tabhair isteach ar</t>
+          <t>tit isteach</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>tabhair</t>
+          <t>tit</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>isteach ar</t>
+          <t>isteach</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5566,36 +6501,46 @@
       <c r="J95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Gan dabht chun iad a chur ar an sráid, bheadh orthu iad a thabhairt isteach sa chathair ar dtúis. [UD_Irish-IDT 794, CC BY-SA 3.0]
-Seans gur thug sirtheoirí ar thóir an mhiotail an ealaín isteach leo ó thuaisceart na Spáinne agus ón bPortaingéil. [UD_Irish-IDT 2191, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tabhair</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr"/>
-      <c r="N95" s="3" t="inlineStr"/>
+      <c r="K95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>) Lean gach duine eile é ar ball cé gur bheag nár thit an Prionsa Eoin isteach san abhainn arís. [UD_Irish-IDT 812, CC BY-SA 3.0]
+Rith cuid ach síos na taobhshráideanna, agus thiteadar isteach sna poill ansin freisin. [UD_Irish-IDT 2891, CC BY-SA 3.0]
+“Tuitim isteach i Lochán na Luachra a rinne sí,” adeir an Dearg-Daol. [Wikisource: An Mháthair agus Sgéalta Eile/An Dearg-Daol, pre-standard, public domain]
+Acht do thuiteadar isteach chum cainte le n-a [Wikisource: Cnuasacht trágha/An Baile fá an bhFairrge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/An_Dearg-Daol
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/An_Baile_f%C3%A1_an_bhFairrge
+https://www.teanglann.ie/en/fgb/tit</t>
+        </is>
+      </c>
       <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="3" t="inlineStr"/>
+      <c r="Q95" s="3" t="inlineStr"/>
+      <c r="R95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>tit isteach</t>
+          <t>tóg as</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>tit</t>
+          <t>tóg</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>isteach</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5615,26 +6560,36 @@
       <c r="J96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>) Lean gach duine eile é ar ball cé gur bheag nár thit an Prionsa Eoin isteach san abhainn arís. [UD_Irish-IDT 812, CC BY-SA 3.0]
-Rith cuid ach síos na taobhshráideanna, agus thiteadar isteach sna poill ansin freisin. [UD_Irish-IDT 2891, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tit</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr"/>
-      <c r="N96" s="3" t="inlineStr"/>
+      <c r="K96" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Tógann sé na heochracha as. [UD_Irish-IDT 197, CC BY-SA 3.0]
+@user1747 Mise á leamh an shite seo: TÓG A HAINM DÍLIS AS DO RANCID BÉAL https://t.co/zBFBFPHo5I [UD_Irish-TwittIrish NTC_276, CC BY-SA 4.0]
+Annsin do ghabhadar Midianuigh ré na ttaóbh, ceannuighe; agus do thairngeadar agus do thógbhadar súas Ióseph as an bpoll, agus do reacadur Ióseph ris na hIsmaeliteachuibh ar fhichid píosa airgid, agus rugadarsin Ióseph don Négipt. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Tógadh amach as an mbád ar an dtalamh é agus d’éag gan mhoill. [Wikisource: An t-Oileánach/2, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/2
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O96" s="3" t="inlineStr"/>
       <c r="P96" s="3" t="inlineStr"/>
+      <c r="Q96" s="3" t="inlineStr"/>
+      <c r="R96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>tóg as</t>
+          <t>tóg isteach</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5644,7 +6599,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>isteach</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5664,36 +6619,46 @@
       <c r="J97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Tógann sé na heochracha as. [UD_Irish-IDT 197, CC BY-SA 3.0]
-@user1747 Mise á leamh an shite seo: TÓG A HAINM DÍLIS AS DO RANCID BÉAL https://t.co/zBFBFPHo5I [UD_Irish-TwittIrish NTC_276, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr"/>
-      <c r="N97" s="3" t="inlineStr"/>
+      <c r="K97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Ach buiséad Uí Eachaidh i bhfeidhm roinnt éigin blianta sul má tógadh isteach é, seans maith go mbeadh aithne níos fearr agam ar an gcigire anaithnid úd. [UD_Irish-IDT 2037, CC BY-SA 3.0]
+Thóg sé isteach an mhóin. [UD_Irish-IDT 2478, CC BY-SA 3.0]
+Thóg na fir-ghárda isteach ’na mbád féin gan mhoill iad agus is iad a bhí go sásta. [Wikisource: An t-Oileánach/1, pre-standard, public domain]
+“Seo, tóg é sin leat isteach ’on tseomra san. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/1
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://www.teanglann.ie/en/fgb/tóg</t>
+        </is>
+      </c>
       <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="inlineStr"/>
+      <c r="Q97" s="3" t="inlineStr"/>
+      <c r="R97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>tóg isteach</t>
+          <t>éirigh ar</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>tóg</t>
+          <t>éirigh</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>isteach</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5708,31 +6673,42 @@
         <v>2</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Ach buiséad Uí Eachaidh i bhfeidhm roinnt éigin blianta sul má tógadh isteach é, seans maith go mbeadh aithne níos fearr agam ar an gcigire anaithnid úd. [UD_Irish-IDT 2037, CC BY-SA 3.0]
-Thóg sé isteach an mhóin. [UD_Irish-IDT 2478, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/tóg</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr"/>
-      <c r="N98" s="3" t="inlineStr"/>
+      <c r="K98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>(8) Ar chothromdháta an lae bunaithe agus, dá éis sin, ar gach cothromdháta den lá bunaithe, éireoidh beirt chomhalta den Bhord (seachas an cathaoirleach agus an príomhoifigeach feidhmiúcháin) as oifig. [UD_Irish-IDT 1187, CC BY-SA 3.0]
+Bhí máthair Jamesie ag éirí ar mire gur tubaist éigin trom a bhain dóibh. [UD_Irish-IDT 1349, CC BY-SA 3.0]
+Nir eirigh neach thiar no thoir ar druim do rotha a shaoghail nach é [a] dheireadh iar gach sódh a chur faoi an roth fa dhubrón. [UD_Irish-Cadhan bardic_1387-8, pre-standard, CC BY-SA 4.0]
+“Éiríg,” ar seisean, ”agus téanam go bhfeiceam an rígh!” [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]
+Agus do éirigh Abraham go moch ar maidhin go nuige anáit ar sheas sé as choinne an tighearna. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/éirigh</t>
+        </is>
+      </c>
       <c r="O98" s="3" t="inlineStr"/>
       <c r="P98" s="3" t="inlineStr"/>
+      <c r="Q98" s="3" t="inlineStr"/>
+      <c r="R98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>éirigh ar</t>
+          <t>éirigh do</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5742,7 +6718,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5757,246 +6733,300 @@
         <v>2</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>(8) Ar chothromdháta an lae bunaithe agus, dá éis sin, ar gach cothromdháta den lá bunaithe, éireoidh beirt chomhalta den Bhord (seachas an cathaoirleach agus an príomhoifigeach feidhmiúcháin) as oifig. [UD_Irish-IDT 1187, CC BY-SA 3.0]
-Bhí máthair Jamesie ag éirí ar mire gur tubaist éigin trom a bhain dóibh. [UD_Irish-IDT 1349, CC BY-SA 3.0]
-Nir eirigh neach thiar no thoir ar druim do rotha a shaoghail nach é [a] dheireadh iar gach sódh a chur faoi an roth fa dhubrón. [UD_Irish-Cadhan bardic_1387-8, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/éirigh</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="inlineStr"/>
-      <c r="N99" s="3" t="inlineStr"/>
+      <c r="K99" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Breacfaidh mé síos go beacht mar a d'éirigh dom. [UD_Irish-IDT 241, CC BY-SA 3.0]
+Bhí fearg orm nár bacadh liom - nár fiafraíodh scéala díom - nár cuireadh ceist orm i dtaobh na timpiste a d'éirigh dom; ach nuair a dhearc ógbhean dheas a bhí ag dul thart go truamhéileach orm, agus í ar tí labharta, tháinig cuthach orm. [UD_Irish-IDT 1669, CC BY-SA 3.0]
+Cúig cubhaid déug do éirigh an tuisge súas agus do folchadh na sléibhte. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus anuáir do éirigh an mhaidion, annsin do bhrosduighedar na h aingil Lot ag rádh: éirigh glac do bhean agus do dhías inghean atá ann so, deagla go ttuitfeá a ccionta na caithreach. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/éirigh</t>
+        </is>
+      </c>
       <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="3" t="inlineStr"/>
+      <c r="Q99" s="3" t="inlineStr"/>
+      <c r="R99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>éirigh do</t>
+          <t>bí ar</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>éirigh</t>
+          <t>bí</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>new compound</t>
+          <t>new verb</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>must, have to | to be owed by</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="n">
-        <v>2</v>
+        <v>592</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Breacfaidh mé síos go beacht mar a d'éirigh dom. [UD_Irish-IDT 241, CC BY-SA 3.0]
-Bhí fearg orm nár bacadh liom - nár fiafraíodh scéala díom - nár cuireadh ceist orm i dtaobh na timpiste a d'éirigh dom; ach nuair a dhearc ógbhean dheas a bhí ag dul thart go truamhéileach orm, agus í ar tí labharta, tháinig cuthach orm. [UD_Irish-IDT 1669, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/éirigh</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr"/>
-      <c r="N100" s="3" t="inlineStr"/>
-      <c r="O100" s="3" t="inlineStr"/>
-      <c r="P100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>bí ar</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>bí</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>must, have to | to be owed by</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J101" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K100" s="2" t="n">
+        <v>4852</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>Ach beo bocht a bheadh ar an té nach mbeadh aige ach preátaí tura. [UD_Irish-IDT 460, CC BY-SA 3.0]
 'Ar ndóigh, sé'n t-ainm atá baistithe ar an gcuid is faide thiar dhe, ná an Aill. [UD_Irish-IDT 464, CC BY-SA 3.0]
 Muintir na Fraince bhí an-tóir go deo acu orthu bhí sé ráite, ach níorbh aon iontas é sin, bhí an-tóir ag na Francaigh ar chuile shórt, ar loscáin lathaí, ar phortáin agus ar ghailléisc bhréana. [UD_Irish-IDT 468, CC BY-SA 3.0]
 An bhfuil orm déanamh deifir? = Must I hurry? [Tatoeba 3786843, CC BY 2.0 FR]
 An bhfuil tuirse ort? = Are you tired? [Tatoeba 625716, CC BY 2.0 FR]
-Ar tteacht abhaile dhom um cronughadh lae, bhí cuma feargach ar an speir, le neulta dubha dearga ruadha agus forruadha, le h-anfa aniar. [UD_Irish-Cadhan cinlae-302, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
+Ar tteacht abhaile dhom um cronughadh lae, bhí cuma feargach ar an speir, le neulta dubha dearga ruadha agus forruadha, le h-anfa aniar. [UD_Irish-Cadhan cinlae-302, pre-standard, CC BY-SA 4.0]
+A Róisín ná bíodh brón ort fé'r éirigh dhuit: [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]
+'S bhí ceol téad ar gach taobh díom is mo Róisín Dubh. [Wikisource: Róisín Dubh, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/bí_ar#Irish
 https://tatoeba.org/en/sentences/show/3786843
 https://tatoeba.org/en/sentences/show/625716
+https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
+https://wikisource.org/wiki/R%C3%B3is%C3%ADn_Dubh
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M101" s="3" t="inlineStr"/>
-      <c r="N101" s="3" t="inlineStr"/>
-      <c r="O101" s="3" t="inlineStr"/>
-      <c r="P101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="O100" s="3" t="inlineStr"/>
+      <c r="P100" s="3" t="inlineStr"/>
+      <c r="Q100" s="3" t="inlineStr"/>
+      <c r="R100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>bí le</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>bí</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>le</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="n">
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="I102" s="2" t="n">
+      <c r="I101" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J101" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K101" s="2" t="n">
+        <v>1921</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>Ní hé nach bhfuil Cois Fharraige chomh spéisiúil leis an leath thiar de Chonamara Theas, ach tá an saol ró-ghearr! [UD_Irish-IDT 481, CC BY-SA 3.0]
 Le seachtain anuas tá Comhchomhairle ar bun ag Anglacánaigh as gach taobh den domhan: tá breis agus ceithre scór daoine, idir chléir agus tuath, páirteach sa ghnó, agus tá seisear as Eaglais na hÉireann ann. [UD_Irish-IDT 495, CC BY-SA 3.0]
 Ní raibh aon ghá le cuireadh. [UD_Irish-IDT 504, CC BY-SA 3.0]
 An bhfuil tú ag bualadh le duine éigin anseo? = Are you meeting someone here? [Tatoeba 752751, CC BY 2.0 FR]
 An bhfuil tú réidh le himeacht? = Are you ready to go? [Tatoeba 12274856, CC BY 2.0 FR]
-Ach d'fhoghluim Buck go furas, agus leis an teagasg a thug a dhá chomrádaidhe agus François dó bhí sé ag éirghe eólach gach aon bhomaite. [UD_Irish-Cadhan scairt-243, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
+Ach d'fhoghluim Buck go furas, agus leis an teagasg a thug a dhá chomrádaidhe agus François dó bhí sé ag éirghe eólach gach aon bhomaite. [UD_Irish-Cadhan scairt-243, pre-standard, CC BY-SA 4.0]
+Tá bean ab fhearr liom nó cath is céad dhíobh nach bhfagham go deo [Wikisource: Mná na hÉireann, Ulster-leaning, pre-standard, public domain]
+Tá bean is b'fhearr leí ag cruinniú déirce nó cráite re cró [Wikisource: Mná na hÉireann, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/752751
 https://tatoeba.org/en/sentences/show/12274856
+https://wikisource.org/wiki/Mn%C3%A1_na_h%C3%89ireann
+https://wikisource.org/wiki/Mn%C3%A1_na_h%C3%89ireann
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M102" s="3" t="inlineStr"/>
-      <c r="N102" s="3" t="inlineStr"/>
-      <c r="O102" s="3" t="inlineStr"/>
-      <c r="P102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="O101" s="3" t="inlineStr"/>
+      <c r="P101" s="3" t="inlineStr"/>
+      <c r="Q101" s="3" t="inlineStr"/>
+      <c r="R101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>bí do</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>bí</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>do</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="n">
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="I102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J102" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K102" s="2" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Liobairt mhaith de'n teangaidh a bhí in áithrid dó ag a' siopadóir, a's sé a dtug sé d'áirleacan dó, noiméad a' chloig le crapadh leis as a siopa, nó go gcuirfeadh sé na póilíos in a dhiaidh. [UD_Irish-IDT 561, CC BY-SA 3.0]
 Dráma an-dána ar fad a bhí ann don am úd - phléigh sí ann ceisteanna an-chonspóideacha mar mháithreacha neamhphósta agus ginmhilleadh. [UD_Irish-IDT 594, CC BY-SA 3.0]
 Bhí sé an-chóngarach don bhaile agus bhí mé ábalta dul ann go minic. [UD_Irish-IDT 597, CC BY-SA 3.0]
 An bhfuil tú réidh don turas? = Are you ready for the trip? [Tatoeba 2715249, CC BY 2.0 FR]
 An bhfuil tú réidh don dinnéar? = Are you ready for dinner? [Tatoeba 2715255, CC BY 2.0 FR]
-An treas easbaidh, do bhí sé uaillmhianach, agus d'á réir sin, do bhí súil aige le meudughadh d'fhaghbháil ó'n droing lér' gríosadh é le scríobhadh go holc ar Éirinn: agus fós, re linn bheith 'na shagart 'na dhiaidh sin dó, do gheall gairm tar ais do dhéanamh ar mhórán do na neithibh maslaightheacha do scríobh ar Éirinn, agus dochluinim go bhfuil sé i gclódh anois re n-a thaisbéanadh i n-Éirinn. [UD_Irish-Cadhan forasfeasa-97, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
+An treas easbaidh, do bhí sé uaillmhianach, agus d'á réir sin, do bhí súil aige le meudughadh d'fhaghbháil ó'n droing lér' gríosadh é le scríobhadh go holc ar Éirinn: agus fós, re linn bheith 'na shagart 'na dhiaidh sin dó, do gheall gairm tar ais do dhéanamh ar mhórán do na neithibh maslaightheacha do scríobh ar Éirinn, agus dochluinim go bhfuil sé i gclódh anois re n-a thaisbéanadh i n-Éirinn. [UD_Irish-Cadhan forasfeasa-97, pre-standard, CC BY-SA 4.0]
+Tú bheith i do luí ar leaca lom’, [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]
+Is gurbh iomaí lá a chluininn do ghrág [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/2715249
 https://tatoeba.org/en/sentences/show/2715255
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M103" s="3" t="inlineStr"/>
-      <c r="N103" s="3" t="inlineStr"/>
+      <c r="O102" s="3" t="inlineStr"/>
+      <c r="P102" s="3" t="inlineStr"/>
+      <c r="Q102" s="3" t="inlineStr"/>
+      <c r="R102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>bí faoi</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>bí</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>faoi</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>) 'Tá mé buartha fán trioblóid uilig ach tabhair maithiúnas domh... 'Tá mé cinnte gur baineadh scanradh asat,' arsa Peadar. [UD_Irish-IDT 456, CC BY-SA 3.0]
+Bheadh an scoil éisc faoi lán siúil faoin uisce agus an t-iascaire ag iarraidh é a locadh chun líon trom a chaitheamh timpeall air. [UD_Irish-IDT 534, CC BY-SA 3.0]
+Ar dtús seo liosta iomlán de na litreacha: Is saothar lae eile é fáil amach cé mhéad de na litreacha seo a scríobh Séamus Ó Grianna agus cé eile a bhí ag folach faoi ainmneacha cleite. [UD_Irish-IDT 656, CC BY-SA 3.0]
+Níl aon eolas agam faoin mBéarla. = I have zero knowledge of English. [Tatoeba 3944933, CC BY 2.0 FR]
+Níl Tom á iarraidh sin faoi láthair. = Tom doesn't want that right now. [Tatoeba 6319276, CC BY 2.0 FR]
+Tárla long mhór dóibh ann agus do ghabhadar í fá n-a lucht do shíol [Wikisource: Alasdair Mac Colla/Cóir Fáilte re fear do sgéil, pre-standard, public domain]
+Atá fé gheall ag Éirinn, [Wikisource: Amhrán na bhFiann, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/3944933
+https://tatoeba.org/en/sentences/show/6319276
+https://wikisource.org/wiki/Alasdair_Mac_Colla/C%C3%B3ir_F%C3%A1ilte_re_fear_do_sg%C3%A9il
+https://wikisource.org/wiki/Amhr%C3%A1n_na_bhFiann
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="3" t="inlineStr"/>
+      <c r="Q103" s="3" t="inlineStr"/>
+      <c r="R103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6023,40 +7053,50 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I104" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>726</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
         <is>
           <t>Ag tús na hócáide, bhí siamsa bríomhar ó cheoltóirí óga Scoil Francis McPeake agus chan na páistí ón dara bliain i mbunscoil Mhic Reachtain amhrán breá faoi chur chun cinn na Gaeilge. [UD_Irish-IDT 515, CC BY-SA 3.0]
-Ó thaobh na polaitíochta de, beidh an scéal seo chun tairbhe Shinn Fein, atá tar éis diúltú a bheith ar an bhord póilíneachta úr. [UD_Irish-IDT 723, CC BY-SA 3.0]
 'Tá fuipeanna dhá n-úsáid ó thús an chine dhaonna! [UD_Irish-IDT 755, CC BY-SA 3.0]
+Tá an fhoireann taighde roinnte ar cheithre rannóg ó 1977 i leith, nó cúig cinn má chuirtear an tSeirbhís Leabharlainne agus Eolaslainne san áireamh. [UD_Irish-IDT 771, CC BY-SA 3.0]
 Bhí rialtas nua uathu chun bheith i gceannas ar an ainriail. = They needed a new government to control the anarchy. [Tatoeba 10925711, CC BY 2.0 FR]
 Dúirt Tom go raibh comhluadar uaidh. = Tom said he wanted some company. [Tatoeba 6319282, CC BY 2.0 FR]
-Óir ní fhuil stáraidhe ó shoin i leith d'á scríobhann uirre nach ag iarraidh lochta agus toibhéime do thabhairt do Shean-Ghallaibh agus do Ghaedealaibh bhíd. [UD_Irish-Cadhan forasfeasa-5, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
+Óir ní fhuil stáraidhe ó shoin i leith d'á scríobhann uirre nach ag iarraidh lochta agus toibhéime do thabhairt do Shean-Ghallaibh agus do Ghaedealaibh bhíd. [UD_Irish-Cadhan forasfeasa-5, pre-standard, CC BY-SA 4.0]
+Is tá bean in Éirinn is ba bhinne léithe mo ráfla ceoil [Wikisource: Mná na hÉireann, Ulster-leaning, pre-standard, public domain]
+Nuair bhuailidís na luchaig a bhí sa chómharsanacht uime ó am go h-am agus nuair fhiafraighdís dé cad é an saghas áite an baile mór ní fhéadaidís a fhághail as choídhche acht—“Ní cathair mar a thuairisg é!” [Wikisource: Aesop a tháinig go h-Éirinn/An Fhiolar agus an Mada Ruadh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10925711
 https://tatoeba.org/en/sentences/show/6319282
+https://wikisource.org/wiki/Mn%C3%A1_na_h%C3%89ireann
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Fhiolar_agus_an_Mada_Ruadh
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M104" s="3" t="inlineStr"/>
-      <c r="N104" s="3" t="inlineStr"/>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="3" t="inlineStr"/>
+      <c r="Q104" s="3" t="inlineStr"/>
+      <c r="R104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>bí faoi</t>
+          <t>bí de</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6066,7 +7106,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>de</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6078,39 +7118,48 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>) 'Tá mé buartha fán trioblóid uilig ach tabhair maithiúnas domh... 'Tá mé cinnte gur baineadh scanradh asat,' arsa Peadar. [UD_Irish-IDT 456, CC BY-SA 3.0]
-Bheadh an scoil éisc faoi lán siúil faoin uisce agus an t-iascaire ag iarraidh é a locadh chun líon trom a chaitheamh timpeall air. [UD_Irish-IDT 534, CC BY-SA 3.0]
-Ar dtús seo liosta iomlán de na litreacha: Is saothar lae eile é fáil amach cé mhéad de na litreacha seo a scríobh Séamus Ó Grianna agus cé eile a bhí ag folach faoi ainmneacha cleite. [UD_Irish-IDT 656, CC BY-SA 3.0]
-Níl aon eolas agam faoin mBéarla. = I have zero knowledge of English. [Tatoeba 3944933, CC BY 2.0 FR]
-Níl Tom á iarraidh sin faoi láthair. = Tom doesn't want that right now. [Tatoeba 6319276, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/3944933
-https://tatoeba.org/en/sentences/show/6319276
+        <v>1</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Rinne Íosa iarracht ar shólás a thabhairt dóibh: 'Chuir mé amach sa saol sibh gan sparán, ná mála, ná bróga - an raibh aon rud de dhíth oraibh? [UD_Irish-IDT 599, CC BY-SA 3.0]
+Níl de dhíth ach aon fhocal amháin, sin a bhfuil. [UD_Irish-IDT 731, CC BY-SA 3.0]
+Tá Seáinín ina aonar i gclós mhuintir Bhraonáin - níl de chompánach aige ach cearc mhór mhuintir Bhraonáin. [UD_Irish-IDT 880, CC BY-SA 3.0]
+Táim i mo bhall den club leadóige. = I'm in the tennis club. [Tatoeba 748598, CC BY 2.0 FR]
+Ní raibh truaigh ar bith agam dhi. [UD_Irish-Cadhan deoraidheacht-3128, pre-standard, CC BY-SA 4.0]
+Ach mo bhonnán buí, bhí lán de chroí, [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]
+Is tá bean a dhéanfadh de dh'olainn gréas is thairnfeadh an bhró [Wikisource: Mná na hÉireann, Ulster-leaning, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/748598
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
+https://wikisource.org/wiki/Mn%C3%A1_na_h%C3%89ireann
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M105" s="3" t="inlineStr"/>
-      <c r="N105" s="3" t="inlineStr"/>
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="3" t="inlineStr"/>
+      <c r="Q105" s="3" t="inlineStr"/>
+      <c r="R105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>bí de</t>
+          <t>bí as</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6120,7 +7169,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6132,351 +7181,354 @@
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Rinne Íosa iarracht ar shólás a thabhairt dóibh: 'Chuir mé amach sa saol sibh gan sparán, ná mála, ná bróga - an raibh aon rud de dhíth oraibh? [UD_Irish-IDT 599, CC BY-SA 3.0]
-Níl de dhíth ach aon fhocal amháin, sin a bhfuil. [UD_Irish-IDT 731, CC BY-SA 3.0]
-(ii) I gcás na bliana 1999-2000 nó aon bhliana measúnachta dá éis, féadfaidh an tArd-Bhailitheoir, in aon chás áirithe, d'fhonn íoc réamhchánach de réir an fho-ailt seo a éascú, aontú líon na dtráthchodanna comhionanna míosúla a bheidh le bailiú i rith bliana a athrú nó, tar éis tráthchuid amháin nó níos mó a bheith íoctha sa bhliain sin, aontú le méadú nó laghdú ar an méid a bheidh le bailiú i dtráthchodanna dá éis sin sa bhliain sin; ach ní dhéileálfar le duine inmhuirearaithe mar dhuine a mbeidh méid réamhchánach íoctha aige nó aici de réir an fho-ailt seo mura rud é - (I) nach lú ná 10 líon na dtráthchodanna míosúla a bheidh íoctha ag an duine sin sa bhliain mheasúnachta, agus (II) go ndéantar méid nach lú ná 70 faoin gcéad de mhéid na réamhchánach is iníoctha ag an duine sin don bhliain sin a íoc i dtráthchodanna ar nó roimh an 31ú lá de Nollaig sa bhliain sin. [UD_Irish-IDT 821, CC BY-SA 3.0]
-Táim i mo bhall den club leadóige. = I'm in the tennis club. [Tatoeba 748598, CC BY 2.0 FR]
-Ní raibh truaigh ar bith agam dhi. [UD_Irish-Cadhan deoraidheacht-3128, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/748598
-https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr"/>
-      <c r="N106" s="3" t="inlineStr"/>
-      <c r="O106" s="3" t="inlineStr"/>
-      <c r="P106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>bí as</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>bí</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K106" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>Le seachtain anuas tá Comhchomhairle ar bun ag Anglacánaigh as gach taobh den domhan: tá breis agus ceithre scór daoine, idir chléir agus tuath, páirteach sa ghnó, agus tá seisear as Eaglais na hÉireann ann. [UD_Irish-IDT 495, CC BY-SA 3.0]
 'Bhí alt as Foinse ar an dreapadóir Paul Pritchard ar pháipéar an Teastais Shóisearaigh gnáthleibhéal. [UD_Irish-IDT 580, CC BY-SA 3.0]
 Faoi mar a tharla, is oth liom go raibh triúr de na comhaltaí nach bhféadfainnse glacadh leis an dearcadh a bhí acu agus, sna cúinsí uile, ní raibh dul as agam ach iad a chur as oifig. [UD_Irish-IDT 787, CC BY-SA 3.0]
 Ceapaim go bhfuil mé líofa as Fraincis. = I think that I'm fluent in French. [Tatoeba 8050258, CC BY 2.0 FR]
-Níl an leabhar seo scríofa as Béarla. = This book is not written in English. [Tatoeba 3523048, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
+Níl an leabhar seo scríofa as Béarla. = This book is not written in English. [Tatoeba 3523048, CC BY 2.0 FR]
+Bhí gal as a shróin, agus bhí cúbhar geal le n-a chorán. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Ná bíodh ”deatach mór as droch theine” agat. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/8050258
 https://tatoeba.org/en/sentences/show/3523048
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M107" s="3" t="inlineStr"/>
-      <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr"/>
-      <c r="P107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="O106" s="3" t="inlineStr"/>
+      <c r="P106" s="3" t="inlineStr"/>
+      <c r="Q106" s="3" t="inlineStr"/>
+      <c r="R106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>abair le</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>abair</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>le</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>to tell (somebody something; somebody to do something)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="n">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="I108" s="2" t="n">
+      <c r="I107" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J107" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K107" s="2" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>Dúrt leis pé duine do raghadh á múscailt nách me féin é; nár bhe' liom a bhfeaca inné dhóibh, agus gan do bheith ag caitheamh an lae inniu ar an gcuma chéanna, agus go ndéanfaidís féin múscailt an uair ba mhaith leo féin é. [UD_Irish-IDT 490, CC BY-SA 3.0]
 Ó, a mhac go deo, a bhí mé a rá liom féin, mé sceanta chun báis i lár na hoíche i Meiriceá, mo cholainn is mo chloigeann caite gan ord ná eagar sa phuiteach, francaigh ag smúrthacht chugam mar a smúrfaidís ar chloigeann gé. [UD_Irish-IDT 516, CC BY-SA 3.0]
 'Dia dhuit, a Mhíchíl,' a deir Sándra leis, 'tá áthas orm bualadh leat. [UD_Irish-IDT 640, CC BY-SA 3.0]
 Cad é ba mhaith leat mé a rá leat? = What do you want me to tell you? [Tatoeba 6319306, CC BY 2.0 FR]
 Is féidir leat féin sin a rá le Tom. = You can say that to Tom yourself. [Tatoeba 2936214, CC BY 2.0 FR]
-Adubhairt Símón Peadar ris, a thighearna, ní hiád mó chosa amhaín, achd mo lámha agus mó cheann mar an gcédna. [UD_Irish-Cadhan eoin-633, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
+Adubhairt Símón Peadar ris, a thighearna, ní hiád mó chosa amhaín, achd mo lámha agus mó cheann mar an gcédna. [UD_Irish-Cadhan eoin-633, pre-standard, CC BY-SA 4.0]
+Ach dúirt mé léithi go dtug sí an bhréag, [Wikisource: An Bonnán Buí, Ulster-leaning, pre-standard, public domain]
+Dúbhairt an león leis an asal an tseilg do raint. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/abair_le#Irish
 https://tatoeba.org/en/sentences/show/6319306
 https://tatoeba.org/en/sentences/show/2936214
+https://wikisource.org/wiki/An_Bonn%C3%A1n_Bu%C3%AD
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
 https://www.teanglann.ie/en/fgb/abair</t>
         </is>
       </c>
-      <c r="M108" s="3" t="inlineStr"/>
-      <c r="N108" s="3" t="inlineStr"/>
-      <c r="O108" s="3" t="inlineStr"/>
-      <c r="P108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr"/>
+      <c r="Q107" s="3" t="inlineStr"/>
+      <c r="R107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>bí amach</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>bí</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>amach</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="n">
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="2" t="n">
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K108" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Bhíodh féar is fiche againn amach in éineacht Bhíodh an 'turnkey' amach romhainn sa bpáirc Ní raibh aon tsamhail againn ach mar a bheadh caoirigh A bheadh ag gabháil thart timpeall leis an ngalra cam. [UD_Irish-IDT 365, CC BY-SA 3.0]
 Bhíodh féar is fiche againn amach in éineacht Bhíodh an 'turnkey' amach romhainn sa bpáirc Ní raibh aon tsamhail againn ach mar a bheadh caoirigh A bheadh ag gabháil thart timpeall leis an ngalra cam. [UD_Irish-IDT 365, CC BY-SA 3.0]
 A luaithe is a shroicheamar an stad bhí fear óg scafánta amach go dtí muid lenár dtrealamh bagáiste a bhaint dínn. [UD_Irish-IDT 370, CC BY-SA 3.0]
 Bhí an fear bocht sínte amach ar an talamh, gan aithne gan urlabhra. = The poor man was stretched out on the ground, unconscious. [Tatoeba 5592152, CC BY 2.0 FR]
-Ní raibh muid in ann déanamh amach ceard a bhí Paul ag iarraidh a dhéanamh. = We couldn't figure out what Paul wanted to do. [Tatoeba 5015996, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
+Ní raibh muid in ann déanamh amach ceard a bhí Paul ag iarraidh a dhéanamh. = We couldn't figure out what Paul wanted to do. [Tatoeba 5015996, CC BY 2.0 FR]
+Fé dheire bhí sé iompuighthe amach chómh goirgeach san ná féadadh sé stad gan bheith coitchianta ag spriúchadh agus ag adharcáil agus ag búirthig, i dtreó go raibh an tréad go léir cráidhte ciapaithe aige. [Wikisource: Aesop a tháinig go h-Éirinn/An Sean Phoc agus an Laogh, pre-standard, public domain]
+Bhí long tamal amach ar an uisge, agus a seólta breaghtha geala uirthi. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aodhre agus an Fharge, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/5592152
 https://tatoeba.org/en/sentences/show/5015996
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Sean_Phoc_agus_an_Laogh
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-Aodhre_agus_an_Fharge
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M109" s="3" t="inlineStr"/>
-      <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="inlineStr"/>
-      <c r="P109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="O108" s="3" t="inlineStr"/>
+      <c r="P108" s="3" t="inlineStr"/>
+      <c r="Q108" s="3" t="inlineStr"/>
+      <c r="R108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>taitin le</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>taitin</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>le</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>to please, be liked by</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="n">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="2" t="n">
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K109" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>Tá scáth na linne ar an aiste aige, ceann nach dtaitneodh lenár gcáinteoir úd ón Irish Times - 'Tairgim an Aiste seo dosna Fearaibh dfhuiling an t-ocras ar son na hÉireann Abrán 1920' - ná ní thaithneodh an chéad dán sa leabhar leis ach an oiread, is dócha. [UD_Irish-IDT 1797, CC BY-SA 3.0]
 Tá scáth na linne ar an aiste aige, ceann nach dtaitneodh lenár gcáinteoir úd ón Irish Times - 'Tairgim an Aiste seo dosna Fearaibh dfhuiling an t-ocras ar son na hÉireann Abrán 1920' - ná ní thaithneodh an chéad dán sa leabhar leis ach an oiread, is dócha. [UD_Irish-IDT 1797, CC BY-SA 3.0]
 An iomarca uisce a cuireadh san fhuisce; an iomarca d'uisce na cladhaireachta a chuir lucht na Dála i mBille an Óil sa chaoi nach dtaitníonn sé le haon dream sa tír faoi láthair. [UD_Irish-IDT 1861, CC BY-SA 3.0]
 Ar dtús níor thaitin rac-cheol liom ach anois taitníonn sé liom. = At first I did not like rock music, but now I do. [Tatoeba 10317559, CC BY 2.0 FR]
-"Ar thaitin an scannán seo leat?" "Níor thaitin sé liom ar chor ar bith." = “Did you like the movie?” “No, not at all.” [Tatoeba 9044835, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
+"Ar thaitin an scannán seo leat?" "Níor thaitin sé liom ar chor ar bith." = “Did you like the movie?” “No, not at all.” [Tatoeba 9044835, CC BY 2.0 FR]
+Do thaitin an freagra ris an marcós agus do aomh triall d’Earr-Ghaoidheal. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]
+Do thaitin sin le Muntrós agus leis an arm uile, ionnus gur b’é Domhnall agus a mhuinntir is mó do rinn creacha dá raibh san arm uile. [Wikisource: Alasdair Mac Colla/Caithréim Chlainne Raghnaill, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/taitin_le#Irish
 https://tatoeba.org/en/sentences/show/10317559
 https://tatoeba.org/en/sentences/show/9044835
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Chlainne_Raghnaill
 https://www.teanglann.ie/en/fgb/taitin</t>
         </is>
       </c>
-      <c r="M110" s="3" t="inlineStr"/>
-      <c r="N110" s="3" t="inlineStr"/>
-      <c r="O110" s="3" t="inlineStr"/>
-      <c r="P110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="3" t="inlineStr"/>
+      <c r="Q109" s="3" t="inlineStr"/>
+      <c r="R109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>breathnaigh ar</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>breathnaigh</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>ar</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="n">
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="2" t="n">
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K110" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>Má bhreathnaítear ar Ghaillimh i dtosach, tá Michael Crimmins ar ais sa gcúl. [UD_Irish-IDT 245, CC BY-SA 3.0]
 Is leor breathnú ar staitisticí scrúdúcháin an Bhéarla nó na matamaitice chun a fheiceáil gur thit na caighdeáin in ábhair eile chomh maith de réir mar chuaigh daonra na scoile i dtreo dhaonra na tíre san iomlán. [UD_Irish-IDT 247, CC BY-SA 3.0]
 D'inis mé di gurbh iomaí athair agus máthair a sheas sa spota céanna seo ag breathnú ar na báid seoil ar a mbealach le lucht imirce go Meiriceá, ag faire ar na seolta go ndeachadar as amharc ag bun na spéire siar ó thuaidh de Oileán an dá Bhrannóg. [UD_Irish-IDT 274, CC BY-SA 3.0]
-Sin bealach amháin le breathnú air is docha. = That's one way of looking at it, I suppose. [Tatoeba 5516952, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
+Sin bealach amháin le breathnú air is docha. = That's one way of looking at it, I suppose. [Tatoeba 5516952, CC BY 2.0 FR]
+Do bhíomair ann roim am agus sinn ag breithniú ar gach ní mar thárlaidh dúinn. [Wikisource: An t-Oileánach/17, pre-standard, public domain]
+Luínn ar an urlár sa pharlúis ag aghaidh an tí a bhreathnú ar a doras gach maidin. [Wikisource: Muintir Bhaile Átha Cliath/Araby, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/5516952
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/17
+https://wikisource.org/wiki/Muintir_Bhaile_%C3%81tha_Cliath/Araby
 https://www.teanglann.ie/en/fgb/breathnaigh</t>
         </is>
       </c>
-      <c r="M111" s="3" t="inlineStr"/>
-      <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="3" t="inlineStr"/>
-      <c r="P111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="O110" s="3" t="inlineStr"/>
+      <c r="P110" s="3" t="inlineStr"/>
+      <c r="Q110" s="3" t="inlineStr"/>
+      <c r="R110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>pléigh le</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>pléigh</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>le</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>new verb</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>to deal with</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="n">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I112" s="2" t="n">
+      <c r="I111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
         <is>
           <t>Sé deacracht a bhíodh agam teacht amach as an saol san agus plé le gnáthchúrsaí an tsaoil ina rabhas ag maireachtaint. [UD_Irish-IDT 200, CC BY-SA 3.0]
 Beidh a chomhionann le déanamh le fuaimniú na teanga agus is mithid sin le freastal ar mhúinteoirí, agus orthu sin a bhíonn ag plé le scrúduithe agus le trialacha cainte agus éisteachta, agus go háirithe le cuidiú le lucht raidió agus teilifíse uirlis chumhachtach chumarsáide, a dhéanfadh freastal ar phobal leathan ilbhéascnach, a chothú agus a bhuanú. [UD_Irish-IDT 1079, CC BY-SA 3.0]
@@ -6485,32 +7537,96 @@
 Dá mba rud é go mbeadh breac beag suaithinseach éigin aige bhídís ag pléidhe le chéile cé aige go mbeadh sé. [UD_Irish-Cadhan peig-3760, pre-standard, CC BY-SA 4.0]</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/pléigh_le#Irish
 https://tatoeba.org/en/sentences/show/6319299
 https://www.teanglann.ie/en/fgb/pléigh</t>
         </is>
       </c>
-      <c r="M112" s="3" t="inlineStr"/>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="3" t="inlineStr"/>
+      <c r="Q111" s="3" t="inlineStr"/>
+      <c r="R111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>caith ar</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>caith</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Dúrt leis pé duine do raghadh á múscailt nách me féin é; nár bhe' liom a bhfeaca inné dhóibh, agus gan do bheith ag caitheamh an lae inniu ar an gcuma chéanna, agus go ndéanfaidís féin múscailt an uair ba mhaith leo féin é. [UD_Irish-IDT 490, CC BY-SA 3.0]
+Bheadh an scoil éisc faoi lán siúil faoin uisce agus an t-iascaire ag iarraidh é a locadh chun líon trom a chaitheamh timpeall air. [UD_Irish-IDT 534, CC BY-SA 3.0]
+In aice sin bhí ocras céadtach uirre anois, arae, níor chaith sí mórán ar maidin, agus ba ghnás léithe cupán tae cosnochtuighthe a fhagháil, ag an haon déag gach uile lá i gcaitheamh deich mbliana. [UD_Irish-IDT 761, CC BY-SA 3.0]
+Caithfear cabhair a dhéanamh ar chairde in am an ghátair. = One must help friends in times of such need. [Tatoeba 6319350, CC BY 2.0 FR]
+Is é mo chaitheamh aimsire bácáil agus féachaint ar scannáin. = My hobbies are baking and watching movies. [Tatoeba 10925723, CC BY 2.0 FR]
+An easóg bhradach sin, arsa mise liom féin; caithfidh mé smacht chur uirri.... [Wikisource: An Crann Géagach/An Sean-choiléar, pre-standard, public domain]
+n‑a dhealbh órdha aici; slamanna de sholus buidhe órdha dhá gcaitheamh aici ar chraoibh agus ar ghéig agus ar bhilleóig go gceapthá go raibh an saoghal órdha tagtha.... [Wikisource: An Crann Géagach/An bhean bhí ag an bhfuinneóig, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/6319350
+https://tatoeba.org/en/sentences/show/10925723
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Sean-choil%C3%A9ar
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_bhean_bh%C3%AD_ag_an_bhfuinne%C3%B3ig
+https://www.teanglann.ie/en/fgb/caith</t>
+        </is>
+      </c>
       <c r="O112" s="3" t="inlineStr"/>
       <c r="P112" s="3" t="inlineStr"/>
+      <c r="Q112" s="3" t="inlineStr"/>
+      <c r="R112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>caith ar</t>
+          <t>bí isteach</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>caith</t>
+          <t>bí</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>isteach</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6522,49 +7638,55 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>Dúrt leis pé duine do raghadh á múscailt nách me féin é; nár bhe' liom a bhfeaca inné dhóibh, agus gan do bheith ag caitheamh an lae inniu ar an gcuma chéanna, agus go ndéanfaidís féin múscailt an uair ba mhaith leo féin é. [UD_Irish-IDT 490, CC BY-SA 3.0]
-Bheadh an scoil éisc faoi lán siúil faoin uisce agus an t-iascaire ag iarraidh é a locadh chun líon trom a chaitheamh timpeall air. [UD_Irish-IDT 534, CC BY-SA 3.0]
-In aice sin bhí ocras céadtach uirre anois, arae, níor chaith sí mórán ar maidin, agus ba ghnás léithe cupán tae cosnochtuighthe a fhagháil, ag an haon déag gach uile lá i gcaitheamh deich mbliana. [UD_Irish-IDT 761, CC BY-SA 3.0]
-Caithfear cabhair a dhéanamh ar chairde in am an ghátair. = One must help friends in times of such need. [Tatoeba 6319350, CC BY 2.0 FR]
-Is é mo chaitheamh aimsire bácáil agus féachaint ar scannáin. = My hobbies are baking and watching movies. [Tatoeba 10925723, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/6319350
-https://tatoeba.org/en/sentences/show/10925723
-https://www.teanglann.ie/en/fgb/caith</t>
-        </is>
-      </c>
-      <c r="M113" s="3" t="inlineStr"/>
-      <c r="N113" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Tá beagnach ocht mbliana imithe isteach i muileann an ama orm, ó scríobhadh an léirmheas sin, agus níor chuir mé aon díolaim eile filíochta i gcló i rith na tréimhse sin. [UD_Irish-IDT 667, CC BY-SA 3.0]
+Bhí dhá ard mhóra ar an slí isteach go dtí an Daingean, Ard Leataoibh agus Ard Bhaile an nÁith. [UD_Irish-IDT 864, CC BY-SA 3.0]
+'Mura bhfuil slí isteach, caithfear a sholáthar. [UD_Irish-IDT 1751, CC BY-SA 3.0]
+Tá sé buailte isteach am aigne, agus deirim go [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh Maol, pre-standard, public domain]
+Agus dá dtuigfinn i gceart é, bhí an saoghal mór aisteach seo ag déanamh bróin. [Wikisource: An Crann Géagach/Croidhe-bhrughadh na Cruinne, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_Maol
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Croidhe-bhrughadh_na_Cruinne
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="3" t="inlineStr"/>
+      <c r="Q113" s="3" t="inlineStr"/>
+      <c r="R113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>bí isteach</t>
+          <t>cas ar</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>bí</t>
+          <t>cas</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>isteach</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6573,105 +7695,125 @@
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>to meet, meet with</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Tá beagnach ocht mbliana imithe isteach i muileann an ama orm, ó scríobhadh an léirmheas sin, agus níor chuir mé aon díolaim eile filíochta i gcló i rith na tréimhse sin. [UD_Irish-IDT 667, CC BY-SA 3.0]
-Bhí dhá ard mhóra ar an slí isteach go dtí an Daingean, Ard Leataoibh agus Ard Bhaile an nÁith. [UD_Irish-IDT 864, CC BY-SA 3.0]
-'Mura bhfuil slí isteach, caithfear a sholáthar. [UD_Irish-IDT 1751, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M114" s="3" t="inlineStr"/>
-      <c r="N114" s="3" t="inlineStr"/>
-      <c r="O114" s="3" t="inlineStr"/>
-      <c r="P114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>cas ar</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>cas</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>to meet, meet with</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K114" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>Ag barr an chnoic, ar scáth crainn chnó chapall, casann an bheirt ar deis. [UD_Irish-IDT 577, CC BY-SA 3.0]
 Casaimid beirt ar ár sáil d'aon chéim. [UD_Irish-IDT 50, CC BY-SA 3.0]
 Seo díreach an dara huair riamh a chasfar na contaetha seo ar a chéile sa chluiche ceannais. [UD_Irish-IDT 288, CC BY-SA 3.0]
-Chas sí air an lampa, mar bhí sé dorcha. = She switched on the lamp because it was dark. [Tatoeba 4445001, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
+Chas sí air an lampa, mar bhí sé dorcha. = She switched on the lamp because it was dark. [Tatoeba 4445001, CC BY 2.0 FR]
+Do casadh machtíre air. [Wikisource: Aesop a tháinig go h-Éirinn/An Gadhar agus an Machtíre, pre-standard, public domain]
+Casadh an t-arm Gallda leó ar Alt Éirinn i n-aice Inbhir nArann. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/cas_ar#Irish
 https://tatoeba.org/en/sentences/show/4445001
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Gadhar_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
 https://www.teanglann.ie/en/fgb/cas</t>
         </is>
       </c>
-      <c r="M115" s="3" t="inlineStr"/>
-      <c r="N115" s="3" t="inlineStr"/>
+      <c r="O114" s="3" t="inlineStr"/>
+      <c r="P114" s="3" t="inlineStr"/>
+      <c r="Q114" s="3" t="inlineStr"/>
+      <c r="R114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>imigh le</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>imigh</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>le</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Ach nuair a chas mé síos níor lean sé mé, ach d'imigh leis soir. [UD_Irish-IDT 843, CC BY-SA 3.0]
+'SLUA: Go n-imí an diabhal do bhóthar, imigh leat is ná tar arís! [UD_Irish-IDT 378, CC BY-SA 3.0]
+Agus d'imigh liomsa, 'adeir sé,' agus thosaigh mé ag strapadóireacht, agus suas, suas a chuaigh mé, 'adeir sé,' agus bhí mé a' dhul suas suas ar an gcrann, 'adeir sé,' go brách, ó ghéagán go géagán, 'adeir sé,' go dtáinig mé go dtí doras na bhflaitheas. [UD_Irish-IDT 427, CC BY-SA 3.0]
+imthigh leat féin,” arsa ’n machtíre. [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh agus an Machtíre, pre-standard, public domain]
+“Imthigh,” arsa Iupiter le n-a ghiolla, “agus tabhair rígh dhóibh siúd.” “Cad é an rígh a thabharfad dóibh?” arsan giolla. [Wikisource: Aesop a tháinig go h-Éirinn/Na Frogana a’ Lorg Rígh, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/Na_Frogana_a%E2%80%99_Lorg_R%C3%ADgh
+https://www.teanglann.ie/en/fgb/imigh</t>
+        </is>
+      </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="3" t="inlineStr"/>
+      <c r="Q115" s="3" t="inlineStr"/>
+      <c r="R115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>imigh le</t>
+          <t>beir ar</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>imigh</t>
+          <t>beir</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6680,94 +7822,116 @@
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>to catch | to overtake</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>Ach nuair a chas mé síos níor lean sé mé, ach d'imigh leis soir. [UD_Irish-IDT 843, CC BY-SA 3.0]
-'SLUA: Go n-imí an diabhal do bhóthar, imigh leat is ná tar arís! [UD_Irish-IDT 378, CC BY-SA 3.0]
-Agus d'imigh liomsa, 'adeir sé,' agus thosaigh mé ag strapadóireacht, agus suas, suas a chuaigh mé, 'adeir sé,' agus bhí mé a' dhul suas suas ar an gcrann, 'adeir sé,' go brách, ó ghéagán go géagán, 'adeir sé,' go dtáinig mé go dtí doras na bhflaitheas. [UD_Irish-IDT 427, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/imigh</t>
-        </is>
-      </c>
-      <c r="M116" s="3" t="inlineStr"/>
-      <c r="N116" s="3" t="inlineStr"/>
-      <c r="O116" s="3" t="inlineStr"/>
-      <c r="P116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>beir ar</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>beir</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>to catch | to overtake</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K116" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>Rug Antaine ar an Independant a bhí ar bhinse Charoline is scuab an chuid eile amach chun a saoirse. [UD_Irish-IDT 557, CC BY-SA 3.0]
 Amach leis gur rug sé ar thacsaí. [UD_Irish-IDT 163, CC BY-SA 3.0]
 Anois bhí muid ag breith ar na Sierras, cuid de na Rockies, an sliabhraon mór géar snámhach sin a ritheann ó Alasca go Meicsiceo. [UD_Irish-IDT 969, CC BY-SA 3.0]
-Ar anadhbharsin an uáir do d'aithin Iósa gu raibhe fúthasan teachd agus breith air dochum riogh dho dhéunamh dhé dochúaidh sé dhá leaththáoibh arís ar an sliabh ina áonar. [UD_Irish-Cadhan eoin-238, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
+Ar anadhbharsin an uáir do d'aithin Iósa gu raibhe fúthasan teachd agus breith air dochum riogh dho dhéunamh dhé dochúaidh sé dhá leaththáoibh arís ar an sliabh ina áonar. [UD_Irish-Cadhan eoin-238, pre-standard, CC BY-SA 4.0]
+Os a gcómhair amach, gan blúire iongna ’na thaobh air, do rug sé ar cholúr acu agus do mhairbh agus d’ith! [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]
+Do rug duine acu ar an ndórnán. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>https://en.wiktionary.org/wiki/beir_ar#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
 https://www.teanglann.ie/en/fgb/beir</t>
         </is>
       </c>
-      <c r="M117" s="3" t="inlineStr"/>
-      <c r="N117" s="3" t="inlineStr"/>
+      <c r="O116" s="3" t="inlineStr"/>
+      <c r="P116" s="3" t="inlineStr"/>
+      <c r="Q116" s="3" t="inlineStr"/>
+      <c r="R116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>caith le</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>caith</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>le</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Dhéanadh sé an turas seo uair in aghaidh na míosa chun roinnt ama a chaitheamh lena iníon, Siobhán, agus leis na leanaí. [UD_Irish-IDT 154, CC BY-SA 3.0]
+Chaitheamar roinnt urchar leo le bac a chur ar dhaoine aon chomhluadar a dhéanamh leo. [UD_Irish-IDT 448, CC BY-SA 3.0]
+Chaith sé cúpla bliain ina chónaí ar an oileán leis féin ach bhog sé isteach go tír mór sa bhliain 1975 nuair a bhí sé 63 bliain d'aois. [UD_Irish-IDT 1028, CC BY-SA 3.0]
+Tá fonn ar Tom am a chaitheamh liom. = Tom wants to spend time with me. [Tatoeba 6319288, CC BY 2.0 FR]
+Ualach arbhair a ghoid agus a dhíol agus an t‑airgead a chaitheamh i dteach ósta le fear....” [Wikisource: An Crann Géagach/An bhean bhí ag an bhfuinneóig, pre-standard, public domain]
+agam, go séalaidh an t‑anam uaim, ar an bhfleidh aoibhinn chaitheamar le chéile i lúb na coille craobhaighe. [Wikisource: An Crann Géagach/Slán agaibh, a Cháirde, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/6319288
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_bhean_bh%C3%AD_ag_an_bhfuinne%C3%B3ig
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Sl%C3%A1n_agaibh%2C_a_Ch%C3%A1irde
+https://www.teanglann.ie/en/fgb/caith</t>
+        </is>
+      </c>
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="3" t="inlineStr"/>
+      <c r="Q117" s="3" t="inlineStr"/>
+      <c r="R117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>caith le</t>
+          <t>caith ó</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6777,7 +7941,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6789,47 +7953,55 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>Dhéanadh sé an turas seo uair in aghaidh na míosa chun roinnt ama a chaitheamh lena iníon, Siobhán, agus leis na leanaí. [UD_Irish-IDT 154, CC BY-SA 3.0]
-Chaitheamar roinnt urchar leo le bac a chur ar dhaoine aon chomhluadar a dhéanamh leo. [UD_Irish-IDT 448, CC BY-SA 3.0]
-Chaith sé cúpla bliain ina chónaí ar an oileán leis féin ach bhog sé isteach go tír mór sa bhliain 1975 nuair a bhí sé 63 bliain d'aois. [UD_Irish-IDT 1028, CC BY-SA 3.0]
-Tá fonn ar Tom am a chaitheamh liom. = Tom wants to spend time with me. [Tatoeba 6319288, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/6319288
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Agus ón uair a chuir mé mo chos thar tairseach na Cultúrlainne ag a sé a' chlog tráthnóna, caitheadh go hiontach liom agus mhothaigh mé sa bhaile i measc mo chomhghael Feirsteach. [UD_Irish-IDT 115, CC BY-SA 3.0]
+Bhíodar á gcaitheamh féin anuas ón spéir uachtarach ag tachtadh agus ag slogadh na n-iasc. [UD_Irish-IDT 1508, CC BY-SA 3.0]
+Tusa, a ghiolla na léitheoireachta, caith uait an páipéar nuaíochta sin, tabhair do shúil thart ar an chuideachta agus, má tá tú ar dhóigh ar bith dearcasach tuigseach, toisigh a smaointiú ar a bhfuil ar d'amharc agus ar d'éisteacht. [UD_Irish-IDT 2045, CC BY-SA 3.0]
+Chaith mé uaim an gléas gearrtha agus d’fhéach mé ar obair mo lámh. [Wikisource: An Crann Géagach/Fleadh aoibhinn, pre-standard, public domain]
+Chaith mé uaim mo chuid oirnéis. [Wikisource: An Crann Géagach/Fleadh aoibhinn, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Fleadh_aoibhinn
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Fleadh_aoibhinn
 https://www.teanglann.ie/en/fgb/caith</t>
         </is>
       </c>
-      <c r="M118" s="3" t="inlineStr"/>
-      <c r="N118" s="3" t="inlineStr"/>
       <c r="O118" s="3" t="inlineStr"/>
       <c r="P118" s="3" t="inlineStr"/>
+      <c r="Q118" s="3" t="inlineStr"/>
+      <c r="R118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>caith ó</t>
+          <t>oir do</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>caith</t>
+          <t>oir</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6838,10 +8010,14 @@
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>wish, need, require</t>
+        </is>
+      </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>0</v>
@@ -6849,37 +8025,48 @@
       <c r="J119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>Agus ón uair a chuir mé mo chos thar tairseach na Cultúrlainne ag a sé a' chlog tráthnóna, caitheadh go hiontach liom agus mhothaigh mé sa bhaile i measc mo chomhghael Feirsteach. [UD_Irish-IDT 115, CC BY-SA 3.0]
-Bhíodar á gcaitheamh féin anuas ón spéir uachtarach ag tachtadh agus ag slogadh na n-iasc. [UD_Irish-IDT 1508, CC BY-SA 3.0]
-Tusa, a ghiolla na léitheoireachta, caith uait an páipéar nuaíochta sin, tabhair do shúil thart ar an chuideachta agus, má tá tú ar dhóigh ar bith dearcasach tuigseach, toisigh a smaointiú ar a bhfuil ar d'amharc agus ar d'éisteacht. [UD_Irish-IDT 2045, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/caith</t>
-        </is>
-      </c>
-      <c r="M119" s="3" t="inlineStr"/>
-      <c r="N119" s="3" t="inlineStr"/>
+      <c r="K119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>'' Ní dóigh liom go n-oirfeadh sé duit! [UD_Irish-IDT 614, CC BY-SA 3.0]
+Tá sé in am dúinn anois na huirlisí agus na struchtúir pholaitiúla a chur ar bun chun go mbeimid in ann tabhairt faoi na ceisteanna ar shlí a thuigfidh an pobal agus a chuirfidh ar chumas an phobail páirt a ghlacadh i pé réiteach is fearr a oireann dúinn. [UD_Irish-IDT 1954, CC BY-SA 3.0]
+Seo cúrsaí grádaithe a oireann do gach leibhéal cumais atá forbartha ag Ionad na dTeangacha, Ollscoil na hÉireann, Má Nuad, agus sé Teastas Eorpach na Gaeilge an t-aon teastas creidiúnaithe d’fhoghlaimeoirí Gaeilge atá ar fáil. [UD_Irish-IDT 4169, CC BY-SA 3.0]
+Oirean dom an bhróg so do chríochnughadh. [Wikisource: Séadna/31, pre-standard, public domain]
+Má oirean dó cleamhnas a dhéanamh le Sadhbh, nár chóir go mbéadh an lá fada a dhóithin chuige agus gan bheith ag caitheamh na h‑oídhche amuich ar an gcuma so? [Wikisource: Séadna/9, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/oir_do#Irish
+https://wikisource.org/wiki/S%C3%A9adna/31
+https://wikisource.org/wiki/S%C3%A9adna/9
+https://www.teanglann.ie/en/fgb/oir</t>
+        </is>
+      </c>
       <c r="O119" s="3" t="inlineStr"/>
       <c r="P119" s="3" t="inlineStr"/>
+      <c r="Q119" s="3" t="inlineStr"/>
+      <c r="R119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>oir do</t>
+          <t>bí suas</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>oir</t>
+          <t>bí</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>suas</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6888,107 +8075,125 @@
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>wish, need, require</t>
-        </is>
-      </c>
+      <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>'' Ní dóigh liom go n-oirfeadh sé duit! [UD_Irish-IDT 614, CC BY-SA 3.0]
-Tá sé in am dúinn anois na huirlisí agus na struchtúir pholaitiúla a chur ar bun chun go mbeimid in ann tabhairt faoi na ceisteanna ar shlí a thuigfidh an pobal agus a chuirfidh ar chumas an phobail páirt a ghlacadh i pé réiteach is fearr a oireann dúinn. [UD_Irish-IDT 1954, CC BY-SA 3.0]
-Seo cúrsaí grádaithe a oireann do gach leibhéal cumais atá forbartha ag Ionad na dTeangacha, Ollscoil na hÉireann, Má Nuad, agus sé Teastas Eorpach na Gaeilge an t-aon teastas creidiúnaithe d’fhoghlaimeoirí Gaeilge atá ar fáil. [UD_Irish-IDT 4169, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/oir_do#Irish
-https://www.teanglann.ie/en/fgb/oir</t>
-        </is>
-      </c>
-      <c r="M120" s="3" t="inlineStr"/>
-      <c r="N120" s="3" t="inlineStr"/>
-      <c r="O120" s="3" t="inlineStr"/>
-      <c r="P120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>bí suas</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>bí</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>suas</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K120" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>Bíonn suas le céad cineál éagsúil aimsire agus feiniméan aimsire san áireamh ag meitéareolaithe, ón gceobhrán go dtí tornádónna. [UD_Irish-IDT 1339, CC BY-SA 3.0]
 'Nach bhfuil sé sin suas le deich mbliana fichead ó shoin! [UD_Irish-IDT 1656, CC BY-SA 3.0]
 D'fhógair Seán Kyne T.D., an tAire Stáit do Ghnóthaí Gaeltachta, inniu go bhfuil deontas suas le €5,000 ceadaithe aige do Chomharchumann Mhic Dara Teo. chun cur ar a gcumas córas nua fuaime a cheannach. [UD_Irish-IDT 4651, CC BY-SA 3.0]
 Táim chun briseadh suas le Tomás. = I'm going to break up with Tom. [Tatoeba 10317478, CC BY 2.0 FR]
-Uair a bhí mise ag fás suas, chonaic mé an buachaill is láidre sa mbaile. Agus ó chonaic mé an t-aonad san, nídh 'acainn dom dol im choladh. = When I was growing up, I saw the largest boy in the village. Since I saw that unit, I have not been able to sleep. [Tatoeba 7290681, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
+Uair a bhí mise ag fás suas, chonaic mé an buachaill is láidre sa mbaile. Agus ó chonaic mé an t-aonad san, nídh 'acainn dom dol im choladh. = When I was growing up, I saw the largest boy in the village. Since I saw that unit, I have not been able to sleep. [Tatoeba 7290681, CC BY 2.0 FR]
+Nuair bhíon sé suas ní bhíon uraim dó. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Nuair bhíon sé suas ní bhíon uraim dó. [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/10317478
 https://tatoeba.org/en/sentences/show/7290681
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
 https://www.teanglann.ie/en/fgb/bí</t>
         </is>
       </c>
-      <c r="M121" s="3" t="inlineStr"/>
-      <c r="N121" s="3" t="inlineStr"/>
+      <c r="O120" s="3" t="inlineStr"/>
+      <c r="P120" s="3" t="inlineStr"/>
+      <c r="Q120" s="3" t="inlineStr"/>
+      <c r="R120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>clis ar</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>clis</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>to surpass | to fail | to let down (disappoint)</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Sa deireadh chlis ar a chuid cleasa agus tháinig Margaret Thatcher agus na Tóraithe i réim. [UD_Irish-IDT 2715, CC BY-SA 3.0]
+Meabhraigh gur féidir le tiomnacht nó bronntanas ar bith i d'uacht a chliseadh ar go leor fáthanna. [UD_Irish-IDT 4066, CC BY-SA 3.0]
+Síníonn gach aon duine comhaontú a dhícháilíonn do dhlíodóirí comhoibritheacha ó ionadaíocht a dhéanamh duit sa chúirt má chliseann ar an bpróiseas. [UD_Irish-IDT 4881, CC BY-SA 3.0]
+“Díolfaidh tú as na clis lá éigin, a bhuachaill,” ar seisean. [Wikisource: Jimín/5, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/clis_ar#Irish
+https://wikisource.org/wiki/Jim%C3%ADn/5
+https://www.teanglann.ie/en/fgb/clis</t>
+        </is>
+      </c>
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr"/>
+      <c r="Q121" s="3" t="inlineStr"/>
+      <c r="R121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>clis ar</t>
+          <t>imigh as</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>clis</t>
+          <t>imigh</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -6999,7 +8204,7 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>to surpass | to fail | to let down (disappoint)</t>
+          <t>to go out of | to go from; to be lost to | to fade away; to fail | to give; to slacken</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
@@ -7012,38 +8217,48 @@
       <c r="J122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Sa deireadh chlis ar a chuid cleasa agus tháinig Margaret Thatcher agus na Tóraithe i réim. [UD_Irish-IDT 2715, CC BY-SA 3.0]
-Meabhraigh gur féidir le tiomnacht nó bronntanas ar bith i d'uacht a chliseadh ar go leor fáthanna. [UD_Irish-IDT 4066, CC BY-SA 3.0]
-Síníonn gach aon duine comhaontú a dhícháilíonn do dhlíodóirí comhoibritheacha ó ionadaíocht a dhéanamh duit sa chúirt má chliseann ar an bpróiseas. [UD_Irish-IDT 4881, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/clis_ar#Irish
-https://www.teanglann.ie/en/fgb/clis</t>
-        </is>
-      </c>
-      <c r="M122" s="3" t="inlineStr"/>
-      <c r="N122" s="3" t="inlineStr"/>
+      <c r="K122" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Dá mbeinn gearrtha amach ón gcomhluadar is eol duit b'fhéidir go n-imeodh an díthchéille as mo chroí. [UD_Irish-IDT 1201, CC BY-SA 3.0]
+Faoi mar a bhí na buachaillí ag imeacht as na scoileanna tuaithe, bhí siadsan, ní nach ionadh, ag dul chun deiridh agus ag dul in olcas. [UD_Irish-IDT 1666, CC BY-SA 3.0]
+Dá mbeadh gach rud ag feidhmiú i gceart, ní bheadh orthu imeacht as an tír, an tuairim a bheadh acu, measaim. [UD_Irish-IDT 2078, CC BY-SA 3.0]
+“Imthig as so!” ar seisean. [Wikisource: Aesop a tháinig go h-Éirinn/An tSaint agus an Formad, pre-standard, public domain]
+Agus do imthigh Isaac assin, agus do shuighigh a phubuil a ngleann Gérar, agus do áitribh ann. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/imigh_as#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_tSaint_agus_an_Formad
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/imigh</t>
+        </is>
+      </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="3" t="inlineStr"/>
+      <c r="Q122" s="3" t="inlineStr"/>
+      <c r="R122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>imigh as</t>
+          <t>scaoil le</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>imigh</t>
+          <t>scaoil</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7054,12 +8269,12 @@
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>to go out of | to go from; to be lost to | to fade away; to fail | to give; to slacken</t>
+          <t>to free from restraint | to cast to | to let go with; to make over to | to fire at</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I123" s="2" t="n">
         <v>0</v>
@@ -7067,28 +8282,37 @@
       <c r="J123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>Dá mbeinn gearrtha amach ón gcomhluadar is eol duit b'fhéidir go n-imeodh an díthchéille as mo chroí. [UD_Irish-IDT 1201, CC BY-SA 3.0]
-Faoi mar a bhí na buachaillí ag imeacht as na scoileanna tuaithe, bhí siadsan, ní nach ionadh, ag dul chun deiridh agus ag dul in olcas. [UD_Irish-IDT 1666, CC BY-SA 3.0]
-Dá mbeadh gach rud ag feidhmiú i gceart, ní bheadh orthu imeacht as an tír, an tuairim a bheadh acu, measaim. [UD_Irish-IDT 2078, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/imigh_as#Irish
-https://www.teanglann.ie/en/fgb/imigh</t>
-        </is>
-      </c>
-      <c r="M123" s="3" t="inlineStr"/>
-      <c r="N123" s="3" t="inlineStr"/>
+      <c r="K123" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Is cosúil go bhfuil an tír lán de sheanmháthaireacha, de dhúnmharaithe agus de mhadraí crochta agus chuile dhuine ag gáirí faoin saol nó ag iarraidh iad fhéin a scaoileadh le seanghráinghunnaí meirgeacha. [UD_Irish-IDT 518, CC BY-SA 3.0]
+Bhí beirt fhear sínte ar a mbolg ag scaoileadh le ceathrar eile a bhí tar éis an abha a thrasnú. [UD_Irish-IDT 710, CC BY-SA 3.0]
+Do sgaoíl sí leis go ceann tamail bhig go dtí go raibh sé ag gabhail tré bhearna draoíbe. [Wikisource: Aesop a tháinig go h-Éirinn/An Sean Duine agus an Bás, pre-standard, public domain]
+“Dar Muire!” arsa Diarmaid, “scaoil leis. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_le#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Sean_Duine_agus_an_B%C3%A1s
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://www.teanglann.ie/en/fgb/scaoil</t>
+        </is>
+      </c>
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr"/>
+      <c r="Q123" s="3" t="inlineStr"/>
+      <c r="R123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>scaoil le</t>
+          <t>scaoil ó</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -7098,7 +8322,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -7109,7 +8333,7 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>to free from restraint | to cast to | to let go with; to make over to | to fire at</t>
+          <t>to release from | to let go from</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
@@ -7122,37 +8346,47 @@
       <c r="J124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Is cosúil go bhfuil an tír lán de sheanmháthaireacha, de dhúnmharaithe agus de mhadraí crochta agus chuile dhuine ag gáirí faoin saol nó ag iarraidh iad fhéin a scaoileadh le seanghráinghunnaí meirgeacha. [UD_Irish-IDT 518, CC BY-SA 3.0]
-Bhí beirt fhear sínte ar a mbolg ag scaoileadh le ceathrar eile a bhí tar éis an abha a thrasnú. [UD_Irish-IDT 710, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_le#Irish
+      <c r="K124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>eisfhearadh: scaoileadh dramhaíle ó orgánach. [UD_Irish-IDT 1100, CC BY-SA 3.0]
+Ar an gCoimisiún nó Ballstát á iarraidh sin, féadfaidh an Chomhairle, ag gníomhú di d'aon toil, grádú eile a chur chun feidhme nó an fhaisnéis a scaoileadh ó rúnaicmiú tráth ar bith. [UD_Irish-IDT 3274, CC BY-SA 3.0]
+An uair a chuaidh isteach do scaoil uaidh an t‑ualach. [Wikisource: An t-Oileánach/15, pre-standard, public domain]
+Níor scaoil sí riamh uaithe na buadha is dúthchas di, agus níor leig sí riamh do ré dul thairste gan an náisiúntacht is dual di féin an leithligh do dhearbhadh go dána ó Ghabháltas Gall I leith go dtí an tráth is déadhnaighe dár ghlac sí claidheamh go cródha I mbliadhain a 1916. [Wikisource: Scéal ó Dháil Éireann chum Saor-Náisiún an Domhain, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_ó#Irish
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/15
+https://wikisource.org/wiki/Sc%C3%A9al_%C3%B3_Dh%C3%A1il_%C3%89ireann_chum_Saor-N%C3%A1isi%C3%BAn_an_Domhain
 https://www.teanglann.ie/en/fgb/scaoil</t>
         </is>
       </c>
-      <c r="M124" s="3" t="inlineStr"/>
-      <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="3" t="inlineStr"/>
       <c r="P124" s="3" t="inlineStr"/>
+      <c r="Q124" s="3" t="inlineStr"/>
+      <c r="R124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>scaoil ó</t>
+          <t>abair ar</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>scaoil</t>
+          <t>abair</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -7161,42 +8395,50 @@
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>to release from | to let go from</t>
-        </is>
-      </c>
+      <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>eisfhearadh: scaoileadh dramhaíle ó orgánach. [UD_Irish-IDT 1100, CC BY-SA 3.0]
-Ar an gCoimisiún nó Ballstát á iarraidh sin, féadfaidh an Chomhairle, ag gníomhú di d'aon toil, grádú eile a chur chun feidhme nó an fhaisnéis a scaoileadh ó rúnaicmiú tráth ar bith. [UD_Irish-IDT 3274, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_ó#Irish
-https://www.teanglann.ie/en/fgb/scaoil</t>
-        </is>
-      </c>
-      <c r="M125" s="3" t="inlineStr"/>
-      <c r="N125" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>Ach an oiread le Steven Stiofáinín (Seoige), dúirt sé ar television é agus dúirt sé an ceart. [UD_Irish-IDT 1260, CC BY-SA 3.0]
+B'fhéidir gurbh fhearr gan a thuilleadh a rá ar ábhar atá chomh goilliúnach sin. [UD_Irish-IDT 2308, CC BY-SA 3.0]
+Ar an dtaobh eile don scéal deireann sé gur Sasanach é - cé nach bhfuil sé sásta cónaí ann agus cé go bhfuil an ghráin dearg aige air. [UD_Irish-IDT 2651, CC BY-SA 3.0]
+Dúirt Tomás go bhfuil áthas ar Máire. = Tom said Mary was happy. [Tatoeba 3600043, CC BY 2.0 FR]
+Agus do ghoir Phárao Abram agus adubhairt; créad éso dorinne tu oram, créd nár innis tú dham gurbh í do bhean í? [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus adubhairt Abraham ar bhfreagra dho; féuch do ghabh misi orm labhairt ris an tighearna, nach bhfuil ionnam ach cré, agus luáithreadh. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/3600043
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/abair</t>
+        </is>
+      </c>
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr"/>
+      <c r="Q125" s="3" t="inlineStr"/>
+      <c r="R125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>abair ar</t>
+          <t>abair do</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -7206,7 +8448,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -7218,37 +8460,45 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Ach an oiread le Steven Stiofáinín (Seoige), dúirt sé ar television é agus dúirt sé an ceart. [UD_Irish-IDT 1260, CC BY-SA 3.0]
-B'fhéidir gurbh fhearr gan a thuilleadh a rá ar ábhar atá chomh goilliúnach sin. [UD_Irish-IDT 2308, CC BY-SA 3.0]
-Ar an dtaobh eile don scéal deireann sé gur Sasanach é - cé nach bhfuil sé sásta cónaí ann agus cé go bhfuil an ghráin dearg aige air. [UD_Irish-IDT 2651, CC BY-SA 3.0]
-Dúirt Tomás go bhfuil áthas ar Máire. = Tom said Mary was happy. [Tatoeba 3600043, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/3600043
+        <v>0</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>'Cad chuige nach n-abrófá féin staic d'amhrán dúinn, is gur tú an fear ceoil is fearr ar an mbaile? [UD_Irish-IDT 14, CC BY-SA 3.0]
+Bhí deis ag na baill athmhachnamh a dhéanamh ar chúrsaí i rith na laethanta saoire agus táimid anois ag tabhairt cluas éisteachta dóibh arís, 'a deir sí. [UD_Irish-IDT 1879, CC BY-SA 3.0]
+Fuaim millteanach ag an charr sa choineascar, déarfá seanghluaisteán a sháródh ar dhlithe fritruaillithe, ó thaobh fuaime is fuíollach peitrealdóite dó. [UD_Irish-IDT 2377, CC BY-SA 3.0]
+An dar lá de mhí Iúil (nó deireadh samhraidh) do bhris Montrós cath eile ar mhuintir an Choibhinint i nAlphort. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]
+’San deireadh thiar, do bhris ar an sluagh Gallda, agus níor stad na Gaedhil de’n ruaig sin nó gur leanadar fad ceithre míle déag iad, agus go dtugadar bás do shé mhíle dá sluagh. [Wikisource: Alasdair Mac Colla/Caithréim Alasdair Mhic Dhomhnaill, II, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
+https://wikisource.org/wiki/Alasdair_Mac_Colla/Caithr%C3%A9im_Alasdair_Mhic_Dhomhnaill%2C_II
 https://www.teanglann.ie/en/fgb/abair</t>
         </is>
       </c>
-      <c r="M126" s="3" t="inlineStr"/>
-      <c r="N126" s="3" t="inlineStr"/>
       <c r="O126" s="3" t="inlineStr"/>
       <c r="P126" s="3" t="inlineStr"/>
+      <c r="Q126" s="3" t="inlineStr"/>
+      <c r="R126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>abair do</t>
+          <t>abair faoi</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -7258,7 +8508,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>faoi</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -7278,37 +8528,47 @@
       <c r="J127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>'Cad chuige nach n-abrófá féin staic d'amhrán dúinn, is gur tú an fear ceoil is fearr ar an mbaile? [UD_Irish-IDT 14, CC BY-SA 3.0]
-Bhí deis ag na baill athmhachnamh a dhéanamh ar chúrsaí i rith na laethanta saoire agus táimid anois ag tabhairt cluas éisteachta dóibh arís, 'a deir sí. [UD_Irish-IDT 1879, CC BY-SA 3.0]
-Fuaim millteanach ag an charr sa choineascar, déarfá seanghluaisteán a sháródh ar dhlithe fritruaillithe, ó thaobh fuaime is fuíollach peitrealdóite dó. [UD_Irish-IDT 2377, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/abair</t>
-        </is>
-      </c>
-      <c r="M127" s="3" t="inlineStr"/>
-      <c r="N127" s="3" t="inlineStr"/>
+      <c r="K127" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>Ba chiallmhar, ba riachtanach agus ba chuí gach focal a dúirt Potter faoi chórais theilifíse an domhain - an BBC ina measc; faoin gcaoi ina bhfuil siad tite i léig; agus faoin dochar atá á dhéanamh do na meáin chumarsáide go léir ag polaiteoirí agus lucht rachmais - go háirithe, Rupert Murdoch. [UD_Irish-IDT 984, CC BY-SA 3.0]
+Labhair sé faoin bhfeamainn, faoi na hoileáin, faoin iascaireacht, faoi gach ar féidir a rá faoin bhfarraige, ba chosúil. [UD_Irish-IDT 1546, CC BY-SA 3.0]
+Faoi mar is eol don uile dhuine, a deir tú, le cúpla mí. [UD_Irish-IDT 2403, CC BY-SA 3.0]
+Dubhairt sé rud éigin fá an “leabhar” ar dtús, agus shaoileadar ar uairibh gurbh é siúd an fáth faoi nár sgríobh sé. [Wikisource: Caoimhghin Ó Cearnaigh/14, pre-standard, public domain]
+Dubhairt sé a lán faoi na neithe seo. [Wikisource: Caoimhghin Ó Cearnaigh/17, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Caoimhghin_%C3%93_Cearnaigh/14
+https://wikisource.org/wiki/Caoimhghin_%C3%93_Cearnaigh/17
+https://www.teanglann.ie/en/fgb/abair</t>
+        </is>
+      </c>
       <c r="O127" s="3" t="inlineStr"/>
       <c r="P127" s="3" t="inlineStr"/>
+      <c r="Q127" s="3" t="inlineStr"/>
+      <c r="R127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>abair faoi</t>
+          <t>airigh ó</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>abair</t>
+          <t>airigh</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -7317,10 +8577,14 @@
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>to miss, feel the want of (the object of ó agrees with the subject of the verb)</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>0</v>
@@ -7328,37 +8592,46 @@
       <c r="J128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Ba chiallmhar, ba riachtanach agus ba chuí gach focal a dúirt Potter faoi chórais theilifíse an domhain - an BBC ina measc; faoin gcaoi ina bhfuil siad tite i léig; agus faoin dochar atá á dhéanamh do na meáin chumarsáide go léir ag polaiteoirí agus lucht rachmais - go háirithe, Rupert Murdoch. [UD_Irish-IDT 984, CC BY-SA 3.0]
-Labhair sé faoin bhfeamainn, faoi na hoileáin, faoin iascaireacht, faoi gach ar féidir a rá faoin bhfarraige, ba chosúil. [UD_Irish-IDT 1546, CC BY-SA 3.0]
-Faoi mar is eol don uile dhuine, a deir tú, le cúpla mí. [UD_Irish-IDT 2403, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/abair</t>
-        </is>
-      </c>
-      <c r="M128" s="3" t="inlineStr"/>
-      <c r="N128" s="3" t="inlineStr"/>
+      <c r="K128" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>@user101  Tuigeann daoine. Féir plé duit. Tá tú i bhfad níos fearr ná mar a bhí mo Sheapáinis san am céanna. Airímid uainn thú #Éireannach [UD_Irish-TwittIrish LTC_782, CC BY-SA 4.0]
+Níor airigh muid uainn é gur labhair Cuimín. [Wikisource: An Mháthair agus Sgéalta Eile/An Bhean Chaointe, pre-standard, public domain]
+D’itheadh a dhinnéar i dtigh béile ar Shráid Sheoirse, áit ar airigh sé slán sábhaile ó chuideachta ógra saibhir Átha Cliath, agus áit ina raibh macántacht thíriúil faoin chlár bia. [Wikisource: Muintir Bhaile Átha Cliath/Cás Coscrach, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/airigh_ó#Irish
+https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/An_Bhean_Chaointe
+https://wikisource.org/wiki/Muintir_Bhaile_%C3%81tha_Cliath/C%C3%A1s_Coscrach
+https://www.teanglann.ie/en/fgb/airigh</t>
+        </is>
+      </c>
       <c r="O128" s="3" t="inlineStr"/>
       <c r="P128" s="3" t="inlineStr"/>
+      <c r="Q128" s="3" t="inlineStr"/>
+      <c r="R128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>airigh ó</t>
+          <t>caith amach</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>airigh</t>
+          <t>caith</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>amach</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -7369,7 +8642,7 @@
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>to miss, feel the want of (the object of ó agrees with the subject of the verb)</t>
+          <t>throw out | project</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
@@ -7382,36 +8655,46 @@
       <c r="J129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>@user101  Tuigeann daoine. Féir plé duit. Tá tú i bhfad níos fearr ná mar a bhí mo Sheapáinis san am céanna. Airímid uainn thú #Éireannach [UD_Irish-TwittIrish LTC_782, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/airigh_ó#Irish
-https://www.teanglann.ie/en/fgb/airigh</t>
-        </is>
-      </c>
-      <c r="M129" s="3" t="inlineStr"/>
-      <c r="N129" s="3" t="inlineStr"/>
+      <c r="K129" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>Ní chaithfidh tú leagan amach ar leith a chur ar d'uacht. [UD_Irish-IDT 3205, CC BY-SA 3.0]
+Do caitheadh an mhil amach i dteanta na cod’ eile. [Wikisource: Aesop a tháinig go h-Éirinn/An t-Aodhre agus an Fharge, pre-standard, public domain]
+Níorbh’ fhearr liom-sa féin an oidhche go léir do chaitheamh age baile ná bualadh amach tamall. [Wikisource: An t-Oileánach/15, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/caith_amach#Irish
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_t-Aodhre_agus_an_Fharge
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/15
+https://www.teanglann.ie/en/fgb/caith</t>
+        </is>
+      </c>
       <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="3" t="inlineStr"/>
+      <c r="Q129" s="3" t="inlineStr"/>
+      <c r="R129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>caith amach</t>
+          <t>imigh ó</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>caith</t>
+          <t>imigh</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>amach</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -7420,103 +8703,119 @@
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>throw out | project</t>
-        </is>
-      </c>
+      <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Ní chaithfidh tú leagan amach ar leith a chur ar d'uacht. [UD_Irish-IDT 3205, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/caith_amach#Irish
-https://www.teanglann.ie/en/fgb/caith</t>
-        </is>
-      </c>
-      <c r="M130" s="3" t="inlineStr"/>
-      <c r="N130" s="3" t="inlineStr"/>
-      <c r="O130" s="3" t="inlineStr"/>
-      <c r="P130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>imigh ó</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>imigh</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>ó</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
+      <c r="K130" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
         <is>
           <t>Tar éis don Choisdealach imeacht uaithi, níor dhúisigh Úna ar feadh tamaill áibhéil mhóir. [UD_Irish-IDT 2354, CC BY-SA 3.0]
 Cuirfear tús leis an nós imeachta má bhíonn na critéir dá bhforáiltear i mír 2 comhlíonta agus má bhíonn d'intinn ag an gComhairle imeacht ón tuairim a ghlac an Tionól. [UD_Irish-IDT 4585, CC BY-SA 3.0]
 Rachaidh an Chomhairle i gcomhairle leis an gCoimisiún agus, más iomchuí, leis na hinstitiúidí eile lena mbaineann, aon uair a bheidh d'intinn aici imeacht ón réamhdhréachtbhuiséad. [UD_Irish-IDT 4589, CC BY-SA 3.0]
-D’imigh sí go Sasana bliain ó shin. = She went to England a year ago. [Tatoeba 875703, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
+D’imigh sí go Sasana bliain ó shin. = She went to England a year ago. [Tatoeba 875703, CC BY 2.0 FR]
+Nuair chonaic sí ná glacfidís cómhairle a leasa uaithi isé rud a dhéin sí ’ná imtheacht uatha ar fad. [Wikisource: Aesop a tháinig go h-Éirinn/An Áinle agus na h-Éin Eile, pre-standard, public domain]
+óir do imthigh an tairgead uáinn. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>https://tatoeba.org/en/sentences/show/875703
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_%C3%81inle_agus_na_h-%C3%89in_Eile
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
 https://www.teanglann.ie/en/fgb/imigh</t>
         </is>
       </c>
-      <c r="M131" s="3" t="inlineStr"/>
-      <c r="N131" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr"/>
+      <c r="P130" s="3" t="inlineStr"/>
+      <c r="Q130" s="3" t="inlineStr"/>
+      <c r="R130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>samhlaigh le</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>samhlaigh</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>le</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>new verb</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>to expect (something) of (someone)</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>Thug sé an íde (nó an oidhe) chéanna do laochra eile dá chuid: M., a cuireadh i gcosúlacht le Cú Chulainn agus le Suibhne; an Cú Chulainnín in 'Cé Acu' (An tSraith ar Lár); lánúin 'Mhuintir na Croise' (An tSraith Tógtha) a samhlaítear le Diarmaid agus Gráinne; agus fiú J., ar féidir a bhás a chur i gcosúlacht le bás Chonaire in Togail Bruidne Da Derga. [UD_Irish-IDT 1866, CC BY-SA 3.0]</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/samhlaigh_le#Irish
+https://www.teanglann.ie/en/fgb/samhlaigh</t>
+        </is>
+      </c>
       <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="3" t="inlineStr"/>
+      <c r="Q131" s="3" t="inlineStr"/>
+      <c r="R131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>samhlaigh le</t>
+          <t>breathnaigh ó</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>samhlaigh</t>
+          <t>breathnaigh</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>ó</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -7527,12 +8826,12 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>to expect (something) of (someone)</t>
+          <t>look (idly) around oneself</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>0</v>
@@ -7540,36 +8839,38 @@
       <c r="J132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Thug sé an íde (nó an oidhe) chéanna do laochra eile dá chuid: M., a cuireadh i gcosúlacht le Cú Chulainn agus le Suibhne; an Cú Chulainnín in 'Cé Acu' (An tSraith ar Lár); lánúin 'Mhuintir na Croise' (An tSraith Tógtha) a samhlaítear le Diarmaid agus Gráinne; agus fiú J., ar féidir a bhás a chur i gcosúlacht le bás Chonaire in Togail Bruidne Da Derga. [UD_Irish-IDT 1866, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/samhlaigh_le#Irish
-https://www.teanglann.ie/en/fgb/samhlaigh</t>
-        </is>
-      </c>
-      <c r="M132" s="3" t="inlineStr"/>
-      <c r="N132" s="3" t="inlineStr"/>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/breathnaigh_ó#Irish
+https://www.teanglann.ie/en/fgb/breathnaigh</t>
+        </is>
+      </c>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="3" t="inlineStr"/>
+      <c r="Q132" s="3" t="inlineStr"/>
+      <c r="R132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>breathnaigh ó</t>
+          <t>bí amach as</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>breathnaigh</t>
+          <t>bí</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ó</t>
+          <t>amach as</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -7578,14 +8879,10 @@
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>look (idly) around oneself</t>
-        </is>
-      </c>
+      <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>0</v>
@@ -7593,22 +8890,37 @@
       <c r="J133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/breathnaigh_ó#Irish
-https://www.teanglann.ie/en/fgb/breathnaigh</t>
-        </is>
-      </c>
-      <c r="M133" s="3" t="inlineStr"/>
-      <c r="N133" s="3" t="inlineStr"/>
+      <c r="K133" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>Fágann siad scoilt agus cogadh ina ndiaidh chun go mbeidh siad ábalta a rá lena bpobal féin: féach, nach maith an rud é go bhfuilimid amach as sin. [UD_Irish-IDT 1400, CC BY-SA 3.0]
+Clúdaigh do thosach leis mar beidh sé fuar istoíche as so amach agus cuir do dhóthain plaincéadaí ar an leaba. [UD_Irish-IDT 2506, CC BY-SA 3.0]
+Tuairsc ón Chúirt: Bhíos istigh ann arís ar maidin ach fós ní raibh an toghairm churtha amach roimh ré as #Gaeilge mar a d'iarr mé orthu #fb [UD_Irish-TwittIrish LTC_1156, CC BY-SA 4.0]
+Ach cuimhnigh ormsa anuáir beathar go maith agad, agus guidhim thú taisbéin cineal damh, agus cuimhnigh do Pháraó mé agus beir amach as a tighsi mé. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Do bhí a lán bailithe amach as tigh an óil san am so ach ní raibh an fear mór. [Wikisource: An t-Oileánach/13, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="3" t="inlineStr"/>
+      <c r="Q133" s="3" t="inlineStr"/>
+      <c r="R133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>bí amach as</t>
+          <t>bí isteach ar</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -7618,7 +8930,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>amach as</t>
+          <t>isteach ar</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -7638,27 +8950,37 @@
       <c r="J134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Fágann siad scoilt agus cogadh ina ndiaidh chun go mbeidh siad ábalta a rá lena bpobal féin: féach, nach maith an rud é go bhfuilimid amach as sin. [UD_Irish-IDT 1400, CC BY-SA 3.0]
-Clúdaigh do thosach leis mar beidh sé fuar istoíche as so amach agus cuir do dhóthain plaincéadaí ar an leaba. [UD_Irish-IDT 2506, CC BY-SA 3.0]
-Tuairsc ón Chúirt: Bhíos istigh ann arís ar maidin ach fós ní raibh an toghairm churtha amach roimh ré as #Gaeilge mar a d'iarr mé orthu #fb [UD_Irish-TwittIrish LTC_1156, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M134" s="3" t="inlineStr"/>
-      <c r="N134" s="3" t="inlineStr"/>
+      <c r="K134" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Tá beagnach ocht mbliana imithe isteach i muileann an ama orm, ó scríobhadh an léirmheas sin, agus níor chuir mé aon díolaim eile filíochta i gcló i rith na tréimhse sin. [UD_Irish-IDT 667, CC BY-SA 3.0]
+Bhí dhá ard mhóra ar an slí isteach go dtí an Daingean, Ard Leataoibh agus Ard Bhaile an nÁith. [UD_Irish-IDT 864, CC BY-SA 3.0]
+Tá cáil mhaith ar Bornholm, oileán idileach Danmhargach ag béal na Mara Bailt isteach agus amach ar leathbhealach idir an tSualainn, an Ghearmáin agus an Pholainn, as a scadán deataithe. [UD_Irish-IDT 3323, CC BY-SA 3.0]
+Do bhí seana-mhná isteach agus amach ar thuairisc mo choise. [Wikisource: An t-Oileánach/9, pre-standard, public domain]
+Bhí fhios aige gurbh aisteach ar fad iad baramhla sean-daoine i gCluaintobair i dtaoibh an ghrádha agus i dtaoibh pósta—pósadh na n-ógán go h-áirithe. [Wikisource: Caoimhghin Ó Cearnaigh/14, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/9
+https://wikisource.org/wiki/Caoimhghin_%C3%93_Cearnaigh/14
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O134" s="3" t="inlineStr"/>
       <c r="P134" s="3" t="inlineStr"/>
+      <c r="Q134" s="3" t="inlineStr"/>
+      <c r="R134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>bí isteach ar</t>
+          <t>bí suas le</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -7668,7 +8990,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>isteach ar</t>
+          <t>suas le</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7680,45 +9002,56 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Tá beagnach ocht mbliana imithe isteach i muileann an ama orm, ó scríobhadh an léirmheas sin, agus níor chuir mé aon díolaim eile filíochta i gcló i rith na tréimhse sin. [UD_Irish-IDT 667, CC BY-SA 3.0]
-Bhí dhá ard mhóra ar an slí isteach go dtí an Daingean, Ard Leataoibh agus Ard Bhaile an nÁith. [UD_Irish-IDT 864, CC BY-SA 3.0]
-Tá cáil mhaith ar Bornholm, oileán idileach Danmhargach ag béal na Mara Bailt isteach agus amach ar leathbhealach idir an tSualainn, an Ghearmáin agus an Pholainn, as a scadán deataithe. [UD_Irish-IDT 3323, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M135" s="3" t="inlineStr"/>
-      <c r="N135" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>'Nach bhfuil sé sin suas le deich mbliana fichead ó shoin! [UD_Irish-IDT 1656, CC BY-SA 3.0]
+Bhí suas le deich gcruinniú ag gach Coiste Réigiúnach i rith 2006. [UD_Irish-IDT 4851, CC BY-SA 3.0]
+Táim chun briseadh suas le Tomás. = I'm going to break up with Tom. [Tatoeba 10317478, CC BY 2.0 FR]
+Acht béadsa suas leis.” [Wikisource: Aesop a tháinig go h-Éirinn/An Mada Ruadh agus an Machtíre, pre-standard, public domain]
+Tráithnín bán feósaidhe bhí suas agus anuas le dhá órdlach go leith ar a fhaid agus iad ag iarraidh é thógáil agus é thabhairt leó ar iomchur. [Wikisource: An Crann Géagach/Fleadh aoibhinn, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>https://tatoeba.org/en/sentences/show/10317478
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Mada_Ruadh_agus_an_Macht%C3%ADre
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/Fleadh_aoibhinn
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="3" t="inlineStr"/>
+      <c r="Q135" s="3" t="inlineStr"/>
+      <c r="R135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>bí suas le</t>
+          <t>clóigh le</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>bí</t>
+          <t>clóigh</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>suas le</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -7727,49 +9060,53 @@
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>to accustom to</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>'Nach bhfuil sé sin suas le deich mbliana fichead ó shoin! [UD_Irish-IDT 1656, CC BY-SA 3.0]
-Bhí suas le deich gcruinniú ag gach Coiste Réigiúnach i rith 2006. [UD_Irish-IDT 4851, CC BY-SA 3.0]
-Táim chun briseadh suas le Tomás. = I'm going to break up with Tom. [Tatoeba 10317478, CC BY 2.0 FR]</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>https://tatoeba.org/en/sentences/show/10317478
-https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M136" s="3" t="inlineStr"/>
-      <c r="N136" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/clóigh_le#Irish
+https://www.teanglann.ie/en/fgb/clóigh</t>
+        </is>
+      </c>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="3" t="inlineStr"/>
+      <c r="Q136" s="3" t="inlineStr"/>
+      <c r="R136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>clóigh le</t>
+          <t>díon as</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>clóigh</t>
+          <t>díon</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7780,7 +9117,7 @@
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>to accustom to</t>
+          <t>Connacht form of déan as</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
@@ -7793,27 +9130,33 @@
       <c r="J137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/clóigh_le#Irish
-https://www.teanglann.ie/en/fgb/clóigh</t>
-        </is>
-      </c>
-      <c r="M137" s="3" t="inlineStr"/>
-      <c r="N137" s="3" t="inlineStr"/>
+      <c r="K137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/díon_as#Irish
+https://www.teanglann.ie/en/fgb/díon</t>
+        </is>
+      </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr"/>
+      <c r="Q137" s="3" t="inlineStr"/>
+      <c r="R137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>díon as</t>
+          <t>díonamh as</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>díon</t>
+          <t>díonamh</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7829,7 +9172,7 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Connacht form of déan as</t>
+          <t>Connacht form of déanamh as</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
@@ -7842,27 +9185,33 @@
       <c r="J138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/díon_as#Irish
-https://www.teanglann.ie/en/fgb/díon</t>
-        </is>
-      </c>
-      <c r="M138" s="3" t="inlineStr"/>
-      <c r="N138" s="3" t="inlineStr"/>
+      <c r="K138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/díonamh_as#Irish
+https://www.teanglann.ie/en/fgb/díonamh</t>
+        </is>
+      </c>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="3" t="inlineStr"/>
+      <c r="Q138" s="3" t="inlineStr"/>
+      <c r="R138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>díonamh as</t>
+          <t>díonann as</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>díonamh</t>
+          <t>díonann</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7878,7 +9227,7 @@
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Connacht form of déanamh as</t>
+          <t>Connacht form of déanann as</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
@@ -7891,27 +9240,33 @@
       <c r="J139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/díonamh_as#Irish
-https://www.teanglann.ie/en/fgb/díonamh</t>
-        </is>
-      </c>
-      <c r="M139" s="3" t="inlineStr"/>
-      <c r="N139" s="3" t="inlineStr"/>
+      <c r="K139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/díonann_as#Irish
+https://www.teanglann.ie/en/fgb/díonann</t>
+        </is>
+      </c>
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="3" t="inlineStr"/>
+      <c r="Q139" s="3" t="inlineStr"/>
+      <c r="R139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>díonann as</t>
+          <t>díonfaidh as</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>díonann</t>
+          <t>díonfaidh</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7927,7 +9282,7 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Connacht form of déanann as</t>
+          <t>Connacht form of déanfaidh as</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
@@ -7940,27 +9295,33 @@
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/díonann_as#Irish
-https://www.teanglann.ie/en/fgb/díonann</t>
-        </is>
-      </c>
-      <c r="M140" s="3" t="inlineStr"/>
-      <c r="N140" s="3" t="inlineStr"/>
+      <c r="K140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/díonfaidh_as#Irish
+https://www.teanglann.ie/en/fgb/díonfaidh</t>
+        </is>
+      </c>
       <c r="O140" s="3" t="inlineStr"/>
       <c r="P140" s="3" t="inlineStr"/>
+      <c r="Q140" s="3" t="inlineStr"/>
+      <c r="R140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>díonfaidh as</t>
+          <t>díonta as</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>díonfaidh</t>
+          <t>díonta</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7976,7 +9337,7 @@
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Connacht form of déanfaidh as</t>
+          <t>Connacht form of déanta as</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
@@ -7989,32 +9350,38 @@
       <c r="J141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/díonfaidh_as#Irish
-https://www.teanglann.ie/en/fgb/díonfaidh</t>
-        </is>
-      </c>
-      <c r="M141" s="3" t="inlineStr"/>
-      <c r="N141" s="3" t="inlineStr"/>
+      <c r="K141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/díonta_as#Irish
+https://www.teanglann.ie/en/fgb/díonta</t>
+        </is>
+      </c>
       <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="3" t="inlineStr"/>
+      <c r="Q141" s="3" t="inlineStr"/>
+      <c r="R141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>díonta as</t>
+          <t>lódáil suas</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>díonta</t>
+          <t>lódáil</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>suas</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -8025,7 +9392,7 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Connacht form of déanta as</t>
+          <t>to upload</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
@@ -8038,32 +9405,38 @@
       <c r="J142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/díonta_as#Irish
-https://www.teanglann.ie/en/fgb/díonta</t>
-        </is>
-      </c>
-      <c r="M142" s="3" t="inlineStr"/>
-      <c r="N142" s="3" t="inlineStr"/>
+      <c r="K142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/lódáil_suas#Irish
+https://www.teanglann.ie/en/fgb/lódáil</t>
+        </is>
+      </c>
       <c r="O142" s="3" t="inlineStr"/>
       <c r="P142" s="3" t="inlineStr"/>
+      <c r="Q142" s="3" t="inlineStr"/>
+      <c r="R142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>lódáil suas</t>
+          <t>mór le</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>lódáil</t>
+          <t>mór</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>suas</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -8074,7 +9447,7 @@
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>to upload</t>
+          <t>friendly with</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
@@ -8087,27 +9460,33 @@
       <c r="J143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/lódáil_suas#Irish
-https://www.teanglann.ie/en/fgb/lódáil</t>
-        </is>
-      </c>
-      <c r="M143" s="3" t="inlineStr"/>
-      <c r="N143" s="3" t="inlineStr"/>
+      <c r="K143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/mór_le#Irish
+https://www.teanglann.ie/en/fgb/mór</t>
+        </is>
+      </c>
       <c r="O143" s="3" t="inlineStr"/>
       <c r="P143" s="3" t="inlineStr"/>
+      <c r="Q143" s="3" t="inlineStr"/>
+      <c r="R143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>mór le</t>
+          <t>neartaigh le</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>mór</t>
+          <t>neartaigh</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8123,7 +9502,7 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>friendly with</t>
+          <t>to abet (assist or encourage in crime) | to corroborate (confirm or support with additional evidence)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
@@ -8136,32 +9515,38 @@
       <c r="J144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/mór_le#Irish
-https://www.teanglann.ie/en/fgb/mór</t>
-        </is>
-      </c>
-      <c r="M144" s="3" t="inlineStr"/>
-      <c r="N144" s="3" t="inlineStr"/>
+      <c r="K144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/neartaigh_le#Irish
+https://www.teanglann.ie/en/fgb/neartaigh</t>
+        </is>
+      </c>
       <c r="O144" s="3" t="inlineStr"/>
       <c r="P144" s="3" t="inlineStr"/>
+      <c r="Q144" s="3" t="inlineStr"/>
+      <c r="R144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>neartaigh le</t>
+          <t>scaoil amach</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>neartaigh</t>
+          <t>scaoil</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>amach</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -8172,7 +9557,7 @@
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>to abet (assist or encourage in crime) | to corroborate (confirm or support with additional evidence)</t>
+          <t>to let out | to release, loosen</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
@@ -8185,22 +9570,33 @@
       <c r="J145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/neartaigh_le#Irish
-https://www.teanglann.ie/en/fgb/neartaigh</t>
-        </is>
-      </c>
-      <c r="M145" s="3" t="inlineStr"/>
-      <c r="N145" s="3" t="inlineStr"/>
+      <c r="K145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>Scaoileas scíobas amach chucha. [Wikisource: An t-Oileánach/15, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_amach#Irish
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/15
+https://www.teanglann.ie/en/fgb/scaoil</t>
+        </is>
+      </c>
       <c r="O145" s="3" t="inlineStr"/>
       <c r="P145" s="3" t="inlineStr"/>
+      <c r="Q145" s="3" t="inlineStr"/>
+      <c r="R145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>scaoil amach</t>
+          <t>scaoil as</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -8210,7 +9606,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>amach</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -8221,7 +9617,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>to let out | to release, loosen</t>
+          <t>to let out of | to fire from | to break loose from</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -8234,22 +9630,33 @@
       <c r="J146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_amach#Irish
+      <c r="K146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>roinnt nómantaí tharraing sé leis a phíopa agus gan aon fhocal cainte aige, acht fé dheireadh scaoil sé a dhá láimh as a chéile agus bhain sé an píopa as a bheul agus labhair sé. [Wikisource: Eachtradh Eibhlís i dTír na nIongantas/V, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_as#Irish
+https://wikisource.org/wiki/Eachtradh_Eibhl%C3%ADs_i_dT%C3%ADr_na_nIongantas/V
 https://www.teanglann.ie/en/fgb/scaoil</t>
         </is>
       </c>
-      <c r="M146" s="3" t="inlineStr"/>
-      <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="3" t="inlineStr"/>
       <c r="P146" s="3" t="inlineStr"/>
+      <c r="Q146" s="3" t="inlineStr"/>
+      <c r="R146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>scaoil as</t>
+          <t>scaoil de</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -8259,7 +9666,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>de</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -8270,7 +9677,7 @@
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>to let out of | to fire from | to break loose from</t>
+          <t>to let go, release, undo</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
@@ -8283,22 +9690,28 @@
       <c r="J147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K147" s="2" t="inlineStr"/>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_as#Irish
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_de#Irish
 https://www.teanglann.ie/en/fgb/scaoil</t>
         </is>
       </c>
-      <c r="M147" s="3" t="inlineStr"/>
-      <c r="N147" s="3" t="inlineStr"/>
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="3" t="inlineStr"/>
+      <c r="Q147" s="3" t="inlineStr"/>
+      <c r="R147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>scaoil de</t>
+          <t>scaoil faoi</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -8308,7 +9721,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>faoi</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -8319,7 +9732,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>to let go, release, undo</t>
+          <t>to set about</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
@@ -8327,37 +9740,49 @@
         <v>0</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_de#Irish
+      <c r="K148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>Rugais leat fós iar gach seal iad uile ag dol fa dhligheadh gor sgaoilset siar agus soir ag port Eirne fad lamhaibh. [UD_Irish-Cadhan bardic_1387-32, pre-standard, CC BY-SA 4.0]
+scaoileadh iad fá an ngleann mar a mbidheadh fuaim [Wikisource: Cnuasacht trágha/Seán gan Eagla, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wiktionary.org/wiki/scaoil_faoi#Irish
+https://wikisource.org/wiki/Cnuasacht_tr%C3%A1gha/Se%C3%A1n_gan_Eagla
 https://www.teanglann.ie/en/fgb/scaoil</t>
         </is>
       </c>
-      <c r="M148" s="3" t="inlineStr"/>
-      <c r="N148" s="3" t="inlineStr"/>
       <c r="O148" s="3" t="inlineStr"/>
       <c r="P148" s="3" t="inlineStr"/>
+      <c r="Q148" s="3" t="inlineStr"/>
+      <c r="R148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>scaoil faoi</t>
+          <t>beir do</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>scaoil</t>
+          <t>beir</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>faoi</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -8366,51 +9791,57 @@
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>to set about</t>
-        </is>
-      </c>
+      <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Rugais leat fós iar gach seal iad uile ag dol fa dhligheadh gor sgaoilset siar agus soir ag port Eirne fad lamhaibh. [UD_Irish-Cadhan bardic_1387-32, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wiktionary.org/wiki/scaoil_faoi#Irish
-https://www.teanglann.ie/en/fgb/scaoil</t>
-        </is>
-      </c>
-      <c r="M149" s="3" t="inlineStr"/>
-      <c r="N149" s="3" t="inlineStr"/>
+      <c r="K149" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>D'inis sí an scéal ar fad di - gur rugadh iníon óg rua d'Eithne, an Bhanríon Óg, beagnach seacht mbliana déag roimhe sin agus gur cailleadh í i dtinneas clainne. [UD_Irish-IDT 86, CC BY-SA 3.0]
+A Phádraig Uí Chaiticín beirim an sbhae duit Ar a bhfaca mé féin de bhádóirín fóill Le féile, le hoineach, le tuiscint is le méin mhaith Is ní fhaca mé féin do shárú go fóill. [UD_Irish-IDT 267, CC BY-SA 3.0]
+Agus do Enoch rugadh Irad agus do ghein Irad Mehujael, agus do ghein Mehujael Metusael, agus do ghein Metusael Lamech. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]
+Agus tárla anuáir do thosuigheadar na daoine ar líonadh ar dhruim na talmhan agus rugadh ingheana dhóibh. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/beir</t>
+        </is>
+      </c>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="3" t="inlineStr"/>
+      <c r="Q149" s="3" t="inlineStr"/>
+      <c r="R149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>beir do</t>
+          <t>caith de</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>beir</t>
+          <t>caith</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>de</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -8430,36 +9861,46 @@
       <c r="J150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>D'inis sí an scéal ar fad di - gur rugadh iníon óg rua d'Eithne, an Bhanríon Óg, beagnach seacht mbliana déag roimhe sin agus gur cailleadh í i dtinneas clainne. [UD_Irish-IDT 86, CC BY-SA 3.0]
-A Phádraig Uí Chaiticín beirim an sbhae duit Ar a bhfaca mé féin de bhádóirín fóill Le féile, le hoineach, le tuiscint is le méin mhaith Is ní fhaca mé féin do shárú go fóill. [UD_Irish-IDT 267, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/beir</t>
-        </is>
-      </c>
-      <c r="M150" s="3" t="inlineStr"/>
-      <c r="N150" s="3" t="inlineStr"/>
+      <c r="K150" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>De ghnáth nuair atá duine éigin eile i mbun peannaireachta seachas an té atá faoi chaibidil sa dírbheathaisnéis caitear an caidreamh eatarthu beirt a scrúdú go mion. [UD_Irish-IDT 253, CC BY-SA 3.0]
+'Chaith mé díom mála na bhfód, agus sháigh an bior i gceann acu agus thug tine dó. [UD_Irish-IDT 1457, CC BY-SA 3.0]
+is dócha nár chaith sé a leithéid de shéire ó rinne sé comhnaidhe sa gcoiléar! [Wikisource: An Crann Géagach/An Sean-choiléar, pre-standard, public domain]
+Bhris mé cuid díobh faoi m’fhiaclaibh féin agus chaith mé ceann díobh chuig an iorruidh. [Wikisource: An Crann Géagach/An Sean-choiléar, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Sean-choil%C3%A9ar
+https://wikisource.org/wiki/An_Crann_G%C3%A9agach/An_Sean-choil%C3%A9ar
+https://www.teanglann.ie/en/fgb/caith</t>
+        </is>
+      </c>
       <c r="O150" s="3" t="inlineStr"/>
       <c r="P150" s="3" t="inlineStr"/>
+      <c r="Q150" s="3" t="inlineStr"/>
+      <c r="R150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>caith de</t>
+          <t>cas do</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>caith</t>
+          <t>cas</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -8479,36 +9920,46 @@
       <c r="J151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>De ghnáth nuair atá duine éigin eile i mbun peannaireachta seachas an té atá faoi chaibidil sa dírbheathaisnéis caitear an caidreamh eatarthu beirt a scrúdú go mion. [UD_Irish-IDT 253, CC BY-SA 3.0]
-'Chaith mé díom mála na bhfód, agus sháigh an bior i gceann acu agus thug tine dó. [UD_Irish-IDT 1457, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/caith</t>
-        </is>
-      </c>
-      <c r="M151" s="3" t="inlineStr"/>
-      <c r="N151" s="3" t="inlineStr"/>
+      <c r="K151" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>Ná fuil aon amhras air ná go gcasfaidh an roth arís duit. [UD_Irish-IDT 1902, CC BY-SA 3.0]
+Nuair a tháinig muid ní ba gaire di thug muid faoi deara go raibh sí ag casadh amhráin di féin. [UD_Irish-IDT 2738, CC BY-SA 3.0]
+Do lúb sé é agus do chas sé é, acht do theip air é bhriseadh. [Wikisource: Aesop a tháinig go h-Éirinn/An Dórnán Slat, pre-standard, public domain]
+Do lean sí uirthi, is cosmhail, ag iarraidh eolais an bhóthair ar na daoinibh do casadh di, ag coisidheacht i gcomhnaidhe, nó gur fhág sí ina diaidh Cois Locha, agus an Spidéal, agus Gaillimh, agus an tÓrán Mór, agus Baile Átha an Ríogh, agus Cill Chonaill, agus Béal Átha na Sluaigheadh, agus Béal Átha Luain, agus an Muileann Cearr, agus Magh Nuadhad, nó sa deireadh go bhfaca sí uaithi tighthe Bha [Wikisource: An Mháthair agus Sgéalta Eile/Bríghid na nAmhrán, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_D%C3%B3rn%C3%A1n_Slat
+https://wikisource.org/wiki/An_Mh%C3%A1thair_agus_Sg%C3%A9alta_Eile/Br%C3%ADghid_na_nAmhr%C3%A1n
+https://www.teanglann.ie/en/fgb/cas</t>
+        </is>
+      </c>
       <c r="O151" s="3" t="inlineStr"/>
       <c r="P151" s="3" t="inlineStr"/>
+      <c r="Q151" s="3" t="inlineStr"/>
+      <c r="R151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>cas do</t>
+          <t>pléigh ar</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>cas</t>
+          <t>pléigh</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -8528,36 +9979,42 @@
       <c r="J152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Ná fuil aon amhras air ná go gcasfaidh an roth arís duit. [UD_Irish-IDT 1902, CC BY-SA 3.0]
-Nuair a tháinig muid ní ba gaire di thug muid faoi deara go raibh sí ag casadh amhráin di féin. [UD_Irish-IDT 2738, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/cas</t>
-        </is>
-      </c>
-      <c r="M152" s="3" t="inlineStr"/>
-      <c r="N152" s="3" t="inlineStr"/>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Is féidir tuiscint an pháiste ar an Pleanáil gcróineolaíocht a chothú (rud a phléitear ar bhealach níos iomláine sna treoirlínte do mhúinteoirí a ghabhann leis seo) trí línte ama agus mhodhanna eile a úsáid. [UD_Irish-IDT 2599, CC BY-SA 3.0]
+@user1530 @user1681. Óró! Ach pléifimid 20ú Bealtaine ar aon chaoi.... ✊ #AchtGaeilge https://t.co/KDvOjIwbO3 [UD_Irish-TwittIrish NTC_291, CC BY-SA 4.0]</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.teanglann.ie/en/fgb/pléigh</t>
+        </is>
+      </c>
       <c r="O152" s="3" t="inlineStr"/>
       <c r="P152" s="3" t="inlineStr"/>
+      <c r="Q152" s="3" t="inlineStr"/>
+      <c r="R152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>pléigh ar</t>
+          <t>samhlaigh do</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>pléigh</t>
+          <t>samhlaigh</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>do</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -8577,36 +10034,46 @@
       <c r="J153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Is féidir tuiscint an pháiste ar an Pleanáil gcróineolaíocht a chothú (rud a phléitear ar bhealach níos iomláine sna treoirlínte do mhúinteoirí a ghabhann leis seo) trí línte ama agus mhodhanna eile a úsáid. [UD_Irish-IDT 2599, CC BY-SA 3.0]
-@user1530 @user1681. Óró! Ach pléifimid 20ú Bealtaine ar aon chaoi.... ✊ #AchtGaeilge https://t.co/KDvOjIwbO3 [UD_Irish-TwittIrish NTC_291, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/pléigh</t>
-        </is>
-      </c>
-      <c r="M153" s="3" t="inlineStr"/>
-      <c r="N153" s="3" t="inlineStr"/>
+      <c r="K153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>Bhíodh sí dá shamhlú dó gach áit - an seibineach de ghiorria a d'éiríodh as a leaba dhearg - an t-éan ag ceiliúr ar an gcraobh - an bradán san abhainn, an breac sa loch - gach rud beo dearfa ba ar Mháirín a smaoiníodh sé nuair a d'fheicfeadh sé iad. [UD_Irish-IDT 1310, CC BY-SA 3.0]
+Samhlaítear do Mháirtín Ó Direáin go bhfuil substaint agus buaine ag baint leis an saol traidisiúnta as ar fáisceadh é. [UD_Irish-IDT 2704, CC BY-SA 3.0]
+Lonnaigh a shúile achar fada ar a haghaidh agus ar a gruaig: agus, ag samhlú dhó mar a bheadh sí ag an am sin, in aimsir a céad áilleacht gearrchaile, tháinig trua ait, chairdiúil ina anam. [Wikisource: Muintir Bhaile Átha Cliath/Na Mairbh, pre-standard, public domain]
+Agus nuair a chonacadar-san é ag siubhal ar an bhfaraige cheapadar gur samhail a bhí ann agus do liúgadar. [Wikisource: Na Cheithre Soisgéil/Marcus, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Muintir_Bhaile_%C3%81tha_Cliath/Na_Mairbh
+https://wikisource.org/wiki/Na_Cheithre_Soisg%C3%A9il/Marcus
+https://www.teanglann.ie/en/fgb/samhlaigh</t>
+        </is>
+      </c>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
+      <c r="Q153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>samhlaigh do</t>
+          <t>scaoil ar</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>samhlaigh</t>
+          <t>scaoil</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -8626,36 +10093,46 @@
       <c r="J154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Bhíodh sí dá shamhlú dó gach áit - an seibineach de ghiorria a d'éiríodh as a leaba dhearg - an t-éan ag ceiliúr ar an gcraobh - an bradán san abhainn, an breac sa loch - gach rud beo dearfa ba ar Mháirín a smaoiníodh sé nuair a d'fheicfeadh sé iad. [UD_Irish-IDT 1310, CC BY-SA 3.0]
-Samhlaítear do Mháirtín Ó Direáin go bhfuil substaint agus buaine ag baint leis an saol traidisiúnta as ar fáisceadh é. [UD_Irish-IDT 2704, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/samhlaigh</t>
-        </is>
-      </c>
-      <c r="M154" s="3" t="inlineStr"/>
-      <c r="N154" s="3" t="inlineStr"/>
+      <c r="K154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Ní scaoilfaidh an Chomhairle Ealaion eolas faoi chinneadh i leith deontas ar an nguthán. [UD_Irish-IDT 1735, CC BY-SA 3.0]
+Ar an tríochadú lá d'Eanáir, míle naoi gcéad seachtó's a dó scaoil na Paraí leis an daoine is d'fhág marbh 'na gcosair chró. [UD_Irish-IDT 2057, CC BY-SA 3.0]
+scaoil orainn a’ guth, má ’s é do thoil é,” ar seisean. [Wikisource: An t-Oileánach/13, pre-standard, public domain]
+“Scaoil siar aríst iad,” ar siad-san, mar nár tháinig aon tsiolladh eile gaoithe ar feadh an méid sin aimsire. [Wikisource: An t-Oileánach/23, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/An_t-Oile%C3%A1nach/13
+https://wikisource.org/wiki/An_t-Oile%C3%A1nach/23
+https://www.teanglann.ie/en/fgb/scaoil</t>
+        </is>
+      </c>
       <c r="O154" s="3" t="inlineStr"/>
       <c r="P154" s="3" t="inlineStr"/>
+      <c r="Q154" s="3" t="inlineStr"/>
+      <c r="R154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>scaoil ar</t>
+          <t>beir le</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>scaoil</t>
+          <t>beir</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>le</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -8667,44 +10144,54 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Ní scaoilfaidh an Chomhairle Ealaion eolas faoi chinneadh i leith deontas ar an nguthán. [UD_Irish-IDT 1735, CC BY-SA 3.0]
-Ar an tríochadú lá d'Eanáir, míle naoi gcéad seachtó's a dó scaoil na Paraí leis an daoine is d'fhág marbh 'na gcosair chró. [UD_Irish-IDT 2057, CC BY-SA 3.0]</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/scaoil</t>
-        </is>
-      </c>
-      <c r="M155" s="3" t="inlineStr"/>
-      <c r="N155" s="3" t="inlineStr"/>
+      <c r="K155" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>Dar leis an Ríordánach sa dán Teitheadh, is cosúla an fhilíocht le sacraimint eile, an fhaoistin, ná le comaoineach naofa; agus tugann sé peaca ar an dán dá réir: Do rugas liom don eaglais Mo chnuasach nuapheacaí, Do chuireas iad in eagar Don fhoilsitheoir a bhíonn Ag cló-dhearmhad peacaí. [UD_Irish-IDT 506, CC BY-SA 3.0]
+Agus do ghlacadarsan Iósa, agus rugadar léo hé. [UD_Irish-Cadhan eoin-870, pre-standard, CC BY-SA 4.0]
+Do rug sé leis isteach ’na phluais féin é. [Wikisource: Aesop a tháinig go h-Éirinn/An tSaint agus an Formad, pre-standard, public domain]
+Agus rug Abram Sárai a bhean leis agus Lot mar a dhearbhrathar agus a substaint uile noch do chruinnigheadar, agus na hanmanna fúaradar ann Háran: agus dochúadar amach do dhul go tír Canaáin, agus tangadar go tír Chanaáin. [Wikisource: An Biobla Naomhtha/Genesis, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_tSaint_agus_an_Formad
+https://wikisource.org/wiki/An_Biobla_Naomhtha/Genesis
+https://www.teanglann.ie/en/fgb/beir</t>
+        </is>
+      </c>
       <c r="O155" s="3" t="inlineStr"/>
       <c r="P155" s="3" t="inlineStr"/>
+      <c r="Q155" s="3" t="inlineStr"/>
+      <c r="R155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>beir le</t>
+          <t>bí síos</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>beir</t>
+          <t>bí</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>síos</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -8719,75 +10206,36 @@
         <v>1</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Dar leis an Ríordánach sa dán Teitheadh, is cosúla an fhilíocht le sacraimint eile, an fhaoistin, ná le comaoineach naofa; agus tugann sé peaca ar an dán dá réir: Do rugas liom don eaglais Mo chnuasach nuapheacaí, Do chuireas iad in eagar Don fhoilsitheoir a bhíonn Ag cló-dhearmhad peacaí. [UD_Irish-IDT 506, CC BY-SA 3.0]
-Agus do ghlacadarsan Iósa, agus rugadar léo hé. [UD_Irish-Cadhan eoin-870, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/beir</t>
-        </is>
-      </c>
-      <c r="M156" s="3" t="inlineStr"/>
-      <c r="N156" s="3" t="inlineStr"/>
+      <c r="K156" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>Má tharlaíonn seo déantar airgead agus maoin an duine a dháileadh de réir na rialacha atá leagtha síos san Acht Comharbachta, 1965. [UD_Irish-IDT 2946, CC BY-SA 3.0]
+Bhí a ruball síos leis agus a chorp ar bharra creatha; bhí an créatúr conáilte, agus é ag siubhal thart agus thart ar an chábán gan fhios aige cá rachadh sé. [UD_Irish-Cadhan scairt-281, pre-standard, CC BY-SA 4.0]
+Nuair bhíon sé síos ní bhíon truagh dhó. [Wikisource: Aesop a tháinig go h-Éirinn/An Capal agus an t-Asal, pre-standard, public domain]
+Nuair bhíon sé síos ní bhíon truagh dhó. [Wikisource: Aesop a tháinig go h-Éirinn/An Cromán agus na Colúra, pre-standard, public domain]</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Capal_agus_an_t-Asal
+https://wikisource.org/wiki/Aesop_a_th%C3%A1inig_go_h-%C3%89irinn/An_Crom%C3%A1n_agus_na_Col%C3%BAra
+https://www.teanglann.ie/en/fgb/bí</t>
+        </is>
+      </c>
       <c r="O156" s="3" t="inlineStr"/>
       <c r="P156" s="3" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>bí síos</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>bí</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>síos</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>new verb</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Má tharlaíonn seo déantar airgead agus maoin an duine a dháileadh de réir na rialacha atá leagtha síos san Acht Comharbachta, 1965. [UD_Irish-IDT 2946, CC BY-SA 3.0]
-Bhí a ruball síos leis agus a chorp ar bharra creatha; bhí an créatúr conáilte, agus é ag siubhal thart agus thart ar an chábán gan fhios aige cá rachadh sé. [UD_Irish-Cadhan scairt-281, pre-standard, CC BY-SA 4.0]</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.teanglann.ie/en/fgb/bí</t>
-        </is>
-      </c>
-      <c r="M157" s="3" t="inlineStr"/>
-      <c r="N157" s="3" t="inlineStr"/>
-      <c r="O157" s="3" t="inlineStr"/>
-      <c r="P157" s="3" t="inlineStr"/>
+      <c r="Q156" s="3" t="inlineStr"/>
+      <c r="R156" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
